--- a/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
+++ b/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\15198\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DigitalHelper\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="138">
   <si>
     <t>密级：</t>
   </si>
@@ -467,6 +467,24 @@
     <t>新增5个需求对应的开发工作量</t>
   </si>
   <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>完善.vrma动作表情驱动</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>v1.2</t>
+  </si>
+  <si>
+    <t>需求条目无增删，完善动作表情驱动实现</t>
+  </si>
+  <si>
+    <t>动作表情联调与单元测试</t>
+  </si>
+  <si>
     <t>SUM</t>
   </si>
   <si>
@@ -479,24 +497,7 @@
     <t>数字人交互系统（安心健康助手）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>PM:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>安家谊</t>
-    </r>
+    <t>PM:安家谊</t>
   </si>
   <si>
     <t>担当:具体参与设计的成员名单</t>
@@ -550,7 +551,7 @@
     <t>品牌标识</t>
   </si>
   <si>
-    <t>静态显示圆形"安"字品牌标记（青绿色背景），作为系统 Logo</t>
+    <t>静态显示圆形"安"字品牌标记（青绿色背景），作为系统Logo</t>
   </si>
   <si>
     <t>○</t>
@@ -592,7 +593,7 @@
     <t>数字人模型渲染</t>
   </si>
   <si>
-    <t>使用 Three.js + three-vrm 加载本地 .vrm 模型并在舞台渲染；动作：加载后模型居中展示，支持鼠标拖动旋转、滚轮缩放</t>
+    <t>使用Three.js + three-vrm加载本地.vrm模型并在舞台渲染；动作：加载后模型居中展示，支持鼠标拖动旋转、滚轮缩放</t>
   </si>
   <si>
     <t>口型同步</t>
@@ -601,27 +602,27 @@
     <t>动态表现：播报语音时按音频能量驱动嘴型张合，形成说话口型</t>
   </si>
   <si>
+    <t>赵燕凯</t>
+  </si>
+  <si>
+    <t>自动眨眼与头部微动</t>
+  </si>
+  <si>
+    <t>动态表现：数字人按时长随机周期自动眨眼，静默时头部缓慢微动，说话时轻微点头</t>
+  </si>
+  <si>
+    <t>赵燕凯、魏鑫鸿</t>
+  </si>
+  <si>
+    <t>肢体动作</t>
+  </si>
+  <si>
+    <t>动态表现：挥手动作右臂抬起摆动后复位；支持播放.vrma动作文件（关键词触发一次/手动循环）；动作可完整显示表情（眨眼/口型/下巴），通过表情独占名单FULL_EXPRESSION_ACTIONS配置</t>
+  </si>
+  <si>
     <t>△</t>
   </si>
   <si>
-    <t>赵燕凯</t>
-  </si>
-  <si>
-    <t>自动眨眼与头部微动</t>
-  </si>
-  <si>
-    <t>动态表现：数字人按时长随机周期自动眨眼，静默时头部缓慢微动，说话时轻微点头</t>
-  </si>
-  <si>
-    <t>赵燕凯、魏鑫鸿</t>
-  </si>
-  <si>
-    <t>肢体动作</t>
-  </si>
-  <si>
-    <t>动态表现：挥手动作右臂抬起摆动后复位；支持播放 .vrma 动作文件（关键词触发一次/手动循环）</t>
-  </si>
-  <si>
     <t>魏鑫鸿</t>
   </si>
   <si>
@@ -703,7 +704,7 @@
     <t>文本输入框</t>
   </si>
   <si>
-    <t>占位提示"输入您的需求"；动作：用户输入需求文字（最长 500 字）</t>
+    <t>占位提示"输入您的需求"；动作：用户输入需求文字（最长500字）</t>
   </si>
   <si>
     <t>发送按钮</t>
@@ -721,34 +722,16 @@
     <t>动作：将后端返回的分句音频依次解码播放，逐句顺序播报并驱动口型</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>演示</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>设置</t>
-    </r>
+    <t>演示设置</t>
   </si>
   <si>
     <t>模型设置</t>
   </si>
   <si>
-    <t>选择 .vrm 模型</t>
-  </si>
-  <si>
-    <t>动作：点击弹出文件选择框，选择本地 .vrm 模型并加载渲染数字人</t>
-  </si>
-  <si>
-    <t>演示设置</t>
+    <t>选择.vrm模型</t>
+  </si>
+  <si>
+    <t>动作：点击弹出文件选择框，选择本地.vrm模型并加载渲染数字人</t>
   </si>
   <si>
     <t>动作设置</t>
@@ -760,10 +743,10 @@
     <t>动作：点击触发数字人挥手动作</t>
   </si>
   <si>
-    <t>选择 .vrma 动作</t>
-  </si>
-  <si>
-    <t>动作：点击选择本地 .vrma 动作文件并加载播放</t>
+    <t>选择.vrma动作</t>
+  </si>
+  <si>
+    <t>动作：点击选择本地.vrma动作文件并加载播放</t>
   </si>
   <si>
     <t>○：完成（通过评审或测试）   △：进行中   ×：未着手   N/A：不适用（没有此项活动）</t>
@@ -787,7 +770,7 @@
     <numFmt numFmtId="182" formatCode="0.0%"/>
     <numFmt numFmtId="183" formatCode="[$-409]yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="61">
+  <fonts count="59">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -818,12 +801,6 @@
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
     </font>
     <font>
@@ -886,11 +863,6 @@
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1996,188 +1968,188 @@
   </borders>
   <cellStyleXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="29" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="29" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="29" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="29" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="29" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="38">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="40">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="41">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="42" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="42">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="41">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="8" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="8" borderId="43">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="44">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="15" fontId="51" fillId="0" borderId="0"/>
-    <xf numFmtId="177" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="46">
+    <xf numFmtId="176" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="15" fontId="49" fillId="0" borderId="0"/>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="46">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="36">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="36">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0">
       <alignment vertical="top"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2188,152 +2160,149 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="59" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="59" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2342,304 +2311,295 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="60" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="60" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="26" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="27" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="27" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="28" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="181" fontId="19" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="16" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="15" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="61" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="61" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2850,6 +2810,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2897,6 +2858,7 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -3875,361 +3837,361 @@
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="8.75221238938053" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="9.87610619469027" style="143" customWidth="1"/>
-    <col min="2" max="2" width="10.3716814159292" style="143" customWidth="1"/>
-    <col min="3" max="3" width="9.87610619469027" style="143" customWidth="1"/>
-    <col min="4" max="4" width="8.75221238938053" style="143" customWidth="1"/>
-    <col min="5" max="5" width="10" style="143" customWidth="1"/>
-    <col min="6" max="6" width="9.75221238938053" style="143" customWidth="1"/>
-    <col min="7" max="7" width="9.50442477876106" style="143" customWidth="1"/>
-    <col min="8" max="8" width="16.7522123893805" style="143" customWidth="1"/>
-    <col min="9" max="16384" width="8.75221238938053" style="143" customWidth="1"/>
+    <col min="1" max="1" width="9.87610619469027" style="139" customWidth="1"/>
+    <col min="2" max="2" width="10.3716814159292" style="139" customWidth="1"/>
+    <col min="3" max="3" width="9.87610619469027" style="139" customWidth="1"/>
+    <col min="4" max="4" width="8.75221238938053" style="139" customWidth="1"/>
+    <col min="5" max="5" width="10" style="139" customWidth="1"/>
+    <col min="6" max="6" width="9.75221238938053" style="139" customWidth="1"/>
+    <col min="7" max="7" width="9.50442477876106" style="139" customWidth="1"/>
+    <col min="8" max="8" width="16.7522123893805" style="139" customWidth="1"/>
+    <col min="9" max="16384" width="8.75221238938053" style="139" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.75" customHeight="1" spans="1:8">
-      <c r="A1" s="144"/>
+      <c r="A1" s="140"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="144"/>
-    </row>
-    <row r="3" s="142" customFormat="1" ht="24" customHeight="1" spans="1:8">
-      <c r="A3" s="145" t="s">
+      <c r="A2" s="140"/>
+    </row>
+    <row r="3" s="138" customFormat="1" ht="24" customHeight="1" spans="1:8">
+      <c r="A3" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="146" t="s">
+      <c r="B3" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="148"/>
-    </row>
-    <row r="4" s="142" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
-      <c r="A4" s="149"/>
-      <c r="H4" s="150" t="s">
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="144"/>
+    </row>
+    <row r="4" s="138" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
+      <c r="A4" s="145"/>
+      <c r="H4" s="146" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="142" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
-      <c r="A5" s="149" t="s">
+    <row r="5" s="138" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
+      <c r="A5" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="147"/>
-      <c r="G5" s="151" t="s">
+      <c r="F5" s="143"/>
+      <c r="G5" s="147" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A6" s="152"/>
-      <c r="B6" s="153"/>
-      <c r="C6" s="153"/>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
-    </row>
-    <row r="7" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A7" s="154"/>
-      <c r="B7" s="148"/>
-      <c r="C7" s="148"/>
-      <c r="D7" s="148"/>
-      <c r="E7" s="148"/>
-      <c r="F7" s="148"/>
-      <c r="G7" s="148"/>
-      <c r="H7" s="148"/>
-    </row>
-    <row r="8" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A8" s="154"/>
-      <c r="B8" s="148"/>
-      <c r="C8" s="148"/>
-      <c r="D8" s="148"/>
-      <c r="E8" s="148"/>
-      <c r="F8" s="148"/>
-      <c r="G8" s="148"/>
-      <c r="H8" s="148"/>
-    </row>
-    <row r="9" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A9" s="154"/>
-      <c r="B9" s="148"/>
-      <c r="C9" s="148"/>
-      <c r="D9" s="148"/>
-      <c r="E9" s="148"/>
-      <c r="F9" s="148"/>
-      <c r="G9" s="148"/>
-      <c r="H9" s="148"/>
-    </row>
-    <row r="10" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A10" s="154"/>
-      <c r="B10" s="148"/>
-      <c r="C10" s="148"/>
-      <c r="D10" s="148"/>
-      <c r="E10" s="148"/>
-      <c r="F10" s="148"/>
-      <c r="G10" s="148"/>
-      <c r="H10" s="148"/>
-    </row>
-    <row r="11" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A11" s="154"/>
-      <c r="B11" s="148"/>
-      <c r="C11" s="148"/>
-      <c r="D11" s="148"/>
-      <c r="E11" s="148"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="148"/>
-      <c r="H11" s="148"/>
-    </row>
-    <row r="12" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A12" s="154"/>
-      <c r="B12" s="148"/>
-      <c r="C12" s="148"/>
-      <c r="D12" s="148"/>
-      <c r="E12" s="148"/>
-      <c r="F12" s="148"/>
-      <c r="G12" s="148"/>
-      <c r="H12" s="148"/>
-    </row>
-    <row r="13" s="142" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
-      <c r="A13" s="155" t="s">
+      <c r="A6" s="148"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
+    </row>
+    <row r="7" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A7" s="150"/>
+      <c r="B7" s="144"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+    </row>
+    <row r="8" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A8" s="150"/>
+      <c r="B8" s="144"/>
+      <c r="C8" s="144"/>
+      <c r="D8" s="144"/>
+      <c r="E8" s="144"/>
+      <c r="F8" s="144"/>
+      <c r="G8" s="144"/>
+      <c r="H8" s="144"/>
+    </row>
+    <row r="9" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A9" s="150"/>
+      <c r="B9" s="144"/>
+      <c r="C9" s="144"/>
+      <c r="D9" s="144"/>
+      <c r="E9" s="144"/>
+      <c r="F9" s="144"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="144"/>
+    </row>
+    <row r="10" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A10" s="150"/>
+      <c r="B10" s="144"/>
+      <c r="C10" s="144"/>
+      <c r="D10" s="144"/>
+      <c r="E10" s="144"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="144"/>
+    </row>
+    <row r="11" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A11" s="150"/>
+      <c r="B11" s="144"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="144"/>
+      <c r="E11" s="144"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="144"/>
+    </row>
+    <row r="12" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A12" s="150"/>
+      <c r="B12" s="144"/>
+      <c r="C12" s="144"/>
+      <c r="D12" s="144"/>
+      <c r="E12" s="144"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="144"/>
+      <c r="H12" s="144"/>
+    </row>
+    <row r="13" s="138" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
+      <c r="A13" s="151" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A14" s="154"/>
-      <c r="B14" s="156"/>
-      <c r="C14" s="148"/>
-      <c r="D14" s="148"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="148"/>
-      <c r="G14" s="148"/>
-      <c r="H14" s="148"/>
-    </row>
-    <row r="15" s="142" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
-      <c r="A15" s="157" t="s">
+    <row r="14" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A14" s="150"/>
+      <c r="B14" s="152"/>
+      <c r="C14" s="144"/>
+      <c r="D14" s="144"/>
+      <c r="E14" s="144"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="144"/>
+      <c r="H14" s="144"/>
+    </row>
+    <row r="15" s="138" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
+      <c r="A15" s="153" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A16" s="154"/>
-      <c r="B16" s="148"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="148"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="148"/>
-      <c r="G16" s="148"/>
-      <c r="H16" s="148"/>
-    </row>
-    <row r="17" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A17" s="154"/>
-      <c r="B17" s="148"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="148"/>
-      <c r="E17" s="148"/>
-      <c r="F17" s="148"/>
-      <c r="G17" s="148"/>
-      <c r="H17" s="148"/>
-    </row>
-    <row r="18" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A18" s="154"/>
-      <c r="B18" s="148"/>
-      <c r="C18" s="148"/>
-      <c r="D18" s="148"/>
-      <c r="E18" s="148"/>
-      <c r="F18" s="148"/>
-      <c r="G18" s="148"/>
-      <c r="H18" s="148"/>
-    </row>
-    <row r="19" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A19" s="154"/>
-      <c r="B19" s="148"/>
-      <c r="C19" s="148"/>
-      <c r="D19" s="148"/>
-      <c r="E19" s="148"/>
-      <c r="F19" s="148"/>
-      <c r="G19" s="148"/>
-      <c r="H19" s="148"/>
-    </row>
-    <row r="20" s="142" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A20" s="158" t="s">
+    <row r="16" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A16" s="150"/>
+      <c r="B16" s="144"/>
+      <c r="C16" s="144"/>
+      <c r="D16" s="144"/>
+      <c r="E16" s="144"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="144"/>
+      <c r="H16" s="144"/>
+    </row>
+    <row r="17" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A17" s="150"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="144"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="144"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="144"/>
+    </row>
+    <row r="18" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A18" s="150"/>
+      <c r="B18" s="144"/>
+      <c r="C18" s="144"/>
+      <c r="D18" s="144"/>
+      <c r="E18" s="144"/>
+      <c r="F18" s="144"/>
+      <c r="G18" s="144"/>
+      <c r="H18" s="144"/>
+    </row>
+    <row r="19" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A19" s="150"/>
+      <c r="B19" s="144"/>
+      <c r="C19" s="144"/>
+      <c r="D19" s="144"/>
+      <c r="E19" s="144"/>
+      <c r="F19" s="144"/>
+      <c r="G19" s="144"/>
+      <c r="H19" s="144"/>
+    </row>
+    <row r="20" s="138" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
+      <c r="A20" s="154" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A21" s="154"/>
-      <c r="B21" s="148"/>
-      <c r="C21" s="148"/>
-      <c r="D21" s="148"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="148"/>
-      <c r="G21" s="148"/>
-      <c r="H21" s="148"/>
-    </row>
-    <row r="22" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A22" s="154"/>
-      <c r="B22" s="148"/>
-      <c r="C22" s="148"/>
-      <c r="D22" s="148"/>
-      <c r="E22" s="148"/>
-      <c r="F22" s="148"/>
-      <c r="G22" s="148"/>
-      <c r="H22" s="148"/>
-    </row>
-    <row r="23" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A23" s="154"/>
-      <c r="B23" s="148"/>
-      <c r="C23" s="148"/>
-      <c r="D23" s="148"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="148"/>
-      <c r="G23" s="148"/>
-      <c r="H23" s="148"/>
-    </row>
-    <row r="24" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A24" s="154"/>
-      <c r="B24" s="148"/>
-      <c r="C24" s="148"/>
-      <c r="D24" s="148"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
-      <c r="G24" s="148"/>
-      <c r="H24" s="148"/>
-    </row>
-    <row r="25" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A25" s="154"/>
-      <c r="B25" s="148"/>
-      <c r="C25" s="148"/>
-      <c r="D25" s="148"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="148"/>
-      <c r="G25" s="148"/>
-      <c r="H25" s="148"/>
-    </row>
-    <row r="26" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A26" s="154"/>
-      <c r="B26" s="148"/>
-      <c r="C26" s="148"/>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="148"/>
-      <c r="H26" s="148"/>
-    </row>
-    <row r="27" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A27" s="154"/>
-      <c r="B27" s="148"/>
-      <c r="C27" s="148"/>
-      <c r="D27" s="148"/>
-      <c r="E27" s="148"/>
-      <c r="F27" s="148"/>
-      <c r="G27" s="148"/>
-      <c r="H27" s="148"/>
-    </row>
-    <row r="28" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A28" s="154"/>
-      <c r="B28" s="148"/>
-      <c r="C28" s="148"/>
-      <c r="D28" s="148"/>
-      <c r="E28" s="148"/>
-      <c r="F28" s="148"/>
-      <c r="G28" s="148"/>
-      <c r="H28" s="148"/>
-    </row>
-    <row r="29" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A29" s="154"/>
-      <c r="B29" s="148"/>
-      <c r="C29" s="148"/>
-      <c r="D29" s="148"/>
-      <c r="E29" s="148"/>
-      <c r="F29" s="148"/>
-      <c r="G29" s="148"/>
-      <c r="H29" s="148"/>
-    </row>
-    <row r="30" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A30" s="154"/>
-      <c r="B30" s="148"/>
-      <c r="C30" s="148"/>
-      <c r="D30" s="148"/>
-      <c r="E30" s="148"/>
-      <c r="F30" s="148"/>
-      <c r="G30" s="148"/>
-      <c r="H30" s="148"/>
-    </row>
-    <row r="31" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A31" s="154"/>
-      <c r="B31" s="148"/>
-      <c r="C31" s="148"/>
-      <c r="D31" s="148"/>
-      <c r="E31" s="148"/>
-      <c r="F31" s="148"/>
-      <c r="G31" s="148"/>
-      <c r="H31" s="148"/>
-    </row>
-    <row r="32" s="142" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A32" s="159"/>
-    </row>
-    <row r="33" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A33" s="154"/>
-      <c r="B33" s="148"/>
-      <c r="C33" s="148"/>
-      <c r="D33" s="148"/>
-      <c r="E33" s="148"/>
-      <c r="F33" s="148"/>
-      <c r="G33" s="148"/>
-      <c r="H33" s="148"/>
-    </row>
-    <row r="34" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A34" s="154"/>
-      <c r="B34" s="148"/>
-      <c r="C34" s="148"/>
-      <c r="D34" s="148"/>
-      <c r="E34" s="148"/>
-      <c r="F34" s="148"/>
-      <c r="G34" s="148"/>
-      <c r="H34" s="148"/>
-    </row>
-    <row r="35" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A35" s="154"/>
-      <c r="B35" s="148"/>
-      <c r="C35" s="148"/>
-      <c r="D35" s="148"/>
-      <c r="E35" s="148"/>
-      <c r="F35" s="148"/>
-      <c r="G35" s="148"/>
-      <c r="H35" s="148"/>
-    </row>
-    <row r="36" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A36" s="160" t="s">
+    <row r="21" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A21" s="150"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="144"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+    </row>
+    <row r="22" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A22" s="150"/>
+      <c r="B22" s="144"/>
+      <c r="C22" s="144"/>
+      <c r="D22" s="144"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="144"/>
+      <c r="G22" s="144"/>
+      <c r="H22" s="144"/>
+    </row>
+    <row r="23" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A23" s="150"/>
+      <c r="B23" s="144"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="144"/>
+      <c r="G23" s="144"/>
+      <c r="H23" s="144"/>
+    </row>
+    <row r="24" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A24" s="150"/>
+      <c r="B24" s="144"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="144"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="144"/>
+      <c r="G24" s="144"/>
+      <c r="H24" s="144"/>
+    </row>
+    <row r="25" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A25" s="150"/>
+      <c r="B25" s="144"/>
+      <c r="C25" s="144"/>
+      <c r="D25" s="144"/>
+      <c r="E25" s="144"/>
+      <c r="F25" s="144"/>
+      <c r="G25" s="144"/>
+      <c r="H25" s="144"/>
+    </row>
+    <row r="26" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A26" s="150"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="144"/>
+      <c r="D26" s="144"/>
+      <c r="E26" s="144"/>
+      <c r="F26" s="144"/>
+      <c r="G26" s="144"/>
+      <c r="H26" s="144"/>
+    </row>
+    <row r="27" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A27" s="150"/>
+      <c r="B27" s="144"/>
+      <c r="C27" s="144"/>
+      <c r="D27" s="144"/>
+      <c r="E27" s="144"/>
+      <c r="F27" s="144"/>
+      <c r="G27" s="144"/>
+      <c r="H27" s="144"/>
+    </row>
+    <row r="28" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A28" s="150"/>
+      <c r="B28" s="144"/>
+      <c r="C28" s="144"/>
+      <c r="D28" s="144"/>
+      <c r="E28" s="144"/>
+      <c r="F28" s="144"/>
+      <c r="G28" s="144"/>
+      <c r="H28" s="144"/>
+    </row>
+    <row r="29" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A29" s="150"/>
+      <c r="B29" s="144"/>
+      <c r="C29" s="144"/>
+      <c r="D29" s="144"/>
+      <c r="E29" s="144"/>
+      <c r="F29" s="144"/>
+      <c r="G29" s="144"/>
+      <c r="H29" s="144"/>
+    </row>
+    <row r="30" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A30" s="150"/>
+      <c r="B30" s="144"/>
+      <c r="C30" s="144"/>
+      <c r="D30" s="144"/>
+      <c r="E30" s="144"/>
+      <c r="F30" s="144"/>
+      <c r="G30" s="144"/>
+      <c r="H30" s="144"/>
+    </row>
+    <row r="31" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A31" s="150"/>
+      <c r="B31" s="144"/>
+      <c r="C31" s="144"/>
+      <c r="D31" s="144"/>
+      <c r="E31" s="144"/>
+      <c r="F31" s="144"/>
+      <c r="G31" s="144"/>
+      <c r="H31" s="144"/>
+    </row>
+    <row r="32" s="138" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
+      <c r="A32" s="155"/>
+    </row>
+    <row r="33" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A33" s="150"/>
+      <c r="B33" s="144"/>
+      <c r="C33" s="144"/>
+      <c r="D33" s="144"/>
+      <c r="E33" s="144"/>
+      <c r="F33" s="144"/>
+      <c r="G33" s="144"/>
+      <c r="H33" s="144"/>
+    </row>
+    <row r="34" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A34" s="150"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="144"/>
+      <c r="D34" s="144"/>
+      <c r="E34" s="144"/>
+      <c r="F34" s="144"/>
+      <c r="G34" s="144"/>
+      <c r="H34" s="144"/>
+    </row>
+    <row r="35" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A35" s="150"/>
+      <c r="B35" s="144"/>
+      <c r="C35" s="144"/>
+      <c r="D35" s="144"/>
+      <c r="E35" s="144"/>
+      <c r="F35" s="144"/>
+      <c r="G35" s="144"/>
+      <c r="H35" s="144"/>
+    </row>
+    <row r="36" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A36" s="156" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="161"/>
-      <c r="C36" s="160" t="s">
+      <c r="B36" s="157"/>
+      <c r="C36" s="156" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="161"/>
-      <c r="E36" s="160" t="s">
+      <c r="D36" s="157"/>
+      <c r="E36" s="156" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="162"/>
-      <c r="G36" s="160" t="s">
+      <c r="F36" s="158"/>
+      <c r="G36" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="163"/>
-    </row>
-    <row r="37" s="142" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A37" s="164" t="s">
+      <c r="H36" s="159"/>
+    </row>
+    <row r="37" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A37" s="160" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="165"/>
-      <c r="C37" s="166"/>
-      <c r="D37" s="167"/>
-      <c r="E37" s="164" t="s">
+      <c r="B37" s="161"/>
+      <c r="C37" s="162"/>
+      <c r="D37" s="163"/>
+      <c r="E37" s="160" t="s">
         <v>13</v>
       </c>
-      <c r="F37" s="168"/>
-      <c r="G37" s="166"/>
-      <c r="H37" s="167"/>
+      <c r="F37" s="164"/>
+      <c r="G37" s="162"/>
+      <c r="H37" s="163"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="144"/>
+      <c r="A38" s="140"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4257,550 +4219,578 @@
   <dimension ref="B1:P30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="0.876106194690266" style="80" customWidth="1"/>
-    <col min="2" max="2" width="3.3716814159292" style="80" customWidth="1"/>
-    <col min="3" max="3" width="10.7522123893805" style="81" customWidth="1"/>
-    <col min="4" max="4" width="23.3716814159292" style="80" customWidth="1"/>
-    <col min="5" max="5" width="7.3716814159292" style="80" customWidth="1"/>
-    <col min="6" max="6" width="12.7522123893805" style="80" customWidth="1"/>
-    <col min="7" max="7" width="9.3716814159292" style="80" customWidth="1"/>
-    <col min="8" max="8" width="6.87610619469027" style="80" customWidth="1"/>
-    <col min="9" max="10" width="6.87610619469027" style="79" customWidth="1"/>
-    <col min="11" max="13" width="6.87610619469027" style="80" customWidth="1"/>
-    <col min="14" max="14" width="36.1150442477876" style="80" customWidth="1"/>
-    <col min="15" max="15" width="27.4159292035398" style="80" customWidth="1"/>
-    <col min="16" max="16" width="12" style="80" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="80" customWidth="1"/>
+    <col min="1" max="1" width="0.876106194690266" style="79" customWidth="1"/>
+    <col min="2" max="2" width="3.3716814159292" style="79" customWidth="1"/>
+    <col min="3" max="3" width="10.7522123893805" style="80" customWidth="1"/>
+    <col min="4" max="4" width="23.3716814159292" style="79" customWidth="1"/>
+    <col min="5" max="5" width="7.3716814159292" style="79" customWidth="1"/>
+    <col min="6" max="6" width="12.7522123893805" style="79" customWidth="1"/>
+    <col min="7" max="7" width="9.3716814159292" style="79" customWidth="1"/>
+    <col min="8" max="8" width="6.87610619469027" style="79" customWidth="1"/>
+    <col min="9" max="10" width="6.87610619469027" style="78" customWidth="1"/>
+    <col min="11" max="13" width="6.87610619469027" style="79" customWidth="1"/>
+    <col min="14" max="14" width="36.1150442477876" style="79" customWidth="1"/>
+    <col min="15" max="15" width="27.4159292035398" style="79" customWidth="1"/>
+    <col min="16" max="16" width="12" style="79" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="79" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="74" customFormat="1" ht="29.25" customHeight="1" spans="2:16">
-      <c r="B1" s="82" t="s">
+    <row r="1" s="73" customFormat="1" ht="29.25" customHeight="1" spans="2:16">
+      <c r="B1" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-    </row>
-    <row r="2" s="75" customFormat="1" ht="24.75" customHeight="1" spans="2:16">
-      <c r="B2" s="85" t="s">
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+    </row>
+    <row r="2" s="74" customFormat="1" ht="24.75" customHeight="1" spans="2:16">
+      <c r="B2" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="86" t="s">
+      <c r="E2" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="86" t="s">
+      <c r="F2" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="86" t="s">
+      <c r="G2" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="86" t="s">
+      <c r="H2" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="86" t="s">
+      <c r="I2" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="86" t="s">
+      <c r="J2" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="86" t="s">
+      <c r="K2" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="86" t="s">
+      <c r="L2" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="86" t="s">
+      <c r="M2" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="87" t="s">
+      <c r="N2" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="87" t="s">
+      <c r="O2" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="88" t="s">
+      <c r="P2" s="87" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" s="76" customFormat="1" customHeight="1" spans="2:16">
-      <c r="B3" s="89">
+    <row r="3" s="75" customFormat="1" ht="14.25" spans="2:16">
+      <c r="B3" s="88">
         <v>1</v>
       </c>
-      <c r="C3" s="90" t="s">
+      <c r="C3" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="91" t="s">
+      <c r="D3" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="92" t="s">
+      <c r="E3" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="93" t="s">
+      <c r="F3" s="92" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="94" t="s">
+      <c r="G3" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="93">
+      <c r="H3" s="92">
         <v>0</v>
       </c>
-      <c r="I3" s="93">
+      <c r="I3" s="92">
         <v>17</v>
       </c>
-      <c r="J3" s="93">
+      <c r="J3" s="92">
         <v>0</v>
       </c>
-      <c r="K3" s="93">
+      <c r="K3" s="92">
         <v>0</v>
       </c>
-      <c r="L3" s="95">
+      <c r="L3" s="94">
         <v>17</v>
       </c>
-      <c r="M3" s="96" t="s">
+      <c r="M3" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="97" t="s">
+      <c r="N3" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="97" t="s">
+      <c r="O3" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="98">
+      <c r="P3" s="97">
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B4" s="99">
+    <row r="4" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B4" s="98">
         <v>2</v>
       </c>
-      <c r="C4" s="100">
+      <c r="C4" s="99">
         <v>46272</v>
       </c>
-      <c r="D4" s="101" t="s">
+      <c r="D4" s="100" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="101" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="103" t="s">
+      <c r="F4" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="104" t="s">
+      <c r="G4" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="105">
+      <c r="H4" s="104">
         <v>17</v>
       </c>
-      <c r="I4" s="106">
+      <c r="I4" s="105">
         <v>22</v>
       </c>
-      <c r="J4" s="106">
+      <c r="J4" s="105">
         <v>0</v>
       </c>
-      <c r="K4" s="106">
+      <c r="K4" s="105">
         <v>0</v>
       </c>
-      <c r="L4" s="107">
+      <c r="L4" s="94">
         <v>22</v>
       </c>
-      <c r="M4" s="108">
+      <c r="M4" s="106">
         <v>0.2941</v>
       </c>
-      <c r="N4" s="97" t="s">
+      <c r="N4" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="97" t="s">
+      <c r="O4" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="P4" s="109">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="5" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B5" s="99">
+      <c r="P4" s="107">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B5" s="98">
         <v>3</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="106"/>
-      <c r="K5" s="106"/>
-      <c r="L5" s="107"/>
-      <c r="M5" s="108"/>
-      <c r="N5" s="104"/>
-      <c r="O5" s="104"/>
-      <c r="P5" s="111"/>
-    </row>
-    <row r="6" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B6" s="99">
+      <c r="C5" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="100" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="109" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="103" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="104">
+        <v>22</v>
+      </c>
+      <c r="I5" s="105">
+        <v>0</v>
+      </c>
+      <c r="J5" s="105">
+        <v>0</v>
+      </c>
+      <c r="K5" s="105">
+        <v>1</v>
+      </c>
+      <c r="L5" s="94">
+        <v>22</v>
+      </c>
+      <c r="M5" s="106">
+        <v>0.045</v>
+      </c>
+      <c r="N5" s="103" t="s">
+        <v>47</v>
+      </c>
+      <c r="O5" s="103" t="s">
+        <v>48</v>
+      </c>
+      <c r="P5" s="107">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B6" s="98">
         <v>4</v>
       </c>
-      <c r="C6" s="110"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="107"/>
-      <c r="M6" s="108"/>
-      <c r="N6" s="104"/>
-      <c r="O6" s="104"/>
-      <c r="P6" s="111"/>
-    </row>
-    <row r="7" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B7" s="99">
+      <c r="C6" s="108"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="106"/>
+      <c r="N6" s="103"/>
+      <c r="O6" s="103"/>
+      <c r="P6" s="110"/>
+    </row>
+    <row r="7" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B7" s="98">
         <v>5</v>
       </c>
-      <c r="C7" s="110"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="108"/>
-      <c r="N7" s="112"/>
-      <c r="O7" s="104"/>
-      <c r="P7" s="111"/>
-    </row>
-    <row r="8" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B8" s="99">
+      <c r="C7" s="108"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="105"/>
+      <c r="K7" s="105"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="111"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="110"/>
+    </row>
+    <row r="8" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B8" s="98">
         <v>6</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="106"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="106"/>
-      <c r="J8" s="106"/>
-      <c r="K8" s="106"/>
-      <c r="L8" s="107"/>
-      <c r="M8" s="108"/>
-      <c r="N8" s="112"/>
-      <c r="O8" s="112"/>
-      <c r="P8" s="111"/>
-    </row>
-    <row r="9" s="77" customFormat="1" ht="12" customHeight="1" spans="2:16">
-      <c r="B9" s="113">
+      <c r="C8" s="108"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="94"/>
+      <c r="M8" s="106"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="111"/>
+      <c r="P8" s="110"/>
+    </row>
+    <row r="9" s="76" customFormat="1" ht="12" customHeight="1" spans="2:16">
+      <c r="B9" s="112">
         <v>7</v>
       </c>
-      <c r="C9" s="114"/>
-      <c r="D9" s="115"/>
-      <c r="E9" s="116"/>
-      <c r="F9" s="117"/>
-      <c r="G9" s="118"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="117"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="107"/>
-      <c r="M9" s="108"/>
-      <c r="N9" s="120"/>
-      <c r="O9" s="120"/>
-      <c r="P9" s="121"/>
-    </row>
-    <row r="10" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B10" s="99">
+      <c r="C9" s="113"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="114"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="115"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="106"/>
+      <c r="N9" s="116"/>
+      <c r="O9" s="116"/>
+      <c r="P9" s="117"/>
+    </row>
+    <row r="10" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B10" s="98">
         <v>8</v>
       </c>
-      <c r="C10" s="122"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="102"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="107"/>
-      <c r="M10" s="108"/>
-      <c r="N10" s="120"/>
-      <c r="O10" s="112"/>
-      <c r="P10" s="121"/>
-    </row>
-    <row r="11" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B11" s="99">
+      <c r="C10" s="118"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="94"/>
+      <c r="M10" s="106"/>
+      <c r="N10" s="116"/>
+      <c r="O10" s="111"/>
+      <c r="P10" s="117"/>
+    </row>
+    <row r="11" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B11" s="98">
         <v>9</v>
       </c>
-      <c r="C11" s="122"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="107"/>
-      <c r="M11" s="108"/>
-      <c r="N11" s="120"/>
-      <c r="O11" s="112"/>
-      <c r="P11" s="121"/>
-    </row>
-    <row r="12" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B12" s="99">
+      <c r="C11" s="118"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="94"/>
+      <c r="M11" s="106"/>
+      <c r="N11" s="116"/>
+      <c r="O11" s="111"/>
+      <c r="P11" s="117"/>
+    </row>
+    <row r="12" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B12" s="98">
         <v>10</v>
       </c>
-      <c r="C12" s="122"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="106"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="107"/>
-      <c r="M12" s="108"/>
-      <c r="N12" s="120"/>
-      <c r="O12" s="112"/>
-      <c r="P12" s="121"/>
-    </row>
-    <row r="13" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B13" s="99">
+      <c r="C12" s="118"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="105"/>
+      <c r="L12" s="94"/>
+      <c r="M12" s="106"/>
+      <c r="N12" s="116"/>
+      <c r="O12" s="111"/>
+      <c r="P12" s="117"/>
+    </row>
+    <row r="13" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B13" s="98">
         <v>11</v>
       </c>
-      <c r="C13" s="123"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="128"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="126"/>
-      <c r="L13" s="129"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="131"/>
-      <c r="O13" s="132"/>
-      <c r="P13" s="133"/>
-    </row>
-    <row r="14" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B14" s="99">
+      <c r="C13" s="119"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="123"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="122"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="125"/>
+      <c r="M13" s="126"/>
+      <c r="N13" s="127"/>
+      <c r="O13" s="128"/>
+      <c r="P13" s="129"/>
+    </row>
+    <row r="14" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B14" s="98">
         <v>12</v>
       </c>
-      <c r="C14" s="123"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="125"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="128"/>
-      <c r="I14" s="126"/>
-      <c r="J14" s="126"/>
-      <c r="K14" s="126"/>
-      <c r="L14" s="129"/>
-      <c r="M14" s="130"/>
-      <c r="N14" s="132"/>
-      <c r="O14" s="132"/>
-      <c r="P14" s="133"/>
-    </row>
-    <row r="15" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B15" s="99">
+      <c r="C14" s="119"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="123"/>
+      <c r="H14" s="124"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="122"/>
+      <c r="K14" s="122"/>
+      <c r="L14" s="125"/>
+      <c r="M14" s="126"/>
+      <c r="N14" s="128"/>
+      <c r="O14" s="128"/>
+      <c r="P14" s="129"/>
+    </row>
+    <row r="15" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B15" s="98">
         <v>13</v>
       </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="102"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="107"/>
-      <c r="M15" s="108"/>
-      <c r="N15" s="134"/>
-      <c r="O15" s="134"/>
-      <c r="P15" s="135"/>
-    </row>
-    <row r="16" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B16" s="99">
+      <c r="C15" s="108"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="104"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="105"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="94"/>
+      <c r="M15" s="106"/>
+      <c r="N15" s="130"/>
+      <c r="O15" s="130"/>
+      <c r="P15" s="131"/>
+    </row>
+    <row r="16" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B16" s="98">
         <v>14</v>
       </c>
-      <c r="C16" s="110"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="102"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="105"/>
-      <c r="I16" s="106"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="107"/>
-      <c r="M16" s="108"/>
-      <c r="N16" s="134"/>
-      <c r="O16" s="134"/>
-      <c r="P16" s="135"/>
-    </row>
-    <row r="17" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B17" s="99">
+      <c r="C16" s="108"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="103"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="105"/>
+      <c r="K16" s="105"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="106"/>
+      <c r="N16" s="130"/>
+      <c r="O16" s="130"/>
+      <c r="P16" s="131"/>
+    </row>
+    <row r="17" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B17" s="98">
         <v>15</v>
       </c>
-      <c r="C17" s="110"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="102"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="107"/>
-      <c r="M17" s="108"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="136"/>
-      <c r="P17" s="135"/>
-    </row>
-    <row r="18" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B18" s="99">
+      <c r="C17" s="108"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="105"/>
+      <c r="K17" s="105"/>
+      <c r="L17" s="94"/>
+      <c r="M17" s="106"/>
+      <c r="N17" s="132"/>
+      <c r="O17" s="132"/>
+      <c r="P17" s="131"/>
+    </row>
+    <row r="18" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B18" s="98">
         <v>16</v>
       </c>
-      <c r="C18" s="110"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="106"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="106"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="106"/>
-      <c r="L18" s="107"/>
-      <c r="M18" s="108"/>
-      <c r="N18" s="136"/>
-      <c r="O18" s="136"/>
-      <c r="P18" s="135"/>
-    </row>
-    <row r="19" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B19" s="99">
+      <c r="C18" s="108"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="105"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="106"/>
+      <c r="N18" s="132"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="131"/>
+    </row>
+    <row r="19" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B19" s="98">
         <v>17</v>
       </c>
-      <c r="C19" s="110"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="102"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="107"/>
-      <c r="M19" s="108"/>
-      <c r="N19" s="136"/>
-      <c r="O19" s="136"/>
-      <c r="P19" s="135"/>
-    </row>
-    <row r="20" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B20" s="99">
+      <c r="C19" s="108"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="105"/>
+      <c r="K19" s="105"/>
+      <c r="L19" s="94"/>
+      <c r="M19" s="106"/>
+      <c r="N19" s="132"/>
+      <c r="O19" s="132"/>
+      <c r="P19" s="131"/>
+    </row>
+    <row r="20" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B20" s="98">
         <v>18</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="102"/>
-      <c r="F20" s="106"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="106"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="106"/>
-      <c r="L20" s="107"/>
-      <c r="M20" s="108"/>
-      <c r="N20" s="136"/>
-      <c r="O20" s="136"/>
-      <c r="P20" s="135"/>
-    </row>
-    <row r="21" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B21" s="99">
+      <c r="C20" s="108"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="101"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="94"/>
+      <c r="M20" s="106"/>
+      <c r="N20" s="132"/>
+      <c r="O20" s="132"/>
+      <c r="P20" s="131"/>
+    </row>
+    <row r="21" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B21" s="98">
         <v>19</v>
       </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="107"/>
-      <c r="M21" s="108"/>
-      <c r="N21" s="136"/>
-      <c r="O21" s="136"/>
-      <c r="P21" s="135"/>
-    </row>
-    <row r="22" s="76" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B22" s="99">
+      <c r="C21" s="108"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="105"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="94"/>
+      <c r="M21" s="106"/>
+      <c r="N21" s="132"/>
+      <c r="O21" s="132"/>
+      <c r="P21" s="131"/>
+    </row>
+    <row r="22" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B22" s="98">
         <v>20</v>
       </c>
-      <c r="C22" s="110"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="102"/>
-      <c r="F22" s="106"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="106"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="106"/>
-      <c r="L22" s="107"/>
-      <c r="M22" s="108"/>
-      <c r="N22" s="136"/>
-      <c r="O22" s="136"/>
-      <c r="P22" s="135"/>
-    </row>
-    <row r="23" s="78" customFormat="1" customHeight="1" spans="2:16">
-      <c r="B23" s="137" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="138"/>
-      <c r="D23" s="138"/>
-      <c r="E23" s="138"/>
-      <c r="F23" s="138"/>
-      <c r="G23" s="138"/>
-      <c r="H23" s="139"/>
-      <c r="I23" s="139"/>
-      <c r="J23" s="139"/>
-      <c r="K23" s="139"/>
-      <c r="L23" s="139"/>
-      <c r="M23" s="140"/>
-      <c r="N23" s="139"/>
-      <c r="O23" s="139"/>
-      <c r="P23" s="141"/>
-    </row>
-    <row r="24" s="79" customFormat="1"/>
-    <row r="25" s="79" customFormat="1"/>
-    <row r="26" s="79" customFormat="1"/>
-    <row r="27" s="79" customFormat="1"/>
-    <row r="28" s="79" customFormat="1"/>
-    <row r="29" s="79" customFormat="1"/>
-    <row r="30" s="79" customFormat="1"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="104"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="105"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="94"/>
+      <c r="M22" s="106"/>
+      <c r="N22" s="132"/>
+      <c r="O22" s="132"/>
+      <c r="P22" s="131"/>
+    </row>
+    <row r="23" s="77" customFormat="1" ht="13.9" spans="2:16">
+      <c r="B23" s="133" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="134"/>
+      <c r="D23" s="134"/>
+      <c r="E23" s="134"/>
+      <c r="F23" s="134"/>
+      <c r="G23" s="134"/>
+      <c r="H23" s="135"/>
+      <c r="I23" s="135"/>
+      <c r="J23" s="135"/>
+      <c r="K23" s="135"/>
+      <c r="L23" s="135"/>
+      <c r="M23" s="136"/>
+      <c r="N23" s="135"/>
+      <c r="O23" s="135"/>
+      <c r="P23" s="137"/>
+    </row>
+    <row r="24" s="78" customFormat="1"/>
+    <row r="25" s="78" customFormat="1"/>
+    <row r="26" s="78" customFormat="1"/>
+    <row r="27" s="78" customFormat="1"/>
+    <row r="28" s="78" customFormat="1"/>
+    <row r="29" s="78" customFormat="1"/>
+    <row r="30" s="78" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="99" fitToHeight="0" orientation="landscape"/>
@@ -4836,1087 +4826,1078 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:11">
       <c r="B1" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="13.9" spans="1:11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="13.9" customHeight="1" spans="1:11">
       <c r="A2" s="1"/>
-      <c r="B2" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="19"/>
+      <c r="B2" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:11">
-      <c r="K3" s="20"/>
+      <c r="K3" s="19"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:11">
       <c r="A4" s="1"/>
-      <c r="B4" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="K4" s="25" t="s">
+      <c r="B4" s="20" t="s">
         <v>55</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:11">
       <c r="A5" s="1"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="30"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="27"/>
+      <c r="G5" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="27"/>
+      <c r="K5" s="29"/>
     </row>
     <row r="6" s="4" customFormat="1" ht="33.75" customHeight="1" spans="1:11">
       <c r="A6" s="1"/>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>1</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I6" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="J6" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="K6" s="37" t="s">
+      <c r="C6" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" s="4" customFormat="1" ht="42.75" customHeight="1" spans="1:11">
       <c r="A7" s="1"/>
-      <c r="B7" s="38">
+      <c r="B7" s="37">
         <v>2</v>
       </c>
-      <c r="C7" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="41" t="s">
+      <c r="C7" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="D7" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I7" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="J7" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="K7" s="37" t="s">
+      <c r="E7" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="J7" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="K7" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:11">
       <c r="A8" s="1"/>
-      <c r="B8" s="38">
+      <c r="B8" s="37">
         <v>3</v>
       </c>
-      <c r="C8" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I8" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" s="37" t="s">
+      <c r="C8" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="K8" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" s="4" customFormat="1" ht="61.5" customHeight="1" spans="1:11">
       <c r="A9" s="1"/>
-      <c r="B9" s="38">
+      <c r="B9" s="37">
         <v>4</v>
       </c>
-      <c r="C9" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="40" t="s">
+      <c r="C9" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="H9" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J9" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" s="4" customFormat="1" ht="62" customHeight="1" spans="1:11">
       <c r="A10" s="1"/>
-      <c r="B10" s="42">
+      <c r="B10" s="41">
         <v>5</v>
       </c>
-      <c r="C10" s="43" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J10" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="K10" s="37" t="s">
+      <c r="C10" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" s="4" customFormat="1" ht="33" customHeight="1" spans="1:11">
       <c r="A11" s="1"/>
-      <c r="B11" s="31">
+      <c r="B11" s="30">
         <v>6</v>
       </c>
-      <c r="C11" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="33" t="s">
+      <c r="C11" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="I11" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J11" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="K11" s="37" t="s">
+      <c r="J11" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" s="4" customFormat="1" ht="41" customHeight="1" spans="1:11">
       <c r="A12" s="1"/>
-      <c r="B12" s="38">
+      <c r="B12" s="37">
         <v>7</v>
       </c>
-      <c r="C12" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="F12" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="35" t="s">
+      <c r="C12" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="I12" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J12" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="K12" s="37" t="s">
+      <c r="D12" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J12" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="K12" s="36" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:11">
+    <row r="13" s="4" customFormat="1" ht="74" customHeight="1" spans="1:11">
       <c r="A13" s="1"/>
-      <c r="B13" s="38">
+      <c r="B13" s="37">
         <v>8</v>
       </c>
-      <c r="C13" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="35" t="s">
+      <c r="C13" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="I13" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J13" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="K13" s="37" t="s">
+      <c r="D13" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="J13" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="K13" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" s="4" customFormat="1" ht="39.75" customHeight="1" spans="1:11">
       <c r="A14" s="1"/>
-      <c r="B14" s="38">
+      <c r="B14" s="37">
         <v>9</v>
       </c>
-      <c r="C14" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="F14" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="35" t="s">
+      <c r="C14" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="I14" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J14" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="K14" s="37" t="s">
+      <c r="D14" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J14" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="K14" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" s="4" customFormat="1" ht="42" customHeight="1" spans="1:11">
       <c r="A15" s="1"/>
-      <c r="B15" s="38">
+      <c r="B15" s="37">
         <v>10</v>
       </c>
-      <c r="C15" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="F15" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I15" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="J15" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="K15" s="37" t="s">
+      <c r="C15" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="J15" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" s="4" customFormat="1" ht="40.5" customHeight="1" spans="1:11">
       <c r="A16" s="1"/>
-      <c r="B16" s="38">
+      <c r="B16" s="37">
         <v>11</v>
       </c>
-      <c r="C16" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" s="41" t="s">
+      <c r="C16" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I16" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J16" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="K16" s="37" t="s">
+      <c r="E16" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J16" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="K16" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="41.25" customHeight="1" spans="1:11">
       <c r="A17" s="1"/>
-      <c r="B17" s="46">
+      <c r="B17" s="45">
         <v>12</v>
       </c>
-      <c r="C17" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="G17" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" s="36" t="s">
+      <c r="C17" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="J17" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="K17" s="37" t="s">
+      <c r="K17" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:11">
       <c r="A18" s="1"/>
-      <c r="B18" s="31">
+      <c r="B18" s="30">
         <v>13</v>
       </c>
-      <c r="C18" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="F18" s="33" t="s">
+      <c r="C18" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="G18" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I18" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="J18" s="36" t="s">
+      <c r="D18" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="J18" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="K18" s="37" t="s">
+      <c r="K18" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="53" customHeight="1" spans="1:11">
       <c r="A19" s="1"/>
-      <c r="B19" s="50">
+      <c r="B19" s="49">
         <v>14</v>
       </c>
-      <c r="C19" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" s="52" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="F19" s="52" t="s">
-        <v>107</v>
-      </c>
-      <c r="G19" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I19" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J19" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="K19" s="37" t="s">
+      <c r="C19" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="K19" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="1" ht="36.75" customHeight="1" spans="1:11">
       <c r="A20" s="1"/>
-      <c r="B20" s="38">
+      <c r="B20" s="37">
         <v>15</v>
       </c>
-      <c r="C20" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="E20" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="52" t="s">
-        <v>110</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J20" s="36" t="s">
+      <c r="C20" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J20" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="K20" s="37" t="s">
+      <c r="K20" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" ht="26.25" customHeight="1" spans="1:11">
       <c r="A21" s="1"/>
-      <c r="B21" s="42">
+      <c r="B21" s="41">
         <v>16</v>
       </c>
-      <c r="C21" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="G21" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I21" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J21" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="K21" s="37" t="s">
+      <c r="C21" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="K21" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="1" ht="41.25" customHeight="1" spans="1:11">
       <c r="A22" s="1"/>
-      <c r="B22" s="38">
+      <c r="B22" s="37">
         <v>17</v>
       </c>
-      <c r="C22" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="F22" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="G22" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H22" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I22" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J22" s="36" t="s">
+      <c r="C22" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J22" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="K22" s="37" t="s">
+      <c r="K22" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="23" s="4" customFormat="1" ht="26.25" customHeight="1" spans="1:11">
       <c r="A23" s="1"/>
-      <c r="B23" s="50">
+      <c r="B23" s="49">
         <v>18</v>
       </c>
-      <c r="C23" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="41" t="s">
+      <c r="C23" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="F23" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="G23" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H23" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I23" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J23" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="K23" s="37" t="s">
+      <c r="E23" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J23" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="K23" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="1" ht="41.25" customHeight="1" spans="1:11">
       <c r="A24" s="1"/>
-      <c r="B24" s="38">
+      <c r="B24" s="37">
         <v>19</v>
       </c>
-      <c r="C24" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="E24" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="F24" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="G24" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H24" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="I24" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J24" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="K24" s="37" t="s">
+      <c r="C24" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I24" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J24" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="K24" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="25" s="4" customFormat="1" ht="51" customHeight="1" spans="1:11">
       <c r="A25" s="1"/>
-      <c r="B25" s="42">
+      <c r="B25" s="41">
         <v>20</v>
       </c>
-      <c r="C25" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="E25" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="F25" s="52" t="s">
-        <v>125</v>
-      </c>
-      <c r="G25" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H25" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I25" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="J25" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="K25" s="37" t="s">
+      <c r="C25" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I25" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="J25" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="K25" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="26" s="4" customFormat="1" ht="49.5" customHeight="1" spans="1:11">
       <c r="A26" s="1"/>
-      <c r="B26" s="46">
+      <c r="B26" s="45">
         <v>21</v>
       </c>
-      <c r="C26" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="D26" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="E26" s="45" t="s">
+      <c r="C26" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="F26" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="G26" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H26" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="I26" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J26" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="K26" s="37" t="s">
+      <c r="D26" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F26" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I26" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J26" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="K26" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="27" s="5" customFormat="1" ht="40.5" customHeight="1" spans="1:11">
-      <c r="A27" s="55"/>
-      <c r="B27" s="31">
+      <c r="A27" s="54"/>
+      <c r="B27" s="30">
         <v>22</v>
       </c>
-      <c r="C27" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F27" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="G27" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H27" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="I27" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="J27" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="K27" s="37" t="s">
+      <c r="C27" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I27" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="J27" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="K27" s="36" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="28" s="6" customFormat="1" ht="40.5" customHeight="1" spans="1:11">
-      <c r="A28" s="56"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="37"/>
+      <c r="A28" s="55"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="36"/>
     </row>
     <row r="29" s="4" customFormat="1" ht="52.5" customHeight="1" spans="1:11">
       <c r="A29" s="1"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="37"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="36"/>
     </row>
     <row r="30" s="4" customFormat="1" ht="52.5" customHeight="1" spans="1:11">
       <c r="A30" s="1"/>
-      <c r="B30" s="59"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="37"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="36"/>
     </row>
     <row r="31" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:11">
       <c r="A31" s="1"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="36"/>
-      <c r="K31" s="37"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="36"/>
     </row>
     <row r="32" s="4" customFormat="1" ht="48.75" customHeight="1" spans="1:11">
       <c r="A32" s="1"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="37"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="36"/>
     </row>
     <row r="33" s="4" customFormat="1" ht="30" customHeight="1" spans="1:11">
       <c r="A33" s="1"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="60"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="37"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="59"/>
+      <c r="I33" s="59"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="36"/>
     </row>
     <row r="34" s="4" customFormat="1" ht="48.75" customHeight="1" spans="1:11">
       <c r="A34" s="1"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="60"/>
-      <c r="H34" s="60"/>
-      <c r="I34" s="60"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="37"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="59"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="36"/>
     </row>
     <row r="35" s="4" customFormat="1" ht="37.5" customHeight="1" spans="1:11">
       <c r="A35" s="1"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="60"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="37"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="36"/>
     </row>
     <row r="36" s="4" customFormat="1" ht="50.25" customHeight="1" spans="1:11">
       <c r="A36" s="1"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="60"/>
-      <c r="H36" s="60"/>
-      <c r="I36" s="60"/>
-      <c r="J36" s="36"/>
-      <c r="K36" s="37"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="36"/>
     </row>
     <row r="37" s="4" customFormat="1" ht="30" customHeight="1" spans="1:11">
       <c r="A37" s="1"/>
-      <c r="B37" s="50"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="60"/>
-      <c r="J37" s="36"/>
-      <c r="K37" s="37"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="36"/>
     </row>
     <row r="38" s="6" customFormat="1" ht="30" customHeight="1" spans="1:11">
-      <c r="A38" s="56"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="60"/>
-      <c r="H38" s="60"/>
-      <c r="I38" s="60"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="37"/>
+      <c r="A38" s="55"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="36"/>
     </row>
     <row r="39" s="7" customFormat="1" ht="39" customHeight="1" spans="1:11">
-      <c r="A39" s="61"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="60"/>
-      <c r="H39" s="60"/>
-      <c r="I39" s="60"/>
-      <c r="J39" s="36"/>
-      <c r="K39" s="37"/>
+      <c r="A39" s="60"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="36"/>
     </row>
     <row r="40" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:11">
       <c r="A40" s="1"/>
-      <c r="B40" s="50"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="53"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="37"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="36"/>
     </row>
     <row r="41" s="4" customFormat="1" ht="36.75" customHeight="1" spans="1:11">
       <c r="A41" s="1"/>
-      <c r="B41" s="50"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="60"/>
-      <c r="H41" s="60"/>
-      <c r="I41" s="60"/>
-      <c r="J41" s="36"/>
-      <c r="K41" s="37"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="36"/>
     </row>
     <row r="42" s="4" customFormat="1" ht="27.75" customHeight="1" spans="1:11">
       <c r="A42" s="1"/>
-      <c r="B42" s="50"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="60"/>
-      <c r="I42" s="60"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="37"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="59"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="36"/>
     </row>
     <row r="43" s="4" customFormat="1" ht="42" customHeight="1" spans="1:11">
       <c r="A43" s="1"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="39"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="60"/>
-      <c r="H43" s="60"/>
-      <c r="I43" s="60"/>
-      <c r="J43" s="36"/>
-      <c r="K43" s="37"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="38"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="59"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="36"/>
     </row>
     <row r="44" s="4" customFormat="1" ht="29.25" customHeight="1" spans="1:11">
       <c r="A44" s="1"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="40"/>
-      <c r="E44" s="62"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="60"/>
-      <c r="H44" s="60"/>
-      <c r="I44" s="60"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="37"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="61"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="36"/>
     </row>
     <row r="45" s="4" customFormat="1" ht="52.5" customHeight="1" spans="1:11">
       <c r="A45" s="1"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="63"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="62"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="60"/>
-      <c r="H45" s="60"/>
-      <c r="I45" s="60"/>
-      <c r="J45" s="36"/>
-      <c r="K45" s="37"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="62"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="61"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="59"/>
+      <c r="J45" s="35"/>
+      <c r="K45" s="36"/>
     </row>
     <row r="46" s="4" customFormat="1" ht="29.25" customHeight="1" spans="1:11">
       <c r="A46" s="1"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="64"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="66"/>
-      <c r="H46" s="66"/>
-      <c r="I46" s="66"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="37"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="63"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="65"/>
+      <c r="H46" s="65"/>
+      <c r="I46" s="65"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="36"/>
     </row>
     <row r="47" s="8" customFormat="1" ht="39" customHeight="1" spans="1:11">
-      <c r="A47" s="67"/>
-      <c r="B47" s="46"/>
-      <c r="C47" s="68"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="71"/>
-      <c r="H47" s="71"/>
-      <c r="I47" s="71"/>
-      <c r="J47" s="36"/>
-      <c r="K47" s="37"/>
+      <c r="A47" s="66"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="67"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="35"/>
+      <c r="K47" s="36"/>
     </row>
     <row r="49" spans="2:7">
-      <c r="B49" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="C49" s="73"/>
-      <c r="D49" s="73"/>
-      <c r="E49" s="73"/>
-      <c r="F49" s="73"/>
-      <c r="G49" s="73"/>
+      <c r="B49" s="71" t="s">
+        <v>137</v>
+      </c>
+      <c r="C49" s="72"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="72"/>
+      <c r="G49" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
+++ b/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="163">
   <si>
     <t>密级：</t>
   </si>
@@ -485,6 +485,24 @@
     <t>动作表情联调与单元测试</t>
   </si>
   <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>根据项目当前实现整体更新需求跟踪矩阵</t>
+  </si>
+  <si>
+    <t>1-3, 23-30</t>
+  </si>
+  <si>
+    <t>v1.3</t>
+  </si>
+  <si>
+    <t>需求规模由22个增至30个，新增8个功能点</t>
+  </si>
+  <si>
+    <t>新增8个需求对应的开发工作量</t>
+  </si>
+  <si>
     <t>SUM</t>
   </si>
   <si>
@@ -551,7 +569,7 @@
     <t>品牌标识</t>
   </si>
   <si>
-    <t>静态显示圆形"安"字品牌标记（青绿色背景），作为系统Logo</t>
+    <t>静态显示"安心 ANXIN"文字品牌标记，作为系统Logo</t>
   </si>
   <si>
     <t>○</t>
@@ -563,13 +581,13 @@
     <t>系统标题</t>
   </si>
   <si>
-    <t>静态显示系统名称"安心健康助手"，作为主标题</t>
+    <t>静态显示系统名称"安心健康助手"，作为主标题（页面标签与后端服务标题）</t>
   </si>
   <si>
     <t>系统副标题</t>
   </si>
   <si>
-    <t>静态显示副标题"用说话的方式，轻松办理健康服务"</t>
+    <t>静态显示品牌描述"一直在您身边"，作为副标题</t>
   </si>
   <si>
     <t>系统状态</t>
@@ -581,60 +599,57 @@
     <t>动态显示后端服务运行状态；通过健康检查接口检测，正常时显示绿色状态点</t>
   </si>
   <si>
+    <t>数字人舞台</t>
+  </si>
+  <si>
+    <t>渲染区</t>
+  </si>
+  <si>
+    <t>数字人模型渲染</t>
+  </si>
+  <si>
+    <t>使用Three.js + three-vrm加载本地.vrm模型并在舞台渲染；动作：加载后模型居中展示，支持鼠标拖动旋转、滚轮缩放</t>
+  </si>
+  <si>
+    <t>口型同步</t>
+  </si>
+  <si>
+    <t>动态表现：播报语音时按音频能量驱动嘴型张合，形成说话口型</t>
+  </si>
+  <si>
+    <t>赵燕凯</t>
+  </si>
+  <si>
+    <t>自动眨眼与头部微动</t>
+  </si>
+  <si>
+    <t>动态表现：数字人按时长随机周期自动眨眼，静默时头部缓慢微动，说话时轻微点头</t>
+  </si>
+  <si>
+    <t>赵燕凯、魏鑫鸿</t>
+  </si>
+  <si>
+    <t>肢体动作</t>
+  </si>
+  <si>
+    <t>动态表现：挥手动作右臂抬起摆动后复位；支持播放.vrma动作文件（关键词触发一次/手动循环）；动作可完整显示表情（眨眼/口型/下巴），通过表情独占名单FULL_EXPRESSION_ACTIONS配置</t>
+  </si>
+  <si>
+    <t>魏鑫鸿</t>
+  </si>
+  <si>
+    <t>状态提示</t>
+  </si>
+  <si>
+    <t>载入占位提示</t>
+  </si>
+  <si>
+    <t>未加载模型时静态显示占位图标与"数字人形象正在准备中"及说明文字，模型加载后隐藏</t>
+  </si>
+  <si>
     <t>×</t>
   </si>
   <si>
-    <t>数字人舞台</t>
-  </si>
-  <si>
-    <t>渲染区</t>
-  </si>
-  <si>
-    <t>数字人模型渲染</t>
-  </si>
-  <si>
-    <t>使用Three.js + three-vrm加载本地.vrm模型并在舞台渲染；动作：加载后模型居中展示，支持鼠标拖动旋转、滚轮缩放</t>
-  </si>
-  <si>
-    <t>口型同步</t>
-  </si>
-  <si>
-    <t>动态表现：播报语音时按音频能量驱动嘴型张合，形成说话口型</t>
-  </si>
-  <si>
-    <t>赵燕凯</t>
-  </si>
-  <si>
-    <t>自动眨眼与头部微动</t>
-  </si>
-  <si>
-    <t>动态表现：数字人按时长随机周期自动眨眼，静默时头部缓慢微动，说话时轻微点头</t>
-  </si>
-  <si>
-    <t>赵燕凯、魏鑫鸿</t>
-  </si>
-  <si>
-    <t>肢体动作</t>
-  </si>
-  <si>
-    <t>动态表现：挥手动作右臂抬起摆动后复位；支持播放.vrma动作文件（关键词触发一次/手动循环）；动作可完整显示表情（眨眼/口型/下巴），通过表情独占名单FULL_EXPRESSION_ACTIONS配置</t>
-  </si>
-  <si>
-    <t>△</t>
-  </si>
-  <si>
-    <t>魏鑫鸿</t>
-  </si>
-  <si>
-    <t>状态提示</t>
-  </si>
-  <si>
-    <t>载入占位提示</t>
-  </si>
-  <si>
-    <t>未加载模型时静态显示占位图标与"数字人形象正在准备中"及说明文字，模型加载后隐藏</t>
-  </si>
-  <si>
     <t>能力标签</t>
   </si>
   <si>
@@ -747,6 +762,66 @@
   </si>
   <si>
     <t>动作：点击选择本地.vrma动作文件并加载播放</t>
+  </si>
+  <si>
+    <t>辅助操作</t>
+  </si>
+  <si>
+    <t>减少动态按钮</t>
+  </si>
+  <si>
+    <t>动作：点击切换"减少动态"模式，暂停数字人待机、动作与视线微动，再次点击恢复；按钮以aria-pressed标注状态</t>
+  </si>
+  <si>
+    <t>放大文字按钮</t>
+  </si>
+  <si>
+    <t>动作：点击切换大字号模式，放大界面文字与点击区域，再次点击恢复字号</t>
+  </si>
+  <si>
+    <t>对话记录</t>
+  </si>
+  <si>
+    <t>动作：点击弹出"对话记录"对话框，展示本次会话全部历史消息，可返回对话</t>
+  </si>
+  <si>
+    <t>自然待机动作</t>
+  </si>
+  <si>
+    <t>动态表现：模型加载后自动播放8秒自然待机动作，含头发/衣服摆动与手部小动作，与口型、眨眼、视线跟随协调</t>
+  </si>
+  <si>
+    <t>视线跟随</t>
+  </si>
+  <si>
+    <t>动态表现：鼠标/触摸移动时数字人视线平滑跟随，移出舞台后回归正视</t>
+  </si>
+  <si>
+    <t>内置人物切换</t>
+  </si>
+  <si>
+    <t>动作：在"演示人员设置"下拉选择内置多个模型并切换，切换后自动恢复全身视角并适配待机/口型/动作</t>
+  </si>
+  <si>
+    <t>声音设置</t>
+  </si>
+  <si>
+    <t>人物声音设置与试听</t>
+  </si>
+  <si>
+    <t>动作：为不同人物设置男声/女声或跟随人物，支持试听；设置按人物保存在浏览器</t>
+  </si>
+  <si>
+    <t>安家谊、魏鑫鸿</t>
+  </si>
+  <si>
+    <t>快捷服务</t>
+  </si>
+  <si>
+    <t>常用服务入口</t>
+  </si>
+  <si>
+    <t>动作：点击底部"问问健康""查看提醒""预约服务"按钮，一键发起对应服务流程，无需打字</t>
   </si>
   <si>
     <t>○：完成（通过评审或测试）   △：进行中   ×：未着手   N/A：不适用（没有此项活动）</t>
@@ -2146,7 +2221,7 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2291,7 +2366,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2419,9 +2494,6 @@
     <xf numFmtId="49" fontId="15" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2440,13 +2512,40 @@
     <xf numFmtId="181" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="15" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3837,361 +3936,361 @@
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="8.75221238938053" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="9.87610619469027" style="139" customWidth="1"/>
-    <col min="2" max="2" width="10.3716814159292" style="139" customWidth="1"/>
-    <col min="3" max="3" width="9.87610619469027" style="139" customWidth="1"/>
-    <col min="4" max="4" width="8.75221238938053" style="139" customWidth="1"/>
-    <col min="5" max="5" width="10" style="139" customWidth="1"/>
-    <col min="6" max="6" width="9.75221238938053" style="139" customWidth="1"/>
-    <col min="7" max="7" width="9.50442477876106" style="139" customWidth="1"/>
-    <col min="8" max="8" width="16.7522123893805" style="139" customWidth="1"/>
-    <col min="9" max="16384" width="8.75221238938053" style="139" customWidth="1"/>
+    <col min="1" max="1" width="9.87610619469027" style="147" customWidth="1"/>
+    <col min="2" max="2" width="10.3716814159292" style="147" customWidth="1"/>
+    <col min="3" max="3" width="9.87610619469027" style="147" customWidth="1"/>
+    <col min="4" max="4" width="8.75221238938053" style="147" customWidth="1"/>
+    <col min="5" max="5" width="10" style="147" customWidth="1"/>
+    <col min="6" max="6" width="9.75221238938053" style="147" customWidth="1"/>
+    <col min="7" max="7" width="9.50442477876106" style="147" customWidth="1"/>
+    <col min="8" max="8" width="16.7522123893805" style="147" customWidth="1"/>
+    <col min="9" max="16384" width="8.75221238938053" style="147" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.75" customHeight="1" spans="1:8">
-      <c r="A1" s="140"/>
+      <c r="A1" s="148"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="140"/>
-    </row>
-    <row r="3" s="138" customFormat="1" ht="24" customHeight="1" spans="1:8">
-      <c r="A3" s="141" t="s">
+      <c r="A2" s="148"/>
+    </row>
+    <row r="3" s="146" customFormat="1" ht="24" customHeight="1" spans="1:8">
+      <c r="A3" s="149" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="142" t="s">
+      <c r="B3" s="150" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="143"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="144"/>
-    </row>
-    <row r="4" s="138" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
-      <c r="A4" s="145"/>
-      <c r="H4" s="146" t="s">
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="152"/>
+    </row>
+    <row r="4" s="146" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
+      <c r="A4" s="153"/>
+      <c r="H4" s="154" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="138" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
-      <c r="A5" s="145" t="s">
+    <row r="5" s="146" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
+      <c r="A5" s="153" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="143"/>
-      <c r="G5" s="147" t="s">
+      <c r="F5" s="151"/>
+      <c r="G5" s="155" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A6" s="148"/>
-      <c r="B6" s="149"/>
-      <c r="C6" s="149"/>
-      <c r="D6" s="149"/>
-      <c r="E6" s="149"/>
-    </row>
-    <row r="7" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A7" s="150"/>
-      <c r="B7" s="144"/>
-      <c r="C7" s="144"/>
-      <c r="D7" s="144"/>
-      <c r="E7" s="144"/>
-      <c r="F7" s="144"/>
-      <c r="G7" s="144"/>
-      <c r="H7" s="144"/>
-    </row>
-    <row r="8" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A8" s="150"/>
-      <c r="B8" s="144"/>
-      <c r="C8" s="144"/>
-      <c r="D8" s="144"/>
-      <c r="E8" s="144"/>
-      <c r="F8" s="144"/>
-      <c r="G8" s="144"/>
-      <c r="H8" s="144"/>
-    </row>
-    <row r="9" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A9" s="150"/>
-      <c r="B9" s="144"/>
-      <c r="C9" s="144"/>
-      <c r="D9" s="144"/>
-      <c r="E9" s="144"/>
-      <c r="F9" s="144"/>
-      <c r="G9" s="144"/>
-      <c r="H9" s="144"/>
-    </row>
-    <row r="10" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A10" s="150"/>
-      <c r="B10" s="144"/>
-      <c r="C10" s="144"/>
-      <c r="D10" s="144"/>
-      <c r="E10" s="144"/>
-      <c r="F10" s="144"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="144"/>
-    </row>
-    <row r="11" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A11" s="150"/>
-      <c r="B11" s="144"/>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-    </row>
-    <row r="12" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A12" s="150"/>
-      <c r="B12" s="144"/>
-      <c r="C12" s="144"/>
-      <c r="D12" s="144"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="144"/>
-    </row>
-    <row r="13" s="138" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
-      <c r="A13" s="151" t="s">
+      <c r="A6" s="156"/>
+      <c r="B6" s="157"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
+    </row>
+    <row r="7" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A7" s="158"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="152"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="152"/>
+    </row>
+    <row r="8" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A8" s="158"/>
+      <c r="B8" s="152"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="152"/>
+      <c r="E8" s="152"/>
+      <c r="F8" s="152"/>
+      <c r="G8" s="152"/>
+      <c r="H8" s="152"/>
+    </row>
+    <row r="9" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A9" s="158"/>
+      <c r="B9" s="152"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="152"/>
+      <c r="E9" s="152"/>
+      <c r="F9" s="152"/>
+      <c r="G9" s="152"/>
+      <c r="H9" s="152"/>
+    </row>
+    <row r="10" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A10" s="158"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="152"/>
+      <c r="E10" s="152"/>
+      <c r="F10" s="152"/>
+      <c r="G10" s="152"/>
+      <c r="H10" s="152"/>
+    </row>
+    <row r="11" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A11" s="158"/>
+      <c r="B11" s="152"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="152"/>
+      <c r="E11" s="152"/>
+      <c r="F11" s="152"/>
+      <c r="G11" s="152"/>
+      <c r="H11" s="152"/>
+    </row>
+    <row r="12" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A12" s="158"/>
+      <c r="B12" s="152"/>
+      <c r="C12" s="152"/>
+      <c r="D12" s="152"/>
+      <c r="E12" s="152"/>
+      <c r="F12" s="152"/>
+      <c r="G12" s="152"/>
+      <c r="H12" s="152"/>
+    </row>
+    <row r="13" s="146" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
+      <c r="A13" s="159" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A14" s="150"/>
-      <c r="B14" s="152"/>
-      <c r="C14" s="144"/>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-    </row>
-    <row r="15" s="138" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
-      <c r="A15" s="153" t="s">
+    <row r="14" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A14" s="158"/>
+      <c r="B14" s="160"/>
+      <c r="C14" s="152"/>
+      <c r="D14" s="152"/>
+      <c r="E14" s="152"/>
+      <c r="F14" s="152"/>
+      <c r="G14" s="152"/>
+      <c r="H14" s="152"/>
+    </row>
+    <row r="15" s="146" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
+      <c r="A15" s="161" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A16" s="150"/>
-      <c r="B16" s="144"/>
-      <c r="C16" s="144"/>
-      <c r="D16" s="144"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="144"/>
-    </row>
-    <row r="17" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A17" s="150"/>
-      <c r="B17" s="144"/>
-      <c r="C17" s="144"/>
-      <c r="D17" s="144"/>
-      <c r="E17" s="144"/>
-      <c r="F17" s="144"/>
-      <c r="G17" s="144"/>
-      <c r="H17" s="144"/>
-    </row>
-    <row r="18" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A18" s="150"/>
-      <c r="B18" s="144"/>
-      <c r="C18" s="144"/>
-      <c r="D18" s="144"/>
-      <c r="E18" s="144"/>
-      <c r="F18" s="144"/>
-      <c r="G18" s="144"/>
-      <c r="H18" s="144"/>
-    </row>
-    <row r="19" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A19" s="150"/>
-      <c r="B19" s="144"/>
-      <c r="C19" s="144"/>
-      <c r="D19" s="144"/>
-      <c r="E19" s="144"/>
-      <c r="F19" s="144"/>
-      <c r="G19" s="144"/>
-      <c r="H19" s="144"/>
-    </row>
-    <row r="20" s="138" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A20" s="154" t="s">
+    <row r="16" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A16" s="158"/>
+      <c r="B16" s="152"/>
+      <c r="C16" s="152"/>
+      <c r="D16" s="152"/>
+      <c r="E16" s="152"/>
+      <c r="F16" s="152"/>
+      <c r="G16" s="152"/>
+      <c r="H16" s="152"/>
+    </row>
+    <row r="17" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A17" s="158"/>
+      <c r="B17" s="152"/>
+      <c r="C17" s="152"/>
+      <c r="D17" s="152"/>
+      <c r="E17" s="152"/>
+      <c r="F17" s="152"/>
+      <c r="G17" s="152"/>
+      <c r="H17" s="152"/>
+    </row>
+    <row r="18" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A18" s="158"/>
+      <c r="B18" s="152"/>
+      <c r="C18" s="152"/>
+      <c r="D18" s="152"/>
+      <c r="E18" s="152"/>
+      <c r="F18" s="152"/>
+      <c r="G18" s="152"/>
+      <c r="H18" s="152"/>
+    </row>
+    <row r="19" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A19" s="158"/>
+      <c r="B19" s="152"/>
+      <c r="C19" s="152"/>
+      <c r="D19" s="152"/>
+      <c r="E19" s="152"/>
+      <c r="F19" s="152"/>
+      <c r="G19" s="152"/>
+      <c r="H19" s="152"/>
+    </row>
+    <row r="20" s="146" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
+      <c r="A20" s="162" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A21" s="150"/>
-      <c r="B21" s="144"/>
-      <c r="C21" s="144"/>
-      <c r="D21" s="144"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-    </row>
-    <row r="22" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A22" s="150"/>
-      <c r="B22" s="144"/>
-      <c r="C22" s="144"/>
-      <c r="D22" s="144"/>
-      <c r="E22" s="144"/>
-      <c r="F22" s="144"/>
-      <c r="G22" s="144"/>
-      <c r="H22" s="144"/>
-    </row>
-    <row r="23" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A23" s="150"/>
-      <c r="B23" s="144"/>
-      <c r="C23" s="144"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="144"/>
-    </row>
-    <row r="24" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A24" s="150"/>
-      <c r="B24" s="144"/>
-      <c r="C24" s="144"/>
-      <c r="D24" s="144"/>
-      <c r="E24" s="144"/>
-      <c r="F24" s="144"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="144"/>
-    </row>
-    <row r="25" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A25" s="150"/>
-      <c r="B25" s="144"/>
-      <c r="C25" s="144"/>
-      <c r="D25" s="144"/>
-      <c r="E25" s="144"/>
-      <c r="F25" s="144"/>
-      <c r="G25" s="144"/>
-      <c r="H25" s="144"/>
-    </row>
-    <row r="26" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A26" s="150"/>
-      <c r="B26" s="144"/>
-      <c r="C26" s="144"/>
-      <c r="D26" s="144"/>
-      <c r="E26" s="144"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="144"/>
-      <c r="H26" s="144"/>
-    </row>
-    <row r="27" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A27" s="150"/>
-      <c r="B27" s="144"/>
-      <c r="C27" s="144"/>
-      <c r="D27" s="144"/>
-      <c r="E27" s="144"/>
-      <c r="F27" s="144"/>
-      <c r="G27" s="144"/>
-      <c r="H27" s="144"/>
-    </row>
-    <row r="28" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A28" s="150"/>
-      <c r="B28" s="144"/>
-      <c r="C28" s="144"/>
-      <c r="D28" s="144"/>
-      <c r="E28" s="144"/>
-      <c r="F28" s="144"/>
-      <c r="G28" s="144"/>
-      <c r="H28" s="144"/>
-    </row>
-    <row r="29" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A29" s="150"/>
-      <c r="B29" s="144"/>
-      <c r="C29" s="144"/>
-      <c r="D29" s="144"/>
-      <c r="E29" s="144"/>
-      <c r="F29" s="144"/>
-      <c r="G29" s="144"/>
-      <c r="H29" s="144"/>
-    </row>
-    <row r="30" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A30" s="150"/>
-      <c r="B30" s="144"/>
-      <c r="C30" s="144"/>
-      <c r="D30" s="144"/>
-      <c r="E30" s="144"/>
-      <c r="F30" s="144"/>
-      <c r="G30" s="144"/>
-      <c r="H30" s="144"/>
-    </row>
-    <row r="31" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A31" s="150"/>
-      <c r="B31" s="144"/>
-      <c r="C31" s="144"/>
-      <c r="D31" s="144"/>
-      <c r="E31" s="144"/>
-      <c r="F31" s="144"/>
-      <c r="G31" s="144"/>
-      <c r="H31" s="144"/>
-    </row>
-    <row r="32" s="138" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A32" s="155"/>
-    </row>
-    <row r="33" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A33" s="150"/>
-      <c r="B33" s="144"/>
-      <c r="C33" s="144"/>
-      <c r="D33" s="144"/>
-      <c r="E33" s="144"/>
-      <c r="F33" s="144"/>
-      <c r="G33" s="144"/>
-      <c r="H33" s="144"/>
-    </row>
-    <row r="34" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A34" s="150"/>
-      <c r="B34" s="144"/>
-      <c r="C34" s="144"/>
-      <c r="D34" s="144"/>
-      <c r="E34" s="144"/>
-      <c r="F34" s="144"/>
-      <c r="G34" s="144"/>
-      <c r="H34" s="144"/>
-    </row>
-    <row r="35" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A35" s="150"/>
-      <c r="B35" s="144"/>
-      <c r="C35" s="144"/>
-      <c r="D35" s="144"/>
-      <c r="E35" s="144"/>
-      <c r="F35" s="144"/>
-      <c r="G35" s="144"/>
-      <c r="H35" s="144"/>
-    </row>
-    <row r="36" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A36" s="156" t="s">
+    <row r="21" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A21" s="158"/>
+      <c r="B21" s="152"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="152"/>
+    </row>
+    <row r="22" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A22" s="158"/>
+      <c r="B22" s="152"/>
+      <c r="C22" s="152"/>
+      <c r="D22" s="152"/>
+      <c r="E22" s="152"/>
+      <c r="F22" s="152"/>
+      <c r="G22" s="152"/>
+      <c r="H22" s="152"/>
+    </row>
+    <row r="23" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A23" s="158"/>
+      <c r="B23" s="152"/>
+      <c r="C23" s="152"/>
+      <c r="D23" s="152"/>
+      <c r="E23" s="152"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="152"/>
+      <c r="H23" s="152"/>
+    </row>
+    <row r="24" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A24" s="158"/>
+      <c r="B24" s="152"/>
+      <c r="C24" s="152"/>
+      <c r="D24" s="152"/>
+      <c r="E24" s="152"/>
+      <c r="F24" s="152"/>
+      <c r="G24" s="152"/>
+      <c r="H24" s="152"/>
+    </row>
+    <row r="25" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A25" s="158"/>
+      <c r="B25" s="152"/>
+      <c r="C25" s="152"/>
+      <c r="D25" s="152"/>
+      <c r="E25" s="152"/>
+      <c r="F25" s="152"/>
+      <c r="G25" s="152"/>
+      <c r="H25" s="152"/>
+    </row>
+    <row r="26" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A26" s="158"/>
+      <c r="B26" s="152"/>
+      <c r="C26" s="152"/>
+      <c r="D26" s="152"/>
+      <c r="E26" s="152"/>
+      <c r="F26" s="152"/>
+      <c r="G26" s="152"/>
+      <c r="H26" s="152"/>
+    </row>
+    <row r="27" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A27" s="158"/>
+      <c r="B27" s="152"/>
+      <c r="C27" s="152"/>
+      <c r="D27" s="152"/>
+      <c r="E27" s="152"/>
+      <c r="F27" s="152"/>
+      <c r="G27" s="152"/>
+      <c r="H27" s="152"/>
+    </row>
+    <row r="28" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A28" s="158"/>
+      <c r="B28" s="152"/>
+      <c r="C28" s="152"/>
+      <c r="D28" s="152"/>
+      <c r="E28" s="152"/>
+      <c r="F28" s="152"/>
+      <c r="G28" s="152"/>
+      <c r="H28" s="152"/>
+    </row>
+    <row r="29" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A29" s="158"/>
+      <c r="B29" s="152"/>
+      <c r="C29" s="152"/>
+      <c r="D29" s="152"/>
+      <c r="E29" s="152"/>
+      <c r="F29" s="152"/>
+      <c r="G29" s="152"/>
+      <c r="H29" s="152"/>
+    </row>
+    <row r="30" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A30" s="158"/>
+      <c r="B30" s="152"/>
+      <c r="C30" s="152"/>
+      <c r="D30" s="152"/>
+      <c r="E30" s="152"/>
+      <c r="F30" s="152"/>
+      <c r="G30" s="152"/>
+      <c r="H30" s="152"/>
+    </row>
+    <row r="31" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A31" s="158"/>
+      <c r="B31" s="152"/>
+      <c r="C31" s="152"/>
+      <c r="D31" s="152"/>
+      <c r="E31" s="152"/>
+      <c r="F31" s="152"/>
+      <c r="G31" s="152"/>
+      <c r="H31" s="152"/>
+    </row>
+    <row r="32" s="146" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
+      <c r="A32" s="163"/>
+    </row>
+    <row r="33" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A33" s="158"/>
+      <c r="B33" s="152"/>
+      <c r="C33" s="152"/>
+      <c r="D33" s="152"/>
+      <c r="E33" s="152"/>
+      <c r="F33" s="152"/>
+      <c r="G33" s="152"/>
+      <c r="H33" s="152"/>
+    </row>
+    <row r="34" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A34" s="158"/>
+      <c r="B34" s="152"/>
+      <c r="C34" s="152"/>
+      <c r="D34" s="152"/>
+      <c r="E34" s="152"/>
+      <c r="F34" s="152"/>
+      <c r="G34" s="152"/>
+      <c r="H34" s="152"/>
+    </row>
+    <row r="35" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A35" s="158"/>
+      <c r="B35" s="152"/>
+      <c r="C35" s="152"/>
+      <c r="D35" s="152"/>
+      <c r="E35" s="152"/>
+      <c r="F35" s="152"/>
+      <c r="G35" s="152"/>
+      <c r="H35" s="152"/>
+    </row>
+    <row r="36" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A36" s="164" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="157"/>
-      <c r="C36" s="156" t="s">
+      <c r="B36" s="165"/>
+      <c r="C36" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="157"/>
-      <c r="E36" s="156" t="s">
+      <c r="D36" s="165"/>
+      <c r="E36" s="164" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="158"/>
-      <c r="G36" s="156" t="s">
+      <c r="F36" s="166"/>
+      <c r="G36" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="159"/>
-    </row>
-    <row r="37" s="138" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A37" s="160" t="s">
+      <c r="H36" s="167"/>
+    </row>
+    <row r="37" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A37" s="168" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="161"/>
-      <c r="C37" s="162"/>
-      <c r="D37" s="163"/>
-      <c r="E37" s="160" t="s">
+      <c r="B37" s="169"/>
+      <c r="C37" s="170"/>
+      <c r="D37" s="171"/>
+      <c r="E37" s="168" t="s">
         <v>13</v>
       </c>
-      <c r="F37" s="164"/>
-      <c r="G37" s="162"/>
-      <c r="H37" s="163"/>
+      <c r="F37" s="172"/>
+      <c r="G37" s="170"/>
+      <c r="H37" s="171"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="140"/>
+      <c r="A38" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4223,7 +4322,7 @@
     <col min="2" max="2" width="3.3716814159292" style="79" customWidth="1"/>
     <col min="3" max="3" width="10.7522123893805" style="80" customWidth="1"/>
     <col min="4" max="4" width="23.3716814159292" style="79" customWidth="1"/>
-    <col min="5" max="5" width="7.3716814159292" style="79" customWidth="1"/>
+    <col min="5" max="5" width="9.55752212389381" style="79" customWidth="1"/>
     <col min="6" max="6" width="12.7522123893805" style="79" customWidth="1"/>
     <col min="7" max="7" width="9.3716814159292" style="79" customWidth="1"/>
     <col min="8" max="8" width="6.87610619469027" style="79" customWidth="1"/>
@@ -4301,7 +4400,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" s="75" customFormat="1" ht="14.25" spans="2:16">
+    <row r="3" s="75" customFormat="1" ht="14.25" customHeight="1" spans="2:16">
       <c r="B3" s="88">
         <v>1</v>
       </c>
@@ -4361,28 +4460,28 @@
       <c r="E4" s="101" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="102" t="s">
+      <c r="F4" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="103" t="s">
+      <c r="G4" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="104">
+      <c r="H4" s="103">
         <v>17</v>
       </c>
-      <c r="I4" s="105">
+      <c r="I4" s="104">
         <v>22</v>
       </c>
-      <c r="J4" s="105">
+      <c r="J4" s="104">
         <v>0</v>
       </c>
-      <c r="K4" s="105">
+      <c r="K4" s="104">
         <v>0</v>
       </c>
       <c r="L4" s="94">
         <v>22</v>
       </c>
-      <c r="M4" s="106">
+      <c r="M4" s="105">
         <v>0.2941</v>
       </c>
       <c r="N4" s="96" t="s">
@@ -4391,7 +4490,7 @@
       <c r="O4" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="P4" s="107">
+      <c r="P4" s="106">
         <v>0.3</v>
       </c>
     </row>
@@ -4399,390 +4498,420 @@
       <c r="B5" s="98">
         <v>3</v>
       </c>
-      <c r="C5" s="108" t="s">
+      <c r="C5" s="107" t="s">
         <v>43</v>
       </c>
       <c r="D5" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="109" t="s">
+      <c r="E5" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="105" t="s">
+      <c r="F5" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="103" t="s">
+      <c r="G5" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="104">
+      <c r="H5" s="103">
         <v>22</v>
       </c>
-      <c r="I5" s="105">
+      <c r="I5" s="104">
         <v>0</v>
       </c>
-      <c r="J5" s="105">
+      <c r="J5" s="104">
         <v>0</v>
       </c>
-      <c r="K5" s="105">
+      <c r="K5" s="104">
         <v>1</v>
       </c>
       <c r="L5" s="94">
         <v>22</v>
       </c>
-      <c r="M5" s="106">
+      <c r="M5" s="105">
         <v>0.045</v>
       </c>
-      <c r="N5" s="103" t="s">
+      <c r="N5" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="O5" s="103" t="s">
+      <c r="O5" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="P5" s="107">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B6" s="98">
+      <c r="P5" s="106">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" s="75" customFormat="1" ht="13" customHeight="1" spans="2:16">
+      <c r="B6" s="108">
         <v>4</v>
       </c>
-      <c r="C6" s="108"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="104"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="105"/>
-      <c r="L6" s="94"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="103"/>
-      <c r="O6" s="103"/>
-      <c r="P6" s="110"/>
+      <c r="C6" s="109" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="111" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="112" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="113" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="114">
+        <v>22</v>
+      </c>
+      <c r="I6" s="112">
+        <v>8</v>
+      </c>
+      <c r="J6" s="112">
+        <v>0</v>
+      </c>
+      <c r="K6" s="112">
+        <v>3</v>
+      </c>
+      <c r="L6" s="115">
+        <v>30</v>
+      </c>
+      <c r="M6" s="116">
+        <v>0.5</v>
+      </c>
+      <c r="N6" s="113" t="s">
+        <v>53</v>
+      </c>
+      <c r="O6" s="113" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" s="117">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="7" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B7" s="98">
         <v>5</v>
       </c>
-      <c r="C7" s="108"/>
+      <c r="C7" s="107"/>
       <c r="D7" s="100"/>
       <c r="E7" s="101"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="104"/>
       <c r="L7" s="94"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="111"/>
-      <c r="O7" s="103"/>
-      <c r="P7" s="110"/>
+      <c r="M7" s="105"/>
+      <c r="N7" s="118"/>
+      <c r="O7" s="102"/>
+      <c r="P7" s="106">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="8" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B8" s="98">
         <v>6</v>
       </c>
-      <c r="C8" s="108"/>
+      <c r="C8" s="107"/>
       <c r="D8" s="100"/>
       <c r="E8" s="101"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
-      <c r="K8" s="105"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="104"/>
+      <c r="K8" s="104"/>
       <c r="L8" s="94"/>
-      <c r="M8" s="106"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="111"/>
-      <c r="P8" s="110"/>
+      <c r="M8" s="105"/>
+      <c r="N8" s="118"/>
+      <c r="O8" s="118"/>
+      <c r="P8" s="119"/>
     </row>
     <row r="9" s="76" customFormat="1" ht="12" customHeight="1" spans="2:16">
-      <c r="B9" s="112">
+      <c r="B9" s="120">
         <v>7</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="121"/>
       <c r="D9" s="90"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="115"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="123"/>
       <c r="G9" s="93"/>
       <c r="H9" s="92"/>
-      <c r="I9" s="115"/>
-      <c r="J9" s="115"/>
-      <c r="K9" s="115"/>
+      <c r="I9" s="123"/>
+      <c r="J9" s="123"/>
+      <c r="K9" s="123"/>
       <c r="L9" s="94"/>
-      <c r="M9" s="106"/>
-      <c r="N9" s="116"/>
-      <c r="O9" s="116"/>
-      <c r="P9" s="117"/>
+      <c r="M9" s="105"/>
+      <c r="N9" s="124"/>
+      <c r="O9" s="124"/>
+      <c r="P9" s="125"/>
     </row>
     <row r="10" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B10" s="98">
         <v>8</v>
       </c>
-      <c r="C10" s="118"/>
+      <c r="C10" s="126"/>
       <c r="D10" s="100"/>
       <c r="E10" s="101"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="103"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="102"/>
       <c r="H10" s="92"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="105"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="104"/>
       <c r="L10" s="94"/>
-      <c r="M10" s="106"/>
-      <c r="N10" s="116"/>
-      <c r="O10" s="111"/>
-      <c r="P10" s="117"/>
+      <c r="M10" s="105"/>
+      <c r="N10" s="124"/>
+      <c r="O10" s="118"/>
+      <c r="P10" s="125"/>
     </row>
     <row r="11" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B11" s="98">
         <v>9</v>
       </c>
-      <c r="C11" s="118"/>
+      <c r="C11" s="126"/>
       <c r="D11" s="100"/>
       <c r="E11" s="101"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="105"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
       <c r="L11" s="94"/>
-      <c r="M11" s="106"/>
-      <c r="N11" s="116"/>
-      <c r="O11" s="111"/>
-      <c r="P11" s="117"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="124"/>
+      <c r="O11" s="118"/>
+      <c r="P11" s="125"/>
     </row>
     <row r="12" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B12" s="98">
         <v>10</v>
       </c>
-      <c r="C12" s="118"/>
+      <c r="C12" s="126"/>
       <c r="D12" s="100"/>
       <c r="E12" s="101"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="105"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="104"/>
       <c r="L12" s="94"/>
-      <c r="M12" s="106"/>
-      <c r="N12" s="116"/>
-      <c r="O12" s="111"/>
-      <c r="P12" s="117"/>
+      <c r="M12" s="105"/>
+      <c r="N12" s="124"/>
+      <c r="O12" s="118"/>
+      <c r="P12" s="125"/>
     </row>
     <row r="13" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B13" s="98">
         <v>11</v>
       </c>
-      <c r="C13" s="119"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="123"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="122"/>
-      <c r="K13" s="122"/>
-      <c r="L13" s="125"/>
-      <c r="M13" s="126"/>
-      <c r="N13" s="127"/>
-      <c r="O13" s="128"/>
-      <c r="P13" s="129"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="128"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="133"/>
+      <c r="M13" s="134"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="136"/>
+      <c r="P13" s="137"/>
     </row>
     <row r="14" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B14" s="98">
         <v>12</v>
       </c>
-      <c r="C14" s="119"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="123"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="122"/>
-      <c r="K14" s="122"/>
-      <c r="L14" s="125"/>
-      <c r="M14" s="126"/>
-      <c r="N14" s="128"/>
-      <c r="O14" s="128"/>
-      <c r="P14" s="129"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="130"/>
+      <c r="G14" s="131"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="130"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="133"/>
+      <c r="M14" s="134"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="137"/>
     </row>
     <row r="15" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B15" s="98">
         <v>13</v>
       </c>
-      <c r="C15" s="108"/>
+      <c r="C15" s="107"/>
       <c r="D15" s="100"/>
       <c r="E15" s="101"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="103"/>
-      <c r="H15" s="104"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="105"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="104"/>
+      <c r="K15" s="104"/>
       <c r="L15" s="94"/>
-      <c r="M15" s="106"/>
-      <c r="N15" s="130"/>
-      <c r="O15" s="130"/>
-      <c r="P15" s="131"/>
+      <c r="M15" s="105"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="138"/>
+      <c r="P15" s="139"/>
     </row>
     <row r="16" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B16" s="98">
         <v>14</v>
       </c>
-      <c r="C16" s="108"/>
+      <c r="C16" s="107"/>
       <c r="D16" s="100"/>
       <c r="E16" s="101"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="105"/>
-      <c r="J16" s="105"/>
-      <c r="K16" s="105"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="103"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="104"/>
+      <c r="K16" s="104"/>
       <c r="L16" s="94"/>
-      <c r="M16" s="106"/>
-      <c r="N16" s="130"/>
-      <c r="O16" s="130"/>
-      <c r="P16" s="131"/>
+      <c r="M16" s="105"/>
+      <c r="N16" s="138"/>
+      <c r="O16" s="138"/>
+      <c r="P16" s="139"/>
     </row>
     <row r="17" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B17" s="98">
         <v>15</v>
       </c>
-      <c r="C17" s="108"/>
+      <c r="C17" s="107"/>
       <c r="D17" s="100"/>
       <c r="E17" s="101"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="104"/>
       <c r="L17" s="94"/>
-      <c r="M17" s="106"/>
-      <c r="N17" s="132"/>
-      <c r="O17" s="132"/>
-      <c r="P17" s="131"/>
+      <c r="M17" s="105"/>
+      <c r="N17" s="140"/>
+      <c r="O17" s="140"/>
+      <c r="P17" s="139"/>
     </row>
     <row r="18" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B18" s="98">
         <v>16</v>
       </c>
-      <c r="C18" s="108"/>
+      <c r="C18" s="107"/>
       <c r="D18" s="100"/>
       <c r="E18" s="101"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="105"/>
-      <c r="K18" s="105"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
       <c r="L18" s="94"/>
-      <c r="M18" s="106"/>
-      <c r="N18" s="132"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="131"/>
+      <c r="M18" s="105"/>
+      <c r="N18" s="140"/>
+      <c r="O18" s="140"/>
+      <c r="P18" s="139"/>
     </row>
     <row r="19" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B19" s="98">
         <v>17</v>
       </c>
-      <c r="C19" s="108"/>
+      <c r="C19" s="107"/>
       <c r="D19" s="100"/>
       <c r="E19" s="101"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="104"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="104"/>
       <c r="L19" s="94"/>
-      <c r="M19" s="106"/>
-      <c r="N19" s="132"/>
-      <c r="O19" s="132"/>
-      <c r="P19" s="131"/>
+      <c r="M19" s="105"/>
+      <c r="N19" s="140"/>
+      <c r="O19" s="140"/>
+      <c r="P19" s="139"/>
     </row>
     <row r="20" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B20" s="98">
         <v>18</v>
       </c>
-      <c r="C20" s="108"/>
+      <c r="C20" s="107"/>
       <c r="D20" s="100"/>
       <c r="E20" s="101"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="103"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
       <c r="L20" s="94"/>
-      <c r="M20" s="106"/>
-      <c r="N20" s="132"/>
-      <c r="O20" s="132"/>
-      <c r="P20" s="131"/>
+      <c r="M20" s="105"/>
+      <c r="N20" s="140"/>
+      <c r="O20" s="140"/>
+      <c r="P20" s="139"/>
     </row>
     <row r="21" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B21" s="98">
         <v>19</v>
       </c>
-      <c r="C21" s="108"/>
+      <c r="C21" s="107"/>
       <c r="D21" s="100"/>
       <c r="E21" s="101"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="104"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="105"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="104"/>
       <c r="L21" s="94"/>
-      <c r="M21" s="106"/>
-      <c r="N21" s="132"/>
-      <c r="O21" s="132"/>
-      <c r="P21" s="131"/>
+      <c r="M21" s="105"/>
+      <c r="N21" s="140"/>
+      <c r="O21" s="140"/>
+      <c r="P21" s="139"/>
     </row>
     <row r="22" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
       <c r="B22" s="98">
         <v>20</v>
       </c>
-      <c r="C22" s="108"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="100"/>
       <c r="E22" s="101"/>
-      <c r="F22" s="105"/>
-      <c r="G22" s="103"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="105"/>
-      <c r="K22" s="105"/>
+      <c r="F22" s="104"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="103"/>
+      <c r="I22" s="104"/>
+      <c r="J22" s="104"/>
+      <c r="K22" s="104"/>
       <c r="L22" s="94"/>
-      <c r="M22" s="106"/>
-      <c r="N22" s="132"/>
-      <c r="O22" s="132"/>
-      <c r="P22" s="131"/>
-    </row>
-    <row r="23" s="77" customFormat="1" ht="13.9" spans="2:16">
-      <c r="B23" s="133" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="134"/>
-      <c r="D23" s="134"/>
-      <c r="E23" s="134"/>
-      <c r="F23" s="134"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="135"/>
-      <c r="I23" s="135"/>
-      <c r="J23" s="135"/>
-      <c r="K23" s="135"/>
-      <c r="L23" s="135"/>
-      <c r="M23" s="136"/>
-      <c r="N23" s="135"/>
-      <c r="O23" s="135"/>
-      <c r="P23" s="137"/>
+      <c r="M22" s="105"/>
+      <c r="N22" s="140"/>
+      <c r="O22" s="140"/>
+      <c r="P22" s="139"/>
+    </row>
+    <row r="23" s="77" customFormat="1" ht="13.9" customHeight="1" spans="2:16">
+      <c r="B23" s="141" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="142"/>
+      <c r="D23" s="142"/>
+      <c r="E23" s="142"/>
+      <c r="F23" s="142"/>
+      <c r="G23" s="142"/>
+      <c r="H23" s="143"/>
+      <c r="I23" s="143"/>
+      <c r="J23" s="143"/>
+      <c r="K23" s="143"/>
+      <c r="L23" s="143"/>
+      <c r="M23" s="144"/>
+      <c r="N23" s="143"/>
+      <c r="O23" s="143"/>
+      <c r="P23" s="145"/>
     </row>
     <row r="24" s="78" customFormat="1"/>
     <row r="25" s="78" customFormat="1"/>
@@ -4826,23 +4955,23 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:11">
       <c r="B1" s="12" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="13.9" customHeight="1" spans="1:11">
       <c r="A2" s="1"/>
       <c r="B2" s="13" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D2" s="14"/>
       <c r="E2" s="15" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G2" s="16"/>
       <c r="H2" s="16"/>
@@ -4856,83 +4985,83 @@
     <row r="4" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:11">
       <c r="A4" s="1"/>
       <c r="B4" s="20" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G4" s="23"/>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
       <c r="J4" s="22" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:11">
       <c r="A5" s="1"/>
       <c r="B5" s="25"/>
       <c r="C5" s="26" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="28" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J5" s="27"/>
       <c r="K5" s="29"/>
     </row>
-    <row r="6" s="4" customFormat="1" ht="33.75" customHeight="1" spans="1:11">
+    <row r="6" s="4" customFormat="1" ht="29" customHeight="1" spans="1:11">
       <c r="A6" s="1"/>
       <c r="B6" s="30">
         <v>1</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J6" s="35" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K6" s="36" t="s">
         <v>34</v>
@@ -4944,28 +5073,28 @@
         <v>2</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J7" s="35" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K7" s="36" t="s">
         <v>34</v>
@@ -4977,28 +5106,28 @@
         <v>3</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J8" s="35" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K8" s="36" t="s">
         <v>34</v>
@@ -5010,28 +5139,28 @@
         <v>4</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E9" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="35" t="s">
         <v>79</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" s="35" t="s">
-        <v>73</v>
       </c>
       <c r="K9" s="36" t="s">
         <v>34</v>
@@ -5043,28 +5172,28 @@
         <v>5</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J10" s="35" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K10" s="36" t="s">
         <v>34</v>
@@ -5076,28 +5205,28 @@
         <v>6</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K11" s="36" t="s">
         <v>34</v>
@@ -5109,28 +5238,28 @@
         <v>7</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H12" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J12" s="35" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K12" s="36" t="s">
         <v>34</v>
@@ -5142,28 +5271,28 @@
         <v>8</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H13" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="J13" s="35" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K13" s="36" t="s">
         <v>34</v>
@@ -5175,28 +5304,28 @@
         <v>9</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K14" s="36" t="s">
         <v>34</v>
@@ -5208,28 +5337,28 @@
         <v>10</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I15" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="K15" s="36" t="s">
         <v>34</v>
@@ -5241,28 +5370,28 @@
         <v>11</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F16" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="G16" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="I16" s="34" t="s">
-        <v>81</v>
-      </c>
       <c r="J16" s="35" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="K16" s="36" t="s">
         <v>34</v>
@@ -5274,25 +5403,25 @@
         <v>12</v>
       </c>
       <c r="C17" s="46" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E17" s="48" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I17" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J17" s="35" t="s">
         <v>34</v>
@@ -5307,25 +5436,25 @@
         <v>13</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F18" s="32" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I18" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J18" s="35" t="s">
         <v>34</v>
@@ -5340,28 +5469,28 @@
         <v>14</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E19" s="52" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I19" s="34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J19" s="35" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K19" s="36" t="s">
         <v>34</v>
@@ -5373,25 +5502,25 @@
         <v>15</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E20" s="40" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F20" s="51" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I20" s="34" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="J20" s="35" t="s">
         <v>34</v>
@@ -5406,28 +5535,28 @@
         <v>16</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H21" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I21" s="34" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="J21" s="35" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="K21" s="36" t="s">
         <v>34</v>
@@ -5439,25 +5568,25 @@
         <v>17</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I22" s="34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J22" s="35" t="s">
         <v>34</v>
@@ -5472,28 +5601,28 @@
         <v>18</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I23" s="34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J23" s="35" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K23" s="36" t="s">
         <v>34</v>
@@ -5505,28 +5634,28 @@
         <v>19</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F24" s="51" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H24" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I24" s="34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J24" s="35" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K24" s="36" t="s">
         <v>34</v>
@@ -5538,28 +5667,28 @@
         <v>20</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H25" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I25" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J25" s="35" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="K25" s="36" t="s">
         <v>34</v>
@@ -5571,28 +5700,28 @@
         <v>21</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F26" s="53" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G26" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H26" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I26" s="34" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="J26" s="35" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K26" s="36" t="s">
         <v>34</v>
@@ -5604,28 +5733,28 @@
         <v>22</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F27" s="32" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H27" s="34" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I27" s="34" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="J27" s="35" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K27" s="36" t="s">
         <v>34</v>
@@ -5633,107 +5762,267 @@
     </row>
     <row r="28" s="6" customFormat="1" ht="40.5" customHeight="1" spans="1:11">
       <c r="A28" s="55"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="36"/>
+      <c r="B28" s="49">
+        <v>23</v>
+      </c>
+      <c r="C28" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28" s="52" t="s">
+        <v>143</v>
+      </c>
+      <c r="F28" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="G28" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="J28" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="K28" s="36" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="29" s="4" customFormat="1" ht="52.5" customHeight="1" spans="1:11">
       <c r="A29" s="1"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="36"/>
+      <c r="B29" s="49">
+        <v>24</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="G29" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="I29" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="J29" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K29" s="36" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="30" s="4" customFormat="1" ht="52.5" customHeight="1" spans="1:11">
       <c r="A30" s="1"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="36"/>
+      <c r="B30" s="58">
+        <v>25</v>
+      </c>
+      <c r="C30" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" s="52" t="s">
+        <v>147</v>
+      </c>
+      <c r="F30" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="G30" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="I30" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="J30" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" s="36" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="31" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:11">
       <c r="A31" s="1"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="36"/>
+      <c r="B31" s="37">
+        <v>26</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="G31" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="I31" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="J31" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="K31" s="36" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="32" s="4" customFormat="1" ht="48.75" customHeight="1" spans="1:11">
       <c r="A32" s="1"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="38"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="59"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="36"/>
-    </row>
-    <row r="33" s="4" customFormat="1" ht="30" customHeight="1" spans="1:11">
+      <c r="B32" s="49">
+        <v>27</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="F32" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="G32" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="I32" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="J32" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="K32" s="36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" s="4" customFormat="1" ht="47" customHeight="1" spans="1:11">
       <c r="A33" s="1"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="59"/>
-      <c r="H33" s="59"/>
-      <c r="I33" s="59"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="36"/>
+      <c r="B33" s="37">
+        <v>28</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="F33" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="G33" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="H33" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="I33" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="J33" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="K33" s="36" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="34" s="4" customFormat="1" ht="48.75" customHeight="1" spans="1:11">
       <c r="A34" s="1"/>
-      <c r="B34" s="37"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="59"/>
-      <c r="I34" s="59"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="36"/>
+      <c r="B34" s="37">
+        <v>29</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="F34" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="G34" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="H34" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="J34" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="K34" s="36" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="35" s="4" customFormat="1" ht="37.5" customHeight="1" spans="1:11">
       <c r="A35" s="1"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
-      <c r="I35" s="59"/>
-      <c r="J35" s="35"/>
-      <c r="K35" s="36"/>
+      <c r="B35" s="30">
+        <v>30</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="G35" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="I35" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="J35" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="K35" s="36" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="36" s="4" customFormat="1" ht="50.25" customHeight="1" spans="1:11">
       <c r="A36" s="1"/>
@@ -5891,7 +6180,7 @@
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="71" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C49" s="72"/>
       <c r="D49" s="72"/>

--- a/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
+++ b/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="11055" tabRatio="486" activeTab="2"/>
+    <workbookView windowWidth="24000" windowHeight="11055" tabRatio="486" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="需求跟踪矩阵封面" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="170">
   <si>
     <t>密级：</t>
   </si>
@@ -503,6 +503,24 @@
     <t>新增8个需求对应的开发工作量</t>
   </si>
   <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>更改部分功能</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>v1.4</t>
+  </si>
+  <si>
+    <t>需减少1个冗余功能点</t>
+  </si>
+  <si>
+    <t>减少1个需求与相关设计</t>
+  </si>
+  <si>
     <t>SUM</t>
   </si>
   <si>
@@ -756,6 +774,9 @@
   </si>
   <si>
     <t>动作：点击触发数字人挥手动作</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>选择.vrma动作</t>
@@ -4592,19 +4613,45 @@
       <c r="B7" s="98">
         <v>5</v>
       </c>
-      <c r="C7" s="107"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="105"/>
-      <c r="N7" s="118"/>
-      <c r="O7" s="102"/>
+      <c r="C7" s="109" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="100" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="101" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="104" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="102" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="103">
+        <v>30</v>
+      </c>
+      <c r="I7" s="104">
+        <v>0</v>
+      </c>
+      <c r="J7" s="104">
+        <v>1</v>
+      </c>
+      <c r="K7" s="104">
+        <v>0</v>
+      </c>
+      <c r="L7" s="94">
+        <v>29</v>
+      </c>
+      <c r="M7" s="105">
+        <v>0.033</v>
+      </c>
+      <c r="N7" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" s="102" t="s">
+        <v>60</v>
+      </c>
       <c r="P7" s="106">
         <v>0.05</v>
       </c>
@@ -4896,7 +4943,7 @@
     </row>
     <row r="23" s="77" customFormat="1" ht="13.9" customHeight="1" spans="2:16">
       <c r="B23" s="141" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C23" s="142"/>
       <c r="D23" s="142"/>
@@ -4955,23 +5002,23 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:11">
       <c r="B1" s="12" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="13.9" customHeight="1" spans="1:11">
       <c r="A2" s="1"/>
       <c r="B2" s="13" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D2" s="14"/>
       <c r="E2" s="15" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G2" s="16"/>
       <c r="H2" s="16"/>
@@ -4985,51 +5032,51 @@
     <row r="4" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:11">
       <c r="A4" s="1"/>
       <c r="B4" s="20" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G4" s="23"/>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
       <c r="J4" s="22" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:11">
       <c r="A5" s="1"/>
       <c r="B5" s="25"/>
       <c r="C5" s="26" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="28" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J5" s="27"/>
       <c r="K5" s="29"/>
@@ -5040,28 +5087,28 @@
         <v>1</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J6" s="35" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K6" s="36" t="s">
         <v>34</v>
@@ -5073,28 +5120,28 @@
         <v>2</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J7" s="35" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K7" s="36" t="s">
         <v>34</v>
@@ -5106,28 +5153,28 @@
         <v>3</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J8" s="35" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K8" s="36" t="s">
         <v>34</v>
@@ -5139,28 +5186,28 @@
         <v>4</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E9" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="J9" s="35" t="s">
         <v>85</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="J9" s="35" t="s">
-        <v>79</v>
       </c>
       <c r="K9" s="36" t="s">
         <v>34</v>
@@ -5172,28 +5219,28 @@
         <v>5</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J10" s="35" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K10" s="36" t="s">
         <v>34</v>
@@ -5205,28 +5252,28 @@
         <v>6</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K11" s="36" t="s">
         <v>34</v>
@@ -5238,28 +5285,28 @@
         <v>7</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H12" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J12" s="35" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K12" s="36" t="s">
         <v>34</v>
@@ -5271,28 +5318,28 @@
         <v>8</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H13" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J13" s="35" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K13" s="36" t="s">
         <v>34</v>
@@ -5304,28 +5351,28 @@
         <v>9</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K14" s="36" t="s">
         <v>34</v>
@@ -5337,28 +5384,28 @@
         <v>10</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I15" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K15" s="36" t="s">
         <v>34</v>
@@ -5370,28 +5417,28 @@
         <v>11</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I16" s="34" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="J16" s="35" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K16" s="36" t="s">
         <v>34</v>
@@ -5403,25 +5450,25 @@
         <v>12</v>
       </c>
       <c r="C17" s="46" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E17" s="48" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I17" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J17" s="35" t="s">
         <v>34</v>
@@ -5436,25 +5483,25 @@
         <v>13</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F18" s="32" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I18" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J18" s="35" t="s">
         <v>34</v>
@@ -5469,28 +5516,28 @@
         <v>14</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E19" s="52" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I19" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J19" s="35" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K19" s="36" t="s">
         <v>34</v>
@@ -5502,25 +5549,25 @@
         <v>15</v>
       </c>
       <c r="C20" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20" s="34" t="s">
         <v>109</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="H20" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="I20" s="34" t="s">
-        <v>103</v>
       </c>
       <c r="J20" s="35" t="s">
         <v>34</v>
@@ -5535,28 +5582,28 @@
         <v>16</v>
       </c>
       <c r="C21" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="F21" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="H21" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="I21" s="34" t="s">
-        <v>103</v>
-      </c>
       <c r="J21" s="35" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K21" s="36" t="s">
         <v>34</v>
@@ -5568,25 +5615,25 @@
         <v>17</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I22" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J22" s="35" t="s">
         <v>34</v>
@@ -5601,28 +5648,28 @@
         <v>18</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I23" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J23" s="35" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K23" s="36" t="s">
         <v>34</v>
@@ -5634,28 +5681,28 @@
         <v>19</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F24" s="51" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H24" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I24" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J24" s="35" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K24" s="36" t="s">
         <v>34</v>
@@ -5667,28 +5714,28 @@
         <v>20</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H25" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I25" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J25" s="35" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K25" s="36" t="s">
         <v>34</v>
@@ -5700,28 +5747,28 @@
         <v>21</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F26" s="53" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G26" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H26" s="34" t="s">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="I26" s="34" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="J26" s="35" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K26" s="36" t="s">
         <v>34</v>
@@ -5733,28 +5780,28 @@
         <v>22</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F27" s="32" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H27" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I27" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J27" s="35" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K27" s="36" t="s">
         <v>34</v>
@@ -5766,28 +5813,28 @@
         <v>23</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E28" s="52" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G28" s="57" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H28" s="57" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I28" s="57" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J28" s="35" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K28" s="36" t="s">
         <v>34</v>
@@ -5799,28 +5846,28 @@
         <v>24</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G29" s="57" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H29" s="57" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I29" s="57" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J29" s="35" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K29" s="36" t="s">
         <v>34</v>
@@ -5832,25 +5879,25 @@
         <v>25</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E30" s="52" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F30" s="51" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="G30" s="57" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H30" s="57" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I30" s="57" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J30" s="35" t="s">
         <v>34</v>
@@ -5865,28 +5912,28 @@
         <v>26</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E31" s="52" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G31" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H31" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I31" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J31" s="35" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K31" s="36" t="s">
         <v>34</v>
@@ -5898,28 +5945,28 @@
         <v>27</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D32" s="39" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E32" s="40" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F32" s="53" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G32" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H32" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I32" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J32" s="35" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K32" s="36" t="s">
         <v>34</v>
@@ -5931,28 +5978,28 @@
         <v>28</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F33" s="39" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="G33" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H33" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I33" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J33" s="35" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K33" s="36" t="s">
         <v>34</v>
@@ -5964,28 +6011,28 @@
         <v>29</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D34" s="39" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F34" s="51" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="G34" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H34" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I34" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J34" s="35" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="K34" s="36" t="s">
         <v>34</v>
@@ -5997,28 +6044,28 @@
         <v>30</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F35" s="32" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G35" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H35" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I35" s="59" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J35" s="35" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K35" s="36" t="s">
         <v>34</v>
@@ -6180,7 +6227,7 @@
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="71" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C49" s="72"/>
       <c r="D49" s="72"/>

--- a/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
+++ b/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="11055" tabRatio="486" activeTab="1"/>
+    <workbookView windowWidth="24000" windowHeight="11055" tabRatio="486" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="需求跟踪矩阵封面" sheetId="1" r:id="rId1"/>
@@ -515,10 +515,10 @@
     <t>v1.4</t>
   </si>
   <si>
-    <t>需减少1个冗余功能点</t>
-  </si>
-  <si>
-    <t>减少1个需求与相关设计</t>
+    <t>减少1个冗余功能点</t>
+  </si>
+  <si>
+    <t>取消1个需求与相关设计</t>
   </si>
   <si>
     <t>SUM</t>
@@ -533,7 +533,18 @@
     <t>数字人交互系统（安心健康助手）</t>
   </si>
   <si>
-    <t>PM:安家谊</t>
+    <r>
+      <t>PM:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>组长</t>
+    </r>
   </si>
   <si>
     <t>担当:具体参与设计的成员名单</t>
@@ -2895,16 +2906,110 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>229235</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>86360</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>149225</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>55245</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>217805</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>17780</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>417195</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1440815" y="4103370"/>
+          <a:ext cx="10600690" cy="5777865"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>508635</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>123190</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1800225" y="733425"/>
+          <a:ext cx="7364730" cy="3923665"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>382270</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2921,8 +3026,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="875030" y="410210"/>
-          <a:ext cx="9675495" cy="5274945"/>
+          <a:off x="2786380" y="384810"/>
+          <a:ext cx="5991225" cy="5640705"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2930,7 +3035,6 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
-          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -2939,24 +3043,24 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>501650</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>39370</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>65405</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>96520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>155575</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>140970</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>309880</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>124460</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPr id="4" name="图片 3"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2969,8 +3073,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1147445" y="525145"/>
-          <a:ext cx="9986645" cy="5445125"/>
+          <a:off x="8460740" y="420370"/>
+          <a:ext cx="4765040" cy="6019165"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2978,7 +3082,6 @@
         <a:noFill/>
         <a:ln w="9525">
           <a:noFill/>
-          <a:prstDash val="solid"/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
@@ -6299,6 +6402,7 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6310,6 +6414,7 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
+++ b/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="169">
   <si>
     <t>密级：</t>
   </si>
@@ -534,6 +534,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>PM:</t>
     </r>
     <r>
@@ -674,9 +680,6 @@
   </si>
   <si>
     <t>未加载模型时静态显示占位图标与"数字人形象正在准备中"及说明文字，模型加载后隐藏</t>
-  </si>
-  <si>
-    <t>×</t>
   </si>
   <si>
     <t>能力标签</t>
@@ -2959,10 +2962,10 @@
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>123190</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>313055</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>122555</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2980,7 +2983,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1800225" y="733425"/>
-          <a:ext cx="7364730" cy="3923665"/>
+          <a:ext cx="9491345" cy="5056505"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3006,10 +3009,10 @@
       <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>382270</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>76835</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3027,7 +3030,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2786380" y="384810"/>
-          <a:ext cx="5991225" cy="5640705"/>
+          <a:ext cx="6331585" cy="5962015"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4615,7 +4618,7 @@
         <v>42</v>
       </c>
       <c r="P4" s="106">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="5" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
@@ -4662,7 +4665,7 @@
         <v>48</v>
       </c>
       <c r="P5" s="106">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" s="75" customFormat="1" ht="13" customHeight="1" spans="2:16">
@@ -4709,7 +4712,7 @@
         <v>54</v>
       </c>
       <c r="P6" s="117">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
@@ -5472,7 +5475,7 @@
         <v>84</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="J14" s="35" t="s">
         <v>99</v>
@@ -5493,22 +5496,22 @@
         <v>106</v>
       </c>
       <c r="E15" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="F15" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="G15" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" s="35" t="s">
         <v>111</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="I15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="J15" s="35" t="s">
-        <v>112</v>
       </c>
       <c r="K15" s="36" t="s">
         <v>34</v>
@@ -5526,11 +5529,11 @@
         <v>106</v>
       </c>
       <c r="E16" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="39" t="s">
-        <v>114</v>
-      </c>
       <c r="G16" s="34" t="s">
         <v>84</v>
       </c>
@@ -5538,10 +5541,10 @@
         <v>84</v>
       </c>
       <c r="I16" s="34" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="J16" s="35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K16" s="36" t="s">
         <v>34</v>
@@ -5553,16 +5556,16 @@
         <v>12</v>
       </c>
       <c r="C17" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="E17" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="48" t="s">
+      <c r="F17" s="47" t="s">
         <v>117</v>
-      </c>
-      <c r="F17" s="47" t="s">
-        <v>118</v>
       </c>
       <c r="G17" s="34" t="s">
         <v>84</v>
@@ -5586,16 +5589,16 @@
         <v>13</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D18" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="E18" s="33" t="s">
+      <c r="F18" s="32" t="s">
         <v>120</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>121</v>
       </c>
       <c r="G18" s="34" t="s">
         <v>84</v>
@@ -5619,16 +5622,16 @@
         <v>14</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D19" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="E19" s="52" t="s">
+      <c r="F19" s="51" t="s">
         <v>123</v>
-      </c>
-      <c r="F19" s="51" t="s">
-        <v>124</v>
       </c>
       <c r="G19" s="34" t="s">
         <v>84</v>
@@ -5652,17 +5655,17 @@
         <v>15</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D20" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="F20" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="F20" s="51" t="s">
-        <v>127</v>
-      </c>
       <c r="G20" s="34" t="s">
         <v>84</v>
       </c>
@@ -5670,7 +5673,7 @@
         <v>84</v>
       </c>
       <c r="I20" s="34" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="J20" s="35" t="s">
         <v>34</v>
@@ -5679,34 +5682,34 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" s="4" customFormat="1" ht="26.25" customHeight="1" spans="1:11">
+    <row r="21" s="4" customFormat="1" ht="47" customHeight="1" spans="1:11">
       <c r="A21" s="1"/>
       <c r="B21" s="41">
         <v>16</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D21" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="F21" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="F21" s="51" t="s">
+      <c r="G21" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="J21" s="35" t="s">
         <v>130</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="I21" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="J21" s="35" t="s">
-        <v>131</v>
       </c>
       <c r="K21" s="36" t="s">
         <v>34</v>
@@ -5718,16 +5721,16 @@
         <v>17</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E22" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="51" t="s">
         <v>132</v>
-      </c>
-      <c r="F22" s="51" t="s">
-        <v>133</v>
       </c>
       <c r="G22" s="34" t="s">
         <v>84</v>
@@ -5745,22 +5748,22 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" s="4" customFormat="1" ht="26.25" customHeight="1" spans="1:11">
+    <row r="23" s="4" customFormat="1" ht="31" customHeight="1" spans="1:11">
       <c r="A23" s="1"/>
       <c r="B23" s="49">
         <v>18</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E23" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23" s="51" t="s">
         <v>134</v>
-      </c>
-      <c r="F23" s="51" t="s">
-        <v>135</v>
       </c>
       <c r="G23" s="34" t="s">
         <v>84</v>
@@ -5784,16 +5787,16 @@
         <v>19</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D24" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="E24" s="40" t="s">
+      <c r="F24" s="51" t="s">
         <v>137</v>
-      </c>
-      <c r="F24" s="51" t="s">
-        <v>138</v>
       </c>
       <c r="G24" s="34" t="s">
         <v>84</v>
@@ -5817,16 +5820,16 @@
         <v>20</v>
       </c>
       <c r="C25" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="D25" s="39" t="s">
+      <c r="E25" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="E25" s="40" t="s">
+      <c r="F25" s="51" t="s">
         <v>141</v>
-      </c>
-      <c r="F25" s="51" t="s">
-        <v>142</v>
       </c>
       <c r="G25" s="34" t="s">
         <v>84</v>
@@ -5850,25 +5853,25 @@
         <v>21</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D26" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="E26" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="E26" s="44" t="s">
+      <c r="F26" s="53" t="s">
         <v>144</v>
       </c>
-      <c r="F26" s="53" t="s">
+      <c r="G26" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H26" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="G26" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H26" s="34" t="s">
-        <v>146</v>
-      </c>
       <c r="I26" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J26" s="35" t="s">
         <v>105</v>
@@ -5883,16 +5886,16 @@
         <v>22</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E27" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" s="32" t="s">
         <v>147</v>
-      </c>
-      <c r="F27" s="32" t="s">
-        <v>148</v>
       </c>
       <c r="G27" s="34" t="s">
         <v>84</v>
@@ -5919,13 +5922,13 @@
         <v>80</v>
       </c>
       <c r="D28" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="E28" s="52" t="s">
+      <c r="F28" s="51" t="s">
         <v>150</v>
-      </c>
-      <c r="F28" s="51" t="s">
-        <v>151</v>
       </c>
       <c r="G28" s="57" t="s">
         <v>84</v>
@@ -5952,13 +5955,13 @@
         <v>80</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E29" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" s="51" t="s">
         <v>152</v>
-      </c>
-      <c r="F29" s="51" t="s">
-        <v>153</v>
       </c>
       <c r="G29" s="57" t="s">
         <v>84</v>
@@ -5985,13 +5988,13 @@
         <v>80</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E30" s="52" t="s">
+        <v>153</v>
+      </c>
+      <c r="F30" s="51" t="s">
         <v>154</v>
-      </c>
-      <c r="F30" s="51" t="s">
-        <v>155</v>
       </c>
       <c r="G30" s="57" t="s">
         <v>84</v>
@@ -6021,10 +6024,10 @@
         <v>94</v>
       </c>
       <c r="E31" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="F31" s="51" t="s">
         <v>156</v>
-      </c>
-      <c r="F31" s="51" t="s">
-        <v>157</v>
       </c>
       <c r="G31" s="59" t="s">
         <v>84</v>
@@ -6054,10 +6057,10 @@
         <v>94</v>
       </c>
       <c r="E32" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="F32" s="53" t="s">
         <v>158</v>
-      </c>
-      <c r="F32" s="53" t="s">
-        <v>159</v>
       </c>
       <c r="G32" s="59" t="s">
         <v>84</v>
@@ -6081,16 +6084,16 @@
         <v>28</v>
       </c>
       <c r="C33" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="39" t="s">
-        <v>140</v>
-      </c>
       <c r="E33" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="F33" s="39" t="s">
         <v>160</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>161</v>
       </c>
       <c r="G33" s="59" t="s">
         <v>84</v>
@@ -6114,28 +6117,28 @@
         <v>29</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D34" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="E34" s="40" t="s">
         <v>162</v>
       </c>
-      <c r="E34" s="40" t="s">
+      <c r="F34" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="F34" s="51" t="s">
+      <c r="G34" s="59" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" s="59" t="s">
+        <v>84</v>
+      </c>
+      <c r="I34" s="59" t="s">
+        <v>84</v>
+      </c>
+      <c r="J34" s="35" t="s">
         <v>164</v>
-      </c>
-      <c r="G34" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="I34" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="J34" s="35" t="s">
-        <v>165</v>
       </c>
       <c r="K34" s="36" t="s">
         <v>34</v>
@@ -6147,17 +6150,17 @@
         <v>30</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D35" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="E35" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="E35" s="33" t="s">
+      <c r="F35" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="F35" s="32" t="s">
-        <v>168</v>
-      </c>
       <c r="G35" s="59" t="s">
         <v>84</v>
       </c>
@@ -6168,7 +6171,7 @@
         <v>84</v>
       </c>
       <c r="J35" s="35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K35" s="36" t="s">
         <v>34</v>
@@ -6330,7 +6333,7 @@
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C49" s="72"/>
       <c r="D49" s="72"/>

--- a/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
+++ b/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="11055" tabRatio="486" activeTab="2"/>
+    <workbookView windowWidth="24000" windowHeight="11055" tabRatio="486" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="需求跟踪矩阵封面" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="167">
   <si>
     <t>密级：</t>
   </si>
@@ -485,9 +485,6 @@
     <t>动作表情联调与单元测试</t>
   </si>
   <si>
-    <t>2026-09-10</t>
-  </si>
-  <si>
     <t>根据项目当前实现整体更新需求跟踪矩阵</t>
   </si>
   <si>
@@ -501,9 +498,6 @@
   </si>
   <si>
     <t>新增8个需求对应的开发工作量</t>
-  </si>
-  <si>
-    <t>2026-09-11</t>
   </si>
   <si>
     <t>更改部分功能</t>
@@ -2550,7 +2544,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4672,17 +4666,17 @@
       <c r="B6" s="108">
         <v>4</v>
       </c>
-      <c r="C6" s="109" t="s">
+      <c r="C6" s="109">
+        <v>46280</v>
+      </c>
+      <c r="D6" s="110" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="110" t="s">
+      <c r="E6" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="111" t="s">
+      <c r="F6" s="112" t="s">
         <v>51</v>
-      </c>
-      <c r="F6" s="112" t="s">
-        <v>52</v>
       </c>
       <c r="G6" s="113" t="s">
         <v>34</v>
@@ -4706,10 +4700,10 @@
         <v>0.5</v>
       </c>
       <c r="N6" s="113" t="s">
+        <v>52</v>
+      </c>
+      <c r="O6" s="113" t="s">
         <v>53</v>
-      </c>
-      <c r="O6" s="113" t="s">
-        <v>54</v>
       </c>
       <c r="P6" s="117">
         <v>0.2</v>
@@ -4719,17 +4713,17 @@
       <c r="B7" s="98">
         <v>5</v>
       </c>
-      <c r="C7" s="109" t="s">
+      <c r="C7" s="109">
+        <v>46283</v>
+      </c>
+      <c r="D7" s="100" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="100" t="s">
+      <c r="F7" s="104" t="s">
         <v>56</v>
-      </c>
-      <c r="E7" s="101" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="104" t="s">
-        <v>58</v>
       </c>
       <c r="G7" s="102" t="s">
         <v>34</v>
@@ -4753,10 +4747,10 @@
         <v>0.033</v>
       </c>
       <c r="N7" s="113" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O7" s="102" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P7" s="106">
         <v>0.05</v>
@@ -5049,7 +5043,7 @@
     </row>
     <row r="23" s="77" customFormat="1" ht="13.9" customHeight="1" spans="2:16">
       <c r="B23" s="141" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C23" s="142"/>
       <c r="D23" s="142"/>
@@ -5108,23 +5102,23 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:11">
       <c r="B1" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="13.9" customHeight="1" spans="1:11">
       <c r="A2" s="1"/>
       <c r="B2" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D2" s="14"/>
       <c r="E2" s="15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G2" s="16"/>
       <c r="H2" s="16"/>
@@ -5138,51 +5132,51 @@
     <row r="4" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:11">
       <c r="A4" s="1"/>
       <c r="B4" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="E4" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="F4" s="22" t="s">
         <v>69</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>71</v>
       </c>
       <c r="G4" s="23"/>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
       <c r="J4" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:11">
       <c r="A5" s="1"/>
       <c r="B5" s="25"/>
       <c r="C5" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>74</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>76</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="28" t="s">
         <v>77</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>79</v>
       </c>
       <c r="J5" s="27"/>
       <c r="K5" s="29"/>
@@ -5193,28 +5187,28 @@
         <v>1</v>
       </c>
       <c r="C6" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="F6" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6" s="32" t="s">
+      <c r="G6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="35" t="s">
         <v>83</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="J6" s="35" t="s">
-        <v>85</v>
       </c>
       <c r="K6" s="36" t="s">
         <v>34</v>
@@ -5226,28 +5220,28 @@
         <v>2</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J7" s="35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K7" s="36" t="s">
         <v>34</v>
@@ -5259,28 +5253,28 @@
         <v>3</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J8" s="35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K8" s="36" t="s">
         <v>34</v>
@@ -5292,28 +5286,28 @@
         <v>4</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D9" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>92</v>
-      </c>
       <c r="G9" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J9" s="35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K9" s="36" t="s">
         <v>34</v>
@@ -5325,28 +5319,28 @@
         <v>5</v>
       </c>
       <c r="C10" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="F10" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" s="43" t="s">
-        <v>96</v>
-      </c>
       <c r="G10" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J10" s="35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K10" s="36" t="s">
         <v>34</v>
@@ -5358,28 +5352,28 @@
         <v>6</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E11" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="35" t="s">
         <v>97</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11" s="35" t="s">
-        <v>99</v>
       </c>
       <c r="K11" s="36" t="s">
         <v>34</v>
@@ -5391,28 +5385,28 @@
         <v>7</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E12" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" s="35" t="s">
         <v>100</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="J12" s="35" t="s">
-        <v>102</v>
       </c>
       <c r="K12" s="36" t="s">
         <v>34</v>
@@ -5424,28 +5418,28 @@
         <v>8</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E13" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="35" t="s">
         <v>103</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="I13" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13" s="35" t="s">
-        <v>105</v>
       </c>
       <c r="K13" s="36" t="s">
         <v>34</v>
@@ -5457,28 +5451,28 @@
         <v>9</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D14" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="F14" s="39" t="s">
-        <v>108</v>
-      </c>
       <c r="G14" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K14" s="36" t="s">
         <v>34</v>
@@ -5490,28 +5484,28 @@
         <v>10</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E15" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" s="35" t="s">
         <v>109</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="I15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="J15" s="35" t="s">
-        <v>111</v>
       </c>
       <c r="K15" s="36" t="s">
         <v>34</v>
@@ -5523,28 +5517,28 @@
         <v>11</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I16" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J16" s="35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K16" s="36" t="s">
         <v>34</v>
@@ -5556,25 +5550,25 @@
         <v>12</v>
       </c>
       <c r="C17" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="F17" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="E17" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="F17" s="47" t="s">
-        <v>117</v>
-      </c>
       <c r="G17" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I17" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J17" s="35" t="s">
         <v>34</v>
@@ -5589,25 +5583,25 @@
         <v>13</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D18" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="E18" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>120</v>
-      </c>
       <c r="G18" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I18" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J18" s="35" t="s">
         <v>34</v>
@@ -5622,28 +5616,28 @@
         <v>14</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D19" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="E19" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="F19" s="51" t="s">
-        <v>123</v>
-      </c>
       <c r="G19" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I19" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J19" s="35" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K19" s="36" t="s">
         <v>34</v>
@@ -5655,25 +5649,25 @@
         <v>15</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D20" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="E20" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>126</v>
-      </c>
       <c r="G20" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I20" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J20" s="35" t="s">
         <v>34</v>
@@ -5688,28 +5682,28 @@
         <v>16</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D21" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="G21" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J21" s="35" t="s">
         <v>128</v>
-      </c>
-      <c r="F21" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="I21" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="J21" s="35" t="s">
-        <v>130</v>
       </c>
       <c r="K21" s="36" t="s">
         <v>34</v>
@@ -5721,25 +5715,25 @@
         <v>17</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I22" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J22" s="35" t="s">
         <v>34</v>
@@ -5754,28 +5748,28 @@
         <v>18</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I23" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J23" s="35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K23" s="36" t="s">
         <v>34</v>
@@ -5787,28 +5781,28 @@
         <v>19</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D24" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="E24" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="F24" s="51" t="s">
-        <v>137</v>
-      </c>
       <c r="G24" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H24" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I24" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J24" s="35" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K24" s="36" t="s">
         <v>34</v>
@@ -5820,28 +5814,28 @@
         <v>20</v>
       </c>
       <c r="C25" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="D25" s="39" t="s">
+      <c r="F25" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="E25" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="F25" s="51" t="s">
-        <v>141</v>
-      </c>
       <c r="G25" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H25" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I25" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J25" s="35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K25" s="36" t="s">
         <v>34</v>
@@ -5853,28 +5847,28 @@
         <v>21</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D26" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E26" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="F26" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="E26" s="44" t="s">
+      <c r="G26" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="F26" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H26" s="34" t="s">
-        <v>145</v>
-      </c>
       <c r="I26" s="34" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J26" s="35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K26" s="36" t="s">
         <v>34</v>
@@ -5886,28 +5880,28 @@
         <v>22</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F27" s="32" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H27" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I27" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J27" s="35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K27" s="36" t="s">
         <v>34</v>
@@ -5919,28 +5913,28 @@
         <v>23</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D28" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" s="52" t="s">
+        <v>147</v>
+      </c>
+      <c r="F28" s="51" t="s">
         <v>148</v>
       </c>
-      <c r="E28" s="52" t="s">
-        <v>149</v>
-      </c>
-      <c r="F28" s="51" t="s">
-        <v>150</v>
-      </c>
       <c r="G28" s="57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H28" s="57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I28" s="57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J28" s="35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K28" s="36" t="s">
         <v>34</v>
@@ -5952,28 +5946,28 @@
         <v>24</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G29" s="57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H29" s="57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I29" s="57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J29" s="35" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K29" s="36" t="s">
         <v>34</v>
@@ -5985,25 +5979,25 @@
         <v>25</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E30" s="52" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F30" s="51" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G30" s="57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H30" s="57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I30" s="57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J30" s="35" t="s">
         <v>34</v>
@@ -6018,28 +6012,28 @@
         <v>26</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E31" s="52" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G31" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H31" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I31" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J31" s="35" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K31" s="36" t="s">
         <v>34</v>
@@ -6051,28 +6045,28 @@
         <v>27</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D32" s="39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E32" s="40" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F32" s="53" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G32" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H32" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I32" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J32" s="35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K32" s="36" t="s">
         <v>34</v>
@@ -6084,28 +6078,28 @@
         <v>28</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F33" s="39" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G33" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H33" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I33" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J33" s="35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K33" s="36" t="s">
         <v>34</v>
@@ -6117,28 +6111,28 @@
         <v>29</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D34" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="F34" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="E34" s="40" t="s">
+      <c r="G34" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="H34" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="I34" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="J34" s="35" t="s">
         <v>162</v>
-      </c>
-      <c r="F34" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="G34" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="I34" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="J34" s="35" t="s">
-        <v>164</v>
       </c>
       <c r="K34" s="36" t="s">
         <v>34</v>
@@ -6150,28 +6144,28 @@
         <v>30</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D35" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="F35" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="E35" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="F35" s="32" t="s">
-        <v>167</v>
-      </c>
       <c r="G35" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H35" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I35" s="59" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J35" s="35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K35" s="36" t="s">
         <v>34</v>
@@ -6333,7 +6327,7 @@
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C49" s="72"/>
       <c r="D49" s="72"/>

--- a/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
+++ b/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="240">
   <si>
     <t>密级：</t>
   </si>
@@ -513,6 +513,21 @@
   </si>
   <si>
     <t>取消1个需求与相关设计</t>
+  </si>
+  <si>
+    <t>补齐数据库业务及新增能力追踪；修订过时描述（待评审）</t>
+  </si>
+  <si>
+    <t>31-51</t>
+  </si>
+  <si>
+    <t>v1.5</t>
+  </si>
+  <si>
+    <t>需求规模由21个增至50个，总规模扩大</t>
+  </si>
+  <si>
+    <t>新增29个需求对应的开发工作量</t>
   </si>
   <si>
     <t>SUM</t>
@@ -625,7 +640,7 @@
     <t>服务状态指示</t>
   </si>
   <si>
-    <t>动态显示后端服务运行状态；通过健康检查接口检测，正常时显示绿色状态点</t>
+    <t>通过/api/health检测后端服务运行状态；接口同时报告数据库启用、后端类型及可用性。模型和语音配置状态不等同于在线服务已验证，不返回数据库路径、账户、密码或模型密钥</t>
   </si>
   <si>
     <t>数字人舞台</t>
@@ -643,7 +658,7 @@
     <t>口型同步</t>
   </si>
   <si>
-    <t>动态表现：播报语音时按音频能量驱动嘴型张合，形成说话口型</t>
+    <t>播报时优先使用Rhubarb口型时间轴并结合音频能量驱动嘴型；时间轴缺失时采用音量驱动的元音轮换；浏览器语音播报时使用近似口型，播报结束或失败后复位</t>
   </si>
   <si>
     <t>赵燕凯</t>
@@ -661,7 +676,7 @@
     <t>肢体动作</t>
   </si>
   <si>
-    <t>动态表现：挥手动作右臂抬起摆动后复位；支持播放.vrma动作文件（关键词触发一次/手动循环）；动作可完整显示表情（眨眼/口型/下巴），通过表情独占名单FULL_EXPRESSION_ACTIONS配置</t>
+    <t>根据回复动作名播放对应场景的.vrma动作，手动加载支持循环播放；同一场景存在多个动作版本时随机选择，并避免连续重复。动作缺失不影响文字对话，动作与口型、表情及待机协调。</t>
   </si>
   <si>
     <t>魏鑫鸿</t>
@@ -727,7 +742,7 @@
     <t>交互状态提示</t>
   </si>
   <si>
-    <t>动态显示交互引导文字（如"可以按住下方按钮说话，也可以打字"）</t>
+    <t>动态显示可输入、正在聆听、正在处理及正在播报等交互提示；语音入口采用点击开始方式，不要求按住按钮；语音不可用时提示使用文字输入</t>
   </si>
   <si>
     <t>输入区</t>
@@ -736,7 +751,7 @@
     <t>语音对话按钮</t>
   </si>
   <si>
-    <t>显示"开始语音对话"按钮；动作：点击后调用浏览器语音识别接收语音并作为输入发送，不支持时降级为文字输入</t>
+    <t>显示“开始说话”语音入口，点击后调用浏览器语音识别，将识别结果作为对话输入；不要求持续按住。不支持识别或无法获取麦克风权限时给出提示，并保留文字输入能力</t>
   </si>
   <si>
     <t>安家谊、赵燕凯</t>
@@ -760,7 +775,7 @@
     <t>语音合成播报</t>
   </si>
   <si>
-    <t>动作：将后端返回的分句音频依次解码播放，逐句顺序播报并驱动口型</t>
+    <t>网页先通过/api/chat取得并展示文字、动作与分句信息，再逐句请求/api/tts并按顺序播放；某句在线音频生成、解码或播放失败时尝试浏览器补播该句，避免跳句、重复或错序</t>
   </si>
   <si>
     <t>演示设置</t>
@@ -799,7 +814,7 @@
     <t>减少动态按钮</t>
   </si>
   <si>
-    <t>动作：点击切换"减少动态"模式，暂停数字人待机、动作与视线微动，再次点击恢复；按钮以aria-pressed标注状态</t>
+    <t>点击切换“减少动态”模式，暂停数字人待机、场景动作、视线微动及环境动效，再次点击恢复；按钮以aria-pressed标注状态。后台标签页暂停环境更新，减少不必要的动画开销</t>
   </si>
   <si>
     <t>放大文字按钮</t>
@@ -851,6 +866,210 @@
   </si>
   <si>
     <t>动作：点击底部"问问健康""查看提醒""预约服务"按钮，一键发起对应服务流程，无需打字</t>
+  </si>
+  <si>
+    <t>数据服务</t>
+  </si>
+  <si>
+    <t>数据库接入</t>
+  </si>
+  <si>
+    <t>数据库开关与双后端适配</t>
+  </si>
+  <si>
+    <t>支持通过服务端配置启用或关闭数据库，并选择SQLite或MySQL后端；默认关闭。关闭后使用原有规则流程，不访问数据库；MySQL需手工准备表结构和虚构数据，不自动初始化外部数据库</t>
+  </si>
+  <si>
+    <t>演示数据维护</t>
+  </si>
+  <si>
+    <t>种子库与运行副本隔离</t>
+  </si>
+  <si>
+    <t>SQLite首次使用时将种子库复制到独立运行文件，默认位于output目录；预约和预警修改只写运行副本，不覆盖种子库。支持停服后删除运行副本，以重新初始化演示数据</t>
+  </si>
+  <si>
+    <t>排班数据维护</t>
+  </si>
+  <si>
+    <t>未来14天号源补充</t>
+  </si>
+  <si>
+    <t>SQLite根据科室每周排班模板，按中国时区补充从当天起共14天的具体日期号源；已有排班不重复插入，历史日期不改写。MySQL只读取预先准备的schedule数据，不自动补号源</t>
+  </si>
+  <si>
+    <t>魏鑫鸿、路昆</t>
+  </si>
+  <si>
+    <t>演示数据边界</t>
+  </si>
+  <si>
+    <t>固定演示用户范围</t>
+  </si>
+  <si>
+    <t>个人健康记录、预警及预约仅面向固定虚构用户demo-001；服务端使用固定用户标识访问个人演示数据，不将前端传入标识作为真实身份认证依据。当前不提供注册、登录或真实患者档案</t>
+  </si>
+  <si>
+    <t>健康服务</t>
+  </si>
+  <si>
+    <t>科室咨询</t>
+  </si>
+  <si>
+    <t>科室资料查询</t>
+  </si>
+  <si>
+    <t>根据用户对科室名称、位置、服务范围或开放时间的询问，从department表读取已启用科室信息；返回对应资料或科室列表，支持继续进入预约流程，不将演示位置描述为真实医院导诊信息</t>
+  </si>
+  <si>
+    <t>服务咨询</t>
+  </si>
+  <si>
+    <t>服务说明查询</t>
+  </si>
+  <si>
+    <t>根据“有哪些服务”等咨询，从service_info表读取服务标题和说明并生成回复；可提供预约、预警及健康记录快捷入口。没有服务资料时明确提示暂无信息，不编造已开通服务</t>
+  </si>
+  <si>
+    <t>健康记录</t>
+  </si>
+  <si>
+    <t>个人演示健康记录查询</t>
+  </si>
+  <si>
+    <t>支持查询固定演示用户的健康记录、血压记录及血糖记录，按记录时间倒序展示近期记录和日期；无匹配数据时提示暂无记录。回复说明数据为虚构演示内容，不能用于诊断</t>
+  </si>
+  <si>
+    <t>健康预警</t>
+  </si>
+  <si>
+    <t>待处理演示预警查询</t>
+  </si>
+  <si>
+    <t>读取固定演示用户的近期预警，展示其中一条待处理预警的内容与日期，并提供“我已确认”“联系家人”“稍后提醒”选项；没有待处理预警或没有数据时返回对应提示</t>
+  </si>
+  <si>
+    <t>预警选择持久化</t>
+  </si>
+  <si>
+    <t>将用户对待处理预警的选择保存为confirmed、family_requested或later，并记录处理时间；重复操作不覆盖已经处理的状态。“联系家人”和“稍后提醒”仅记录选择，不发送消息、不创建定时通知</t>
+  </si>
+  <si>
+    <t>预约服务</t>
+  </si>
+  <si>
+    <t>号源查询</t>
+  </si>
+  <si>
+    <t>具体日期时段与余号展示</t>
+  </si>
+  <si>
+    <t>按科室查询从当天起共14天的排班，展示具体日期、时段及余号；只提供开放且有剩余名额的号源，支持“更多时段”分页。日期或时段不明确时要求用户进一步选择。</t>
+  </si>
+  <si>
+    <t>预约办理</t>
+  </si>
+  <si>
+    <t>分步确认与预约落库</t>
+  </si>
+  <si>
+    <t>按选择科室、选择具体时段、最终确认的步骤办理模拟预约，仅在最终确认成功后写入appointment并返回演示序号；确认前可重新选择或取消当前流程。取消当前流程不等同于撤销已落库预约</t>
+  </si>
+  <si>
+    <t>提交控制</t>
+  </si>
+  <si>
+    <t>预约重复提交防护</t>
+  </si>
+  <si>
+    <t>使用booking_token唯一确认令牌识别重复提交；同一令牌重复确认时返回原预约结果，不新增记录、不重复占用名额。令牌格式不合法或预约信息失效时，引导重新选择</t>
+  </si>
+  <si>
+    <t>一致性控制</t>
+  </si>
+  <si>
+    <t>容量复核与并发事务</t>
+  </si>
+  <si>
+    <t>最终确认时在事务中重新检查排班日期、开放状态及剩余容量；名额已满或排班失效时禁止写入并要求重选。SQLite使用写事务，MySQL锁定目标排班行，避免并发重复占用最后一个名额</t>
+  </si>
+  <si>
+    <t>预约记录</t>
+  </si>
+  <si>
+    <t>已确认演示预约查询</t>
+  </si>
+  <si>
+    <t>支持通过“我的预约”等指令读取固定演示用户近期已确认预约，显示日期、科室、时段和演示序号；没有记录时明确提示。预约序号和前方人数仅表示模拟预约顺序，不代表现场叫号或候诊时长</t>
+  </si>
+  <si>
+    <t>异常与安全</t>
+  </si>
+  <si>
+    <t>数据库异常和缺失数据处理</t>
+  </si>
+  <si>
+    <t>连接或执行失败时提示相关数据服务暂不可用，不返回预约成功或预警已处理，不泄露路径和连接凭据；保留未完成流程以便重试。查询无记录时说明暂无数据，不生成虚构结果</t>
+  </si>
+  <si>
+    <t>场景与氛围</t>
+  </si>
+  <si>
+    <t>三维医院场景切换</t>
+  </si>
+  <si>
+    <t>支持门诊大厅、温馨候诊区和智慧导诊三类三维医院场景，人物与环境共享空间、光照及深度关系；切换时保留人物、对话和预约步骤。按需加载场景，防止旧加载结果覆盖新选择，失败时提供回退与重试</t>
+  </si>
+  <si>
+    <t>安家谊、赵燕凯、魏鑫鸿</t>
+  </si>
+  <si>
+    <t>原图与三维场景对照</t>
+  </si>
+  <si>
+    <t>提供“查看原图场景／查看3D场景”切换，用于比较同一医院场景的原图与实时三维表现；三维模式限制旋转和缩放范围且不支持平移，避免破坏构图。不要求三维画面逐像素还原原图</t>
+  </si>
+  <si>
+    <t>视角控制</t>
+  </si>
+  <si>
+    <t>恢复全身视角</t>
+  </si>
+  <si>
+    <t>提供“恢复全身”操作，根据当前人物尺寸重新适配正面全身视角；在旋转、缩放或更换人物后，可恢复默认观察位置，使人物完整进入舞台画面</t>
+  </si>
+  <si>
+    <t>默认人物偏好与恢复</t>
+  </si>
+  <si>
+    <t>支持在浏览器保存用户明确设置的默认人物偏好，并在再次访问时优先使用；提供“恢复系统默认”操作。当前系统默认人物为schoolBoy，恢复默认后刷新页面应使用校服男生</t>
+  </si>
+  <si>
+    <t>对话服务</t>
+  </si>
+  <si>
+    <t>可选模型接入</t>
+  </si>
+  <si>
+    <t>外部模型与规则回退</t>
+  </si>
+  <si>
+    <t>支持服务端配置OpenAI兼容Chat Completions或Anthropic Messages协议，用于普通单轮聊天；健康规则、预约和预警流程优先，模型不得更改流程状态或执行操作。配置缺失、超时或输出不合法时回退本地规则</t>
+  </si>
+  <si>
+    <t>语音服务</t>
+  </si>
+  <si>
+    <t>语音源配置</t>
+  </si>
+  <si>
+    <t>可选TTS协议与逐级回退</t>
+  </si>
+  <si>
+    <t>支持Edge TTS及OpenAI兼容语音服务，语音配置与聊天模型配置相互独立；外部配置不完整、超时或音频无效时回退Edge，仍失败时交由浏览器播报，均不可用时保留文字提示</t>
+  </si>
+  <si>
+    <t>待确认</t>
   </si>
   <si>
     <t>○：完成（通过评审或测试）   △：进行中   ×：未着手   N/A：不适用（没有此项活动）</t>
@@ -860,7 +1079,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="12">
+  <numFmts count="13">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -873,6 +1092,7 @@
     <numFmt numFmtId="181" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="182" formatCode="0.0%"/>
     <numFmt numFmtId="183" formatCode="[$-409]yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="184" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -1239,7 +1459,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1248,7 +1468,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="44"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2093,7 +2325,7 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="38">
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="38">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
@@ -2117,16 +2349,16 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="41">
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="41">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="7" borderId="42">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="42">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="7" borderId="41">
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="41">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="8" borderId="43">
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="43">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="44">
@@ -2135,85 +2367,85 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="45">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="44" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="28" fillId="0" borderId="0"/>
@@ -2250,7 +2482,7 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2264,6 +2496,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2295,29 +2529,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -2395,7 +2629,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2405,34 +2641,54 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="17" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2440,50 +2696,50 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="60" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="26" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="27" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="27" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="28" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="181" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2511,55 +2767,55 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="183" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="182" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="15" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2568,13 +2824,35 @@
     <xf numFmtId="182" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2595,25 +2873,28 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="17" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2625,34 +2906,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="15" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2679,7 +2960,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2692,7 +2973,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2710,19 +2991,19 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="22" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
@@ -4057,361 +4338,361 @@
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="8.75221238938053" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="9.87610619469027" style="147" customWidth="1"/>
-    <col min="2" max="2" width="10.3716814159292" style="147" customWidth="1"/>
-    <col min="3" max="3" width="9.87610619469027" style="147" customWidth="1"/>
-    <col min="4" max="4" width="8.75221238938053" style="147" customWidth="1"/>
-    <col min="5" max="5" width="10" style="147" customWidth="1"/>
-    <col min="6" max="6" width="9.75221238938053" style="147" customWidth="1"/>
-    <col min="7" max="7" width="9.50442477876106" style="147" customWidth="1"/>
-    <col min="8" max="8" width="16.7522123893805" style="147" customWidth="1"/>
-    <col min="9" max="16384" width="8.75221238938053" style="147" customWidth="1"/>
+    <col min="1" max="1" width="9.87610619469027" style="166" customWidth="1"/>
+    <col min="2" max="2" width="10.3716814159292" style="166" customWidth="1"/>
+    <col min="3" max="3" width="9.87610619469027" style="166" customWidth="1"/>
+    <col min="4" max="4" width="8.75221238938053" style="166" customWidth="1"/>
+    <col min="5" max="5" width="10" style="166" customWidth="1"/>
+    <col min="6" max="6" width="9.75221238938053" style="166" customWidth="1"/>
+    <col min="7" max="7" width="9.50442477876106" style="166" customWidth="1"/>
+    <col min="8" max="8" width="16.7522123893805" style="166" customWidth="1"/>
+    <col min="9" max="16384" width="8.75221238938053" style="166" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.75" customHeight="1" spans="1:8">
-      <c r="A1" s="148"/>
+      <c r="A1" s="167"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="148"/>
-    </row>
-    <row r="3" s="146" customFormat="1" ht="24" customHeight="1" spans="1:8">
-      <c r="A3" s="149" t="s">
+      <c r="A2" s="167"/>
+    </row>
+    <row r="3" s="165" customFormat="1" ht="24" customHeight="1" spans="1:8">
+      <c r="A3" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="150" t="s">
+      <c r="B3" s="169" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="151"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="151"/>
-      <c r="F3" s="151"/>
-      <c r="G3" s="151"/>
-      <c r="H3" s="152"/>
-    </row>
-    <row r="4" s="146" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
-      <c r="A4" s="153"/>
-      <c r="H4" s="154" t="s">
+      <c r="C3" s="170"/>
+      <c r="D3" s="170"/>
+      <c r="E3" s="170"/>
+      <c r="F3" s="170"/>
+      <c r="G3" s="170"/>
+      <c r="H3" s="171"/>
+    </row>
+    <row r="4" s="165" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
+      <c r="A4" s="172"/>
+      <c r="H4" s="173" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="146" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
-      <c r="A5" s="153" t="s">
+    <row r="5" s="165" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
+      <c r="A5" s="172" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="151"/>
-      <c r="G5" s="155" t="s">
+      <c r="F5" s="170"/>
+      <c r="G5" s="174" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A6" s="156"/>
-      <c r="B6" s="157"/>
-      <c r="C6" s="157"/>
-      <c r="D6" s="157"/>
-      <c r="E6" s="157"/>
-    </row>
-    <row r="7" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A7" s="158"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-    </row>
-    <row r="8" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A8" s="158"/>
-      <c r="B8" s="152"/>
-      <c r="C8" s="152"/>
-      <c r="D8" s="152"/>
-      <c r="E8" s="152"/>
-      <c r="F8" s="152"/>
-      <c r="G8" s="152"/>
-      <c r="H8" s="152"/>
-    </row>
-    <row r="9" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A9" s="158"/>
-      <c r="B9" s="152"/>
-      <c r="C9" s="152"/>
-      <c r="D9" s="152"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="152"/>
-      <c r="G9" s="152"/>
-      <c r="H9" s="152"/>
-    </row>
-    <row r="10" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A10" s="158"/>
-      <c r="B10" s="152"/>
-      <c r="C10" s="152"/>
-      <c r="D10" s="152"/>
-      <c r="E10" s="152"/>
-      <c r="F10" s="152"/>
-      <c r="G10" s="152"/>
-      <c r="H10" s="152"/>
-    </row>
-    <row r="11" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A11" s="158"/>
-      <c r="B11" s="152"/>
-      <c r="C11" s="152"/>
-      <c r="D11" s="152"/>
-      <c r="E11" s="152"/>
-      <c r="F11" s="152"/>
-      <c r="G11" s="152"/>
-      <c r="H11" s="152"/>
-    </row>
-    <row r="12" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A12" s="158"/>
-      <c r="B12" s="152"/>
-      <c r="C12" s="152"/>
-      <c r="D12" s="152"/>
-      <c r="E12" s="152"/>
-      <c r="F12" s="152"/>
-      <c r="G12" s="152"/>
-      <c r="H12" s="152"/>
-    </row>
-    <row r="13" s="146" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
-      <c r="A13" s="159" t="s">
+      <c r="A6" s="175"/>
+      <c r="B6" s="176"/>
+      <c r="C6" s="176"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="176"/>
+    </row>
+    <row r="7" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A7" s="177"/>
+      <c r="B7" s="171"/>
+      <c r="C7" s="171"/>
+      <c r="D7" s="171"/>
+      <c r="E7" s="171"/>
+      <c r="F7" s="171"/>
+      <c r="G7" s="171"/>
+      <c r="H7" s="171"/>
+    </row>
+    <row r="8" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A8" s="177"/>
+      <c r="B8" s="171"/>
+      <c r="C8" s="171"/>
+      <c r="D8" s="171"/>
+      <c r="E8" s="171"/>
+      <c r="F8" s="171"/>
+      <c r="G8" s="171"/>
+      <c r="H8" s="171"/>
+    </row>
+    <row r="9" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A9" s="177"/>
+      <c r="B9" s="171"/>
+      <c r="C9" s="171"/>
+      <c r="D9" s="171"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="171"/>
+      <c r="G9" s="171"/>
+      <c r="H9" s="171"/>
+    </row>
+    <row r="10" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A10" s="177"/>
+      <c r="B10" s="171"/>
+      <c r="C10" s="171"/>
+      <c r="D10" s="171"/>
+      <c r="E10" s="171"/>
+      <c r="F10" s="171"/>
+      <c r="G10" s="171"/>
+      <c r="H10" s="171"/>
+    </row>
+    <row r="11" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A11" s="177"/>
+      <c r="B11" s="171"/>
+      <c r="C11" s="171"/>
+      <c r="D11" s="171"/>
+      <c r="E11" s="171"/>
+      <c r="F11" s="171"/>
+      <c r="G11" s="171"/>
+      <c r="H11" s="171"/>
+    </row>
+    <row r="12" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A12" s="177"/>
+      <c r="B12" s="171"/>
+      <c r="C12" s="171"/>
+      <c r="D12" s="171"/>
+      <c r="E12" s="171"/>
+      <c r="F12" s="171"/>
+      <c r="G12" s="171"/>
+      <c r="H12" s="171"/>
+    </row>
+    <row r="13" s="165" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
+      <c r="A13" s="178" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A14" s="158"/>
-      <c r="B14" s="160"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
-      <c r="E14" s="152"/>
-      <c r="F14" s="152"/>
-      <c r="G14" s="152"/>
-      <c r="H14" s="152"/>
-    </row>
-    <row r="15" s="146" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
-      <c r="A15" s="161" t="s">
+    <row r="14" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A14" s="177"/>
+      <c r="B14" s="179"/>
+      <c r="C14" s="171"/>
+      <c r="D14" s="171"/>
+      <c r="E14" s="171"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="171"/>
+    </row>
+    <row r="15" s="165" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
+      <c r="A15" s="180" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A16" s="158"/>
-      <c r="B16" s="152"/>
-      <c r="C16" s="152"/>
-      <c r="D16" s="152"/>
-      <c r="E16" s="152"/>
-      <c r="F16" s="152"/>
-      <c r="G16" s="152"/>
-      <c r="H16" s="152"/>
-    </row>
-    <row r="17" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A17" s="158"/>
-      <c r="B17" s="152"/>
-      <c r="C17" s="152"/>
-      <c r="D17" s="152"/>
-      <c r="E17" s="152"/>
-      <c r="F17" s="152"/>
-      <c r="G17" s="152"/>
-      <c r="H17" s="152"/>
-    </row>
-    <row r="18" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A18" s="158"/>
-      <c r="B18" s="152"/>
-      <c r="C18" s="152"/>
-      <c r="D18" s="152"/>
-      <c r="E18" s="152"/>
-      <c r="F18" s="152"/>
-      <c r="G18" s="152"/>
-      <c r="H18" s="152"/>
-    </row>
-    <row r="19" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A19" s="158"/>
-      <c r="B19" s="152"/>
-      <c r="C19" s="152"/>
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="152"/>
-      <c r="G19" s="152"/>
-      <c r="H19" s="152"/>
-    </row>
-    <row r="20" s="146" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A20" s="162" t="s">
+    <row r="16" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A16" s="177"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="171"/>
+      <c r="D16" s="171"/>
+      <c r="E16" s="171"/>
+      <c r="F16" s="171"/>
+      <c r="G16" s="171"/>
+      <c r="H16" s="171"/>
+    </row>
+    <row r="17" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A17" s="177"/>
+      <c r="B17" s="171"/>
+      <c r="C17" s="171"/>
+      <c r="D17" s="171"/>
+      <c r="E17" s="171"/>
+      <c r="F17" s="171"/>
+      <c r="G17" s="171"/>
+      <c r="H17" s="171"/>
+    </row>
+    <row r="18" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A18" s="177"/>
+      <c r="B18" s="171"/>
+      <c r="C18" s="171"/>
+      <c r="D18" s="171"/>
+      <c r="E18" s="171"/>
+      <c r="F18" s="171"/>
+      <c r="G18" s="171"/>
+      <c r="H18" s="171"/>
+    </row>
+    <row r="19" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A19" s="177"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="171"/>
+      <c r="D19" s="171"/>
+      <c r="E19" s="171"/>
+      <c r="F19" s="171"/>
+      <c r="G19" s="171"/>
+      <c r="H19" s="171"/>
+    </row>
+    <row r="20" s="165" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
+      <c r="A20" s="181" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A21" s="158"/>
-      <c r="B21" s="152"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="152"/>
-    </row>
-    <row r="22" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A22" s="158"/>
-      <c r="B22" s="152"/>
-      <c r="C22" s="152"/>
-      <c r="D22" s="152"/>
-      <c r="E22" s="152"/>
-      <c r="F22" s="152"/>
-      <c r="G22" s="152"/>
-      <c r="H22" s="152"/>
-    </row>
-    <row r="23" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A23" s="158"/>
-      <c r="B23" s="152"/>
-      <c r="C23" s="152"/>
-      <c r="D23" s="152"/>
-      <c r="E23" s="152"/>
-      <c r="F23" s="152"/>
-      <c r="G23" s="152"/>
-      <c r="H23" s="152"/>
-    </row>
-    <row r="24" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A24" s="158"/>
-      <c r="B24" s="152"/>
-      <c r="C24" s="152"/>
-      <c r="D24" s="152"/>
-      <c r="E24" s="152"/>
-      <c r="F24" s="152"/>
-      <c r="G24" s="152"/>
-      <c r="H24" s="152"/>
-    </row>
-    <row r="25" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A25" s="158"/>
-      <c r="B25" s="152"/>
-      <c r="C25" s="152"/>
-      <c r="D25" s="152"/>
-      <c r="E25" s="152"/>
-      <c r="F25" s="152"/>
-      <c r="G25" s="152"/>
-      <c r="H25" s="152"/>
-    </row>
-    <row r="26" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A26" s="158"/>
-      <c r="B26" s="152"/>
-      <c r="C26" s="152"/>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="152"/>
-      <c r="G26" s="152"/>
-      <c r="H26" s="152"/>
-    </row>
-    <row r="27" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A27" s="158"/>
-      <c r="B27" s="152"/>
-      <c r="C27" s="152"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
-      <c r="H27" s="152"/>
-    </row>
-    <row r="28" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A28" s="158"/>
-      <c r="B28" s="152"/>
-      <c r="C28" s="152"/>
-      <c r="D28" s="152"/>
-      <c r="E28" s="152"/>
-      <c r="F28" s="152"/>
-      <c r="G28" s="152"/>
-      <c r="H28" s="152"/>
-    </row>
-    <row r="29" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A29" s="158"/>
-      <c r="B29" s="152"/>
-      <c r="C29" s="152"/>
-      <c r="D29" s="152"/>
-      <c r="E29" s="152"/>
-      <c r="F29" s="152"/>
-      <c r="G29" s="152"/>
-      <c r="H29" s="152"/>
-    </row>
-    <row r="30" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A30" s="158"/>
-      <c r="B30" s="152"/>
-      <c r="C30" s="152"/>
-      <c r="D30" s="152"/>
-      <c r="E30" s="152"/>
-      <c r="F30" s="152"/>
-      <c r="G30" s="152"/>
-      <c r="H30" s="152"/>
-    </row>
-    <row r="31" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A31" s="158"/>
-      <c r="B31" s="152"/>
-      <c r="C31" s="152"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="152"/>
-      <c r="G31" s="152"/>
-      <c r="H31" s="152"/>
-    </row>
-    <row r="32" s="146" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A32" s="163"/>
-    </row>
-    <row r="33" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A33" s="158"/>
-      <c r="B33" s="152"/>
-      <c r="C33" s="152"/>
-      <c r="D33" s="152"/>
-      <c r="E33" s="152"/>
-      <c r="F33" s="152"/>
-      <c r="G33" s="152"/>
-      <c r="H33" s="152"/>
-    </row>
-    <row r="34" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A34" s="158"/>
-      <c r="B34" s="152"/>
-      <c r="C34" s="152"/>
-      <c r="D34" s="152"/>
-      <c r="E34" s="152"/>
-      <c r="F34" s="152"/>
-      <c r="G34" s="152"/>
-      <c r="H34" s="152"/>
-    </row>
-    <row r="35" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A35" s="158"/>
-      <c r="B35" s="152"/>
-      <c r="C35" s="152"/>
-      <c r="D35" s="152"/>
-      <c r="E35" s="152"/>
-      <c r="F35" s="152"/>
-      <c r="G35" s="152"/>
-      <c r="H35" s="152"/>
-    </row>
-    <row r="36" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A36" s="164" t="s">
+    <row r="21" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A21" s="177"/>
+      <c r="B21" s="171"/>
+      <c r="C21" s="171"/>
+      <c r="D21" s="171"/>
+      <c r="E21" s="171"/>
+      <c r="F21" s="171"/>
+      <c r="G21" s="171"/>
+      <c r="H21" s="171"/>
+    </row>
+    <row r="22" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A22" s="177"/>
+      <c r="B22" s="171"/>
+      <c r="C22" s="171"/>
+      <c r="D22" s="171"/>
+      <c r="E22" s="171"/>
+      <c r="F22" s="171"/>
+      <c r="G22" s="171"/>
+      <c r="H22" s="171"/>
+    </row>
+    <row r="23" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A23" s="177"/>
+      <c r="B23" s="171"/>
+      <c r="C23" s="171"/>
+      <c r="D23" s="171"/>
+      <c r="E23" s="171"/>
+      <c r="F23" s="171"/>
+      <c r="G23" s="171"/>
+      <c r="H23" s="171"/>
+    </row>
+    <row r="24" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A24" s="177"/>
+      <c r="B24" s="171"/>
+      <c r="C24" s="171"/>
+      <c r="D24" s="171"/>
+      <c r="E24" s="171"/>
+      <c r="F24" s="171"/>
+      <c r="G24" s="171"/>
+      <c r="H24" s="171"/>
+    </row>
+    <row r="25" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A25" s="177"/>
+      <c r="B25" s="171"/>
+      <c r="C25" s="171"/>
+      <c r="D25" s="171"/>
+      <c r="E25" s="171"/>
+      <c r="F25" s="171"/>
+      <c r="G25" s="171"/>
+      <c r="H25" s="171"/>
+    </row>
+    <row r="26" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A26" s="177"/>
+      <c r="B26" s="171"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="171"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="171"/>
+      <c r="G26" s="171"/>
+      <c r="H26" s="171"/>
+    </row>
+    <row r="27" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A27" s="177"/>
+      <c r="B27" s="171"/>
+      <c r="C27" s="171"/>
+      <c r="D27" s="171"/>
+      <c r="E27" s="171"/>
+      <c r="F27" s="171"/>
+      <c r="G27" s="171"/>
+      <c r="H27" s="171"/>
+    </row>
+    <row r="28" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A28" s="177"/>
+      <c r="B28" s="171"/>
+      <c r="C28" s="171"/>
+      <c r="D28" s="171"/>
+      <c r="E28" s="171"/>
+      <c r="F28" s="171"/>
+      <c r="G28" s="171"/>
+      <c r="H28" s="171"/>
+    </row>
+    <row r="29" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A29" s="177"/>
+      <c r="B29" s="171"/>
+      <c r="C29" s="171"/>
+      <c r="D29" s="171"/>
+      <c r="E29" s="171"/>
+      <c r="F29" s="171"/>
+      <c r="G29" s="171"/>
+      <c r="H29" s="171"/>
+    </row>
+    <row r="30" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A30" s="177"/>
+      <c r="B30" s="171"/>
+      <c r="C30" s="171"/>
+      <c r="D30" s="171"/>
+      <c r="E30" s="171"/>
+      <c r="F30" s="171"/>
+      <c r="G30" s="171"/>
+      <c r="H30" s="171"/>
+    </row>
+    <row r="31" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A31" s="177"/>
+      <c r="B31" s="171"/>
+      <c r="C31" s="171"/>
+      <c r="D31" s="171"/>
+      <c r="E31" s="171"/>
+      <c r="F31" s="171"/>
+      <c r="G31" s="171"/>
+      <c r="H31" s="171"/>
+    </row>
+    <row r="32" s="165" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
+      <c r="A32" s="182"/>
+    </row>
+    <row r="33" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A33" s="177"/>
+      <c r="B33" s="171"/>
+      <c r="C33" s="171"/>
+      <c r="D33" s="171"/>
+      <c r="E33" s="171"/>
+      <c r="F33" s="171"/>
+      <c r="G33" s="171"/>
+      <c r="H33" s="171"/>
+    </row>
+    <row r="34" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A34" s="177"/>
+      <c r="B34" s="171"/>
+      <c r="C34" s="171"/>
+      <c r="D34" s="171"/>
+      <c r="E34" s="171"/>
+      <c r="F34" s="171"/>
+      <c r="G34" s="171"/>
+      <c r="H34" s="171"/>
+    </row>
+    <row r="35" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A35" s="177"/>
+      <c r="B35" s="171"/>
+      <c r="C35" s="171"/>
+      <c r="D35" s="171"/>
+      <c r="E35" s="171"/>
+      <c r="F35" s="171"/>
+      <c r="G35" s="171"/>
+      <c r="H35" s="171"/>
+    </row>
+    <row r="36" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A36" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="165"/>
-      <c r="C36" s="164" t="s">
+      <c r="B36" s="184"/>
+      <c r="C36" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="165"/>
-      <c r="E36" s="164" t="s">
+      <c r="D36" s="184"/>
+      <c r="E36" s="183" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="166"/>
-      <c r="G36" s="164" t="s">
+      <c r="F36" s="185"/>
+      <c r="G36" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="167"/>
-    </row>
-    <row r="37" s="146" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A37" s="168" t="s">
+      <c r="H36" s="186"/>
+    </row>
+    <row r="37" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A37" s="187" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="169"/>
-      <c r="C37" s="170"/>
-      <c r="D37" s="171"/>
-      <c r="E37" s="168" t="s">
+      <c r="B37" s="188"/>
+      <c r="C37" s="189"/>
+      <c r="D37" s="190"/>
+      <c r="E37" s="187" t="s">
         <v>13</v>
       </c>
-      <c r="F37" s="172"/>
-      <c r="G37" s="170"/>
-      <c r="H37" s="171"/>
+      <c r="F37" s="191"/>
+      <c r="G37" s="189"/>
+      <c r="H37" s="190"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="148"/>
+      <c r="A38" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4439,634 +4720,665 @@
   <dimension ref="B1:P30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="0.876106194690266" style="79" customWidth="1"/>
-    <col min="2" max="2" width="3.3716814159292" style="79" customWidth="1"/>
-    <col min="3" max="3" width="10.7522123893805" style="80" customWidth="1"/>
-    <col min="4" max="4" width="23.3716814159292" style="79" customWidth="1"/>
-    <col min="5" max="5" width="9.55752212389381" style="79" customWidth="1"/>
-    <col min="6" max="6" width="12.7522123893805" style="79" customWidth="1"/>
-    <col min="7" max="7" width="9.3716814159292" style="79" customWidth="1"/>
-    <col min="8" max="8" width="6.87610619469027" style="79" customWidth="1"/>
-    <col min="9" max="10" width="6.87610619469027" style="78" customWidth="1"/>
-    <col min="11" max="13" width="6.87610619469027" style="79" customWidth="1"/>
-    <col min="14" max="14" width="36.1150442477876" style="79" customWidth="1"/>
-    <col min="15" max="15" width="27.4159292035398" style="79" customWidth="1"/>
-    <col min="16" max="16" width="12" style="79" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="79" customWidth="1"/>
+    <col min="1" max="1" width="0.876106194690266" style="89" customWidth="1"/>
+    <col min="2" max="2" width="3.3716814159292" style="89" customWidth="1"/>
+    <col min="3" max="3" width="10.7522123893805" style="90" customWidth="1"/>
+    <col min="4" max="4" width="23.3716814159292" style="89" customWidth="1"/>
+    <col min="5" max="5" width="9.55752212389381" style="89" customWidth="1"/>
+    <col min="6" max="6" width="12.7522123893805" style="89" customWidth="1"/>
+    <col min="7" max="7" width="9.3716814159292" style="89" customWidth="1"/>
+    <col min="8" max="8" width="6.87610619469027" style="89" customWidth="1"/>
+    <col min="9" max="10" width="6.87610619469027" style="88" customWidth="1"/>
+    <col min="11" max="13" width="6.87610619469027" style="89" customWidth="1"/>
+    <col min="14" max="14" width="36.1150442477876" style="89" customWidth="1"/>
+    <col min="15" max="15" width="27.4159292035398" style="89" customWidth="1"/>
+    <col min="16" max="16" width="12" style="89" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="89" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="73" customFormat="1" ht="29.25" customHeight="1" spans="2:16">
-      <c r="B1" s="81" t="s">
+    <row r="1" s="83" customFormat="1" ht="29.25" customHeight="1" spans="2:16">
+      <c r="B1" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-    </row>
-    <row r="2" s="74" customFormat="1" ht="24.75" customHeight="1" spans="2:16">
-      <c r="B2" s="84" t="s">
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="93"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+    </row>
+    <row r="2" s="84" customFormat="1" ht="24.75" customHeight="1" spans="2:16">
+      <c r="B2" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="85" t="s">
+      <c r="C2" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="85" t="s">
+      <c r="D2" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="85" t="s">
+      <c r="E2" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="85" t="s">
+      <c r="F2" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="85" t="s">
+      <c r="G2" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="85" t="s">
+      <c r="H2" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="85" t="s">
+      <c r="I2" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="85" t="s">
+      <c r="J2" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="85" t="s">
+      <c r="K2" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="85" t="s">
+      <c r="L2" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="85" t="s">
+      <c r="M2" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="86" t="s">
+      <c r="N2" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="86" t="s">
+      <c r="O2" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="87" t="s">
+      <c r="P2" s="97" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" s="75" customFormat="1" ht="14.25" customHeight="1" spans="2:16">
-      <c r="B3" s="88">
+    <row r="3" s="85" customFormat="1" ht="14.25" customHeight="1" spans="2:16">
+      <c r="B3" s="98">
         <v>1</v>
       </c>
-      <c r="C3" s="89" t="s">
+      <c r="C3" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="90" t="s">
+      <c r="D3" s="100" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="91" t="s">
+      <c r="E3" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="92" t="s">
+      <c r="F3" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="93" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="92">
+      <c r="G3" s="103" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="102">
         <v>0</v>
       </c>
-      <c r="I3" s="92">
+      <c r="I3" s="102">
         <v>17</v>
       </c>
-      <c r="J3" s="92">
+      <c r="J3" s="102">
         <v>0</v>
       </c>
-      <c r="K3" s="92">
+      <c r="K3" s="102">
         <v>0</v>
       </c>
-      <c r="L3" s="94">
+      <c r="L3" s="104">
         <v>17</v>
       </c>
-      <c r="M3" s="95" t="s">
+      <c r="M3" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="96" t="s">
+      <c r="N3" s="106" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="96" t="s">
+      <c r="O3" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="97">
+      <c r="P3" s="107">
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B4" s="98">
+    <row r="4" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B4" s="108">
         <v>2</v>
       </c>
-      <c r="C4" s="99">
+      <c r="C4" s="109">
         <v>46272</v>
       </c>
-      <c r="D4" s="100" t="s">
+      <c r="D4" s="110" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="101" t="s">
+      <c r="E4" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="92" t="s">
+      <c r="F4" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="102" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="103">
+      <c r="G4" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="113">
         <v>17</v>
       </c>
-      <c r="I4" s="104">
+      <c r="I4" s="114">
         <v>22</v>
       </c>
-      <c r="J4" s="104">
+      <c r="J4" s="114">
         <v>0</v>
       </c>
-      <c r="K4" s="104">
+      <c r="K4" s="114">
         <v>0</v>
       </c>
-      <c r="L4" s="94">
+      <c r="L4" s="104">
         <v>22</v>
       </c>
-      <c r="M4" s="105">
+      <c r="M4" s="115">
         <v>0.2941</v>
       </c>
-      <c r="N4" s="96" t="s">
+      <c r="N4" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="96" t="s">
+      <c r="O4" s="106" t="s">
         <v>42</v>
       </c>
-      <c r="P4" s="106">
+      <c r="P4" s="116">
         <v>0.15</v>
       </c>
     </row>
-    <row r="5" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B5" s="98">
+    <row r="5" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B5" s="108">
         <v>3</v>
       </c>
-      <c r="C5" s="107" t="s">
+      <c r="C5" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="100" t="s">
+      <c r="D5" s="110" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="101" t="s">
+      <c r="E5" s="111" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="104" t="s">
+      <c r="F5" s="114" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="102" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="103">
+      <c r="G5" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="113">
         <v>22</v>
       </c>
-      <c r="I5" s="104">
+      <c r="I5" s="114">
         <v>0</v>
       </c>
-      <c r="J5" s="104">
+      <c r="J5" s="114">
         <v>0</v>
       </c>
-      <c r="K5" s="104">
+      <c r="K5" s="114">
         <v>1</v>
       </c>
-      <c r="L5" s="94">
+      <c r="L5" s="104">
         <v>22</v>
       </c>
-      <c r="M5" s="105">
+      <c r="M5" s="115">
         <v>0.045</v>
       </c>
-      <c r="N5" s="102" t="s">
+      <c r="N5" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="O5" s="102" t="s">
+      <c r="O5" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="P5" s="106">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="6" s="75" customFormat="1" ht="13" customHeight="1" spans="2:16">
-      <c r="B6" s="108">
+      <c r="P5" s="116">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" s="85" customFormat="1" ht="13" customHeight="1" spans="2:16">
+      <c r="B6" s="118">
         <v>4</v>
       </c>
-      <c r="C6" s="109">
+      <c r="C6" s="119">
         <v>46280</v>
       </c>
-      <c r="D6" s="110" t="s">
+      <c r="D6" s="120" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="111" t="s">
+      <c r="E6" s="121" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="112" t="s">
+      <c r="F6" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="113" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="114">
+      <c r="G6" s="123" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="124">
         <v>22</v>
       </c>
-      <c r="I6" s="112">
+      <c r="I6" s="122">
         <v>8</v>
       </c>
-      <c r="J6" s="112">
+      <c r="J6" s="122">
         <v>0</v>
       </c>
-      <c r="K6" s="112">
+      <c r="K6" s="122">
         <v>3</v>
       </c>
-      <c r="L6" s="115">
+      <c r="L6" s="125">
         <v>30</v>
       </c>
-      <c r="M6" s="116">
+      <c r="M6" s="126">
         <v>0.5</v>
       </c>
-      <c r="N6" s="113" t="s">
+      <c r="N6" s="123" t="s">
         <v>52</v>
       </c>
-      <c r="O6" s="113" t="s">
+      <c r="O6" s="123" t="s">
         <v>53</v>
       </c>
-      <c r="P6" s="117">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="7" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B7" s="98">
+      <c r="P6" s="127">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B7" s="108">
         <v>5</v>
       </c>
-      <c r="C7" s="109">
-        <v>46283</v>
-      </c>
-      <c r="D7" s="100" t="s">
+      <c r="C7" s="119">
+        <v>46294</v>
+      </c>
+      <c r="D7" s="110" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="101" t="s">
+      <c r="E7" s="111" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="104" t="s">
+      <c r="F7" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="102" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="103">
+      <c r="G7" s="112" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="113">
         <v>30</v>
       </c>
-      <c r="I7" s="104">
+      <c r="I7" s="114">
         <v>0</v>
       </c>
-      <c r="J7" s="104">
+      <c r="J7" s="114">
         <v>1</v>
       </c>
-      <c r="K7" s="104">
+      <c r="K7" s="114">
         <v>0</v>
       </c>
-      <c r="L7" s="94">
+      <c r="L7" s="104">
         <v>29</v>
       </c>
-      <c r="M7" s="105">
+      <c r="M7" s="115">
         <v>0.033</v>
       </c>
-      <c r="N7" s="113" t="s">
+      <c r="N7" s="123" t="s">
         <v>57</v>
       </c>
-      <c r="O7" s="102" t="s">
+      <c r="O7" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="P7" s="106">
+      <c r="P7" s="116">
         <v>0.05</v>
       </c>
     </row>
-    <row r="8" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B8" s="98">
+    <row r="8" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B8" s="108">
         <v>6</v>
       </c>
-      <c r="C8" s="107"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="104"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="94"/>
-      <c r="M8" s="105"/>
-      <c r="N8" s="118"/>
-      <c r="O8" s="118"/>
-      <c r="P8" s="119"/>
-    </row>
-    <row r="9" s="76" customFormat="1" ht="12" customHeight="1" spans="2:16">
-      <c r="B9" s="120">
+      <c r="C8" s="128">
+        <v>46303</v>
+      </c>
+      <c r="D8" s="129" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="131" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="132" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="133">
+        <f>L7</f>
+        <v>29</v>
+      </c>
+      <c r="I8" s="131">
+        <v>21</v>
+      </c>
+      <c r="J8" s="131">
+        <v>0</v>
+      </c>
+      <c r="K8" s="131">
         <v>7</v>
       </c>
-      <c r="C9" s="121"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="122"/>
-      <c r="F9" s="123"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="92"/>
-      <c r="I9" s="123"/>
-      <c r="J9" s="123"/>
-      <c r="K9" s="123"/>
-      <c r="L9" s="94"/>
-      <c r="M9" s="105"/>
-      <c r="N9" s="124"/>
-      <c r="O9" s="124"/>
-      <c r="P9" s="125"/>
-    </row>
-    <row r="10" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B10" s="98">
+      <c r="L8" s="134">
+        <f>H8+I8-J8</f>
+        <v>50</v>
+      </c>
+      <c r="M8" s="135">
+        <f>(I8+J8+K8)/H8</f>
+        <v>0.96551724137931</v>
+      </c>
+      <c r="N8" s="123" t="s">
+        <v>62</v>
+      </c>
+      <c r="O8" s="136" t="s">
+        <v>63</v>
+      </c>
+      <c r="P8" s="137">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" s="86" customFormat="1" ht="12" customHeight="1" spans="2:16">
+      <c r="B9" s="138">
+        <v>7</v>
+      </c>
+      <c r="C9" s="139"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="140"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="102"/>
+      <c r="I9" s="141"/>
+      <c r="J9" s="141"/>
+      <c r="K9" s="141"/>
+      <c r="L9" s="104"/>
+      <c r="M9" s="115"/>
+      <c r="N9" s="142"/>
+      <c r="O9" s="142"/>
+      <c r="P9" s="143"/>
+    </row>
+    <row r="10" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B10" s="108">
         <v>8</v>
       </c>
-      <c r="C10" s="126"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="94"/>
-      <c r="M10" s="105"/>
-      <c r="N10" s="124"/>
-      <c r="O10" s="118"/>
-      <c r="P10" s="125"/>
-    </row>
-    <row r="11" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B11" s="98">
+      <c r="C10" s="144"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="114"/>
+      <c r="L10" s="104"/>
+      <c r="M10" s="115"/>
+      <c r="N10" s="142"/>
+      <c r="O10" s="145"/>
+      <c r="P10" s="143"/>
+    </row>
+    <row r="11" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B11" s="108">
         <v>9</v>
       </c>
-      <c r="C11" s="126"/>
-      <c r="D11" s="100"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104"/>
-      <c r="L11" s="94"/>
-      <c r="M11" s="105"/>
-      <c r="N11" s="124"/>
-      <c r="O11" s="118"/>
-      <c r="P11" s="125"/>
-    </row>
-    <row r="12" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B12" s="98">
+      <c r="C11" s="144"/>
+      <c r="D11" s="110"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="113"/>
+      <c r="I11" s="114"/>
+      <c r="J11" s="114"/>
+      <c r="K11" s="114"/>
+      <c r="L11" s="104"/>
+      <c r="M11" s="115"/>
+      <c r="N11" s="142"/>
+      <c r="O11" s="145"/>
+      <c r="P11" s="143"/>
+    </row>
+    <row r="12" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B12" s="108">
         <v>10</v>
       </c>
-      <c r="C12" s="126"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="94"/>
-      <c r="M12" s="105"/>
-      <c r="N12" s="124"/>
-      <c r="O12" s="118"/>
-      <c r="P12" s="125"/>
-    </row>
-    <row r="13" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B13" s="98">
+      <c r="C12" s="144"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="114"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="114"/>
+      <c r="J12" s="114"/>
+      <c r="K12" s="114"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="115"/>
+      <c r="N12" s="142"/>
+      <c r="O12" s="145"/>
+      <c r="P12" s="143"/>
+    </row>
+    <row r="13" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B13" s="108">
         <v>11</v>
       </c>
-      <c r="C13" s="127"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="133"/>
-      <c r="M13" s="134"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="136"/>
-      <c r="P13" s="137"/>
-    </row>
-    <row r="14" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B14" s="98">
+      <c r="C13" s="146"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="148"/>
+      <c r="F13" s="149"/>
+      <c r="G13" s="150"/>
+      <c r="H13" s="151"/>
+      <c r="I13" s="149"/>
+      <c r="J13" s="149"/>
+      <c r="K13" s="149"/>
+      <c r="L13" s="152"/>
+      <c r="M13" s="153"/>
+      <c r="N13" s="154"/>
+      <c r="O13" s="155"/>
+      <c r="P13" s="156"/>
+    </row>
+    <row r="14" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B14" s="108">
         <v>12</v>
       </c>
-      <c r="C14" s="127"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="130"/>
-      <c r="G14" s="131"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="130"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="133"/>
-      <c r="M14" s="134"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="137"/>
-    </row>
-    <row r="15" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B15" s="98">
+      <c r="C14" s="146"/>
+      <c r="D14" s="147"/>
+      <c r="E14" s="148"/>
+      <c r="F14" s="149"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="151"/>
+      <c r="I14" s="149"/>
+      <c r="J14" s="149"/>
+      <c r="K14" s="149"/>
+      <c r="L14" s="152"/>
+      <c r="M14" s="153"/>
+      <c r="N14" s="155"/>
+      <c r="O14" s="155"/>
+      <c r="P14" s="156"/>
+    </row>
+    <row r="15" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B15" s="108">
         <v>13</v>
       </c>
-      <c r="C15" s="107"/>
-      <c r="D15" s="100"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="104"/>
-      <c r="K15" s="104"/>
-      <c r="L15" s="94"/>
-      <c r="M15" s="105"/>
-      <c r="N15" s="138"/>
-      <c r="O15" s="138"/>
-      <c r="P15" s="139"/>
-    </row>
-    <row r="16" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B16" s="98">
+      <c r="C15" s="117"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="112"/>
+      <c r="H15" s="113"/>
+      <c r="I15" s="114"/>
+      <c r="J15" s="114"/>
+      <c r="K15" s="114"/>
+      <c r="L15" s="104"/>
+      <c r="M15" s="115"/>
+      <c r="N15" s="157"/>
+      <c r="O15" s="157"/>
+      <c r="P15" s="158"/>
+    </row>
+    <row r="16" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B16" s="108">
         <v>14</v>
       </c>
-      <c r="C16" s="107"/>
-      <c r="D16" s="100"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="102"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="104"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="94"/>
-      <c r="M16" s="105"/>
-      <c r="N16" s="138"/>
-      <c r="O16" s="138"/>
-      <c r="P16" s="139"/>
-    </row>
-    <row r="17" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B17" s="98">
+      <c r="C16" s="117"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="114"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="114"/>
+      <c r="L16" s="104"/>
+      <c r="M16" s="115"/>
+      <c r="N16" s="157"/>
+      <c r="O16" s="157"/>
+      <c r="P16" s="158"/>
+    </row>
+    <row r="17" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B17" s="108">
         <v>15</v>
       </c>
-      <c r="C17" s="107"/>
-      <c r="D17" s="100"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="102"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="104"/>
-      <c r="K17" s="104"/>
-      <c r="L17" s="94"/>
-      <c r="M17" s="105"/>
-      <c r="N17" s="140"/>
-      <c r="O17" s="140"/>
-      <c r="P17" s="139"/>
-    </row>
-    <row r="18" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B18" s="98">
+      <c r="C17" s="117"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="112"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
+      <c r="L17" s="104"/>
+      <c r="M17" s="115"/>
+      <c r="N17" s="159"/>
+      <c r="O17" s="159"/>
+      <c r="P17" s="158"/>
+    </row>
+    <row r="18" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B18" s="108">
         <v>16</v>
       </c>
-      <c r="C18" s="107"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="102"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="94"/>
-      <c r="M18" s="105"/>
-      <c r="N18" s="140"/>
-      <c r="O18" s="140"/>
-      <c r="P18" s="139"/>
-    </row>
-    <row r="19" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B19" s="98">
+      <c r="C18" s="117"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="112"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="114"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="114"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="115"/>
+      <c r="N18" s="159"/>
+      <c r="O18" s="159"/>
+      <c r="P18" s="158"/>
+    </row>
+    <row r="19" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B19" s="108">
         <v>17</v>
       </c>
-      <c r="C19" s="107"/>
-      <c r="D19" s="100"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="102"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="104"/>
-      <c r="K19" s="104"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="105"/>
-      <c r="N19" s="140"/>
-      <c r="O19" s="140"/>
-      <c r="P19" s="139"/>
-    </row>
-    <row r="20" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B20" s="98">
+      <c r="C19" s="117"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="114"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="113"/>
+      <c r="I19" s="114"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="114"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="115"/>
+      <c r="N19" s="159"/>
+      <c r="O19" s="159"/>
+      <c r="P19" s="158"/>
+    </row>
+    <row r="20" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B20" s="108">
         <v>18</v>
       </c>
-      <c r="C20" s="107"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="102"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="94"/>
-      <c r="M20" s="105"/>
-      <c r="N20" s="140"/>
-      <c r="O20" s="140"/>
-      <c r="P20" s="139"/>
-    </row>
-    <row r="21" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B21" s="98">
+      <c r="C20" s="117"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="114"/>
+      <c r="G20" s="112"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="114"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="114"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="115"/>
+      <c r="N20" s="159"/>
+      <c r="O20" s="159"/>
+      <c r="P20" s="158"/>
+    </row>
+    <row r="21" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B21" s="108">
         <v>19</v>
       </c>
-      <c r="C21" s="107"/>
-      <c r="D21" s="100"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="104"/>
-      <c r="K21" s="104"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="105"/>
-      <c r="N21" s="140"/>
-      <c r="O21" s="140"/>
-      <c r="P21" s="139"/>
-    </row>
-    <row r="22" s="75" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B22" s="98">
+      <c r="C21" s="117"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="114"/>
+      <c r="G21" s="112"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="114"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="115"/>
+      <c r="N21" s="159"/>
+      <c r="O21" s="159"/>
+      <c r="P21" s="158"/>
+    </row>
+    <row r="22" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B22" s="108">
         <v>20</v>
       </c>
-      <c r="C22" s="107"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="102"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="104"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="104"/>
-      <c r="L22" s="94"/>
-      <c r="M22" s="105"/>
-      <c r="N22" s="140"/>
-      <c r="O22" s="140"/>
-      <c r="P22" s="139"/>
-    </row>
-    <row r="23" s="77" customFormat="1" ht="13.9" customHeight="1" spans="2:16">
-      <c r="B23" s="141" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="142"/>
-      <c r="D23" s="142"/>
-      <c r="E23" s="142"/>
-      <c r="F23" s="142"/>
-      <c r="G23" s="142"/>
-      <c r="H23" s="143"/>
-      <c r="I23" s="143"/>
-      <c r="J23" s="143"/>
-      <c r="K23" s="143"/>
-      <c r="L23" s="143"/>
-      <c r="M23" s="144"/>
-      <c r="N23" s="143"/>
-      <c r="O23" s="143"/>
-      <c r="P23" s="145"/>
-    </row>
-    <row r="24" s="78" customFormat="1"/>
-    <row r="25" s="78" customFormat="1"/>
-    <row r="26" s="78" customFormat="1"/>
-    <row r="27" s="78" customFormat="1"/>
-    <row r="28" s="78" customFormat="1"/>
-    <row r="29" s="78" customFormat="1"/>
-    <row r="30" s="78" customFormat="1"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="114"/>
+      <c r="G22" s="112"/>
+      <c r="H22" s="113"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="114"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="115"/>
+      <c r="N22" s="159"/>
+      <c r="O22" s="159"/>
+      <c r="P22" s="158"/>
+    </row>
+    <row r="23" s="87" customFormat="1" ht="13.9" customHeight="1" spans="2:16">
+      <c r="B23" s="160" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="161"/>
+      <c r="D23" s="161"/>
+      <c r="E23" s="161"/>
+      <c r="F23" s="161"/>
+      <c r="G23" s="161"/>
+      <c r="H23" s="162"/>
+      <c r="I23" s="162"/>
+      <c r="J23" s="162"/>
+      <c r="K23" s="162"/>
+      <c r="L23" s="162"/>
+      <c r="M23" s="163"/>
+      <c r="N23" s="162"/>
+      <c r="O23" s="162"/>
+      <c r="P23" s="164"/>
+    </row>
+    <row r="24" s="88" customFormat="1"/>
+    <row r="25" s="88" customFormat="1"/>
+    <row r="26" s="88" customFormat="1"/>
+    <row r="27" s="88" customFormat="1"/>
+    <row r="28" s="88" customFormat="1"/>
+    <row r="29" s="88" customFormat="1"/>
+    <row r="30" s="88" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="99" fitToHeight="0" orientation="landscape"/>
@@ -5083,1257 +5395,2181 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
     <col min="1" max="1" width="0.876106194690266" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.50442477876106" style="9" customWidth="1"/>
-    <col min="3" max="3" width="15.1238938053097" style="9" customWidth="1"/>
-    <col min="4" max="4" width="23" style="9" customWidth="1"/>
-    <col min="5" max="5" width="24.1238938053097" style="9" customWidth="1"/>
-    <col min="6" max="6" width="32.3716814159292" style="9" customWidth="1"/>
-    <col min="7" max="7" width="3.50442477876106" style="9" customWidth="1"/>
-    <col min="8" max="8" width="4.50442477876106" style="9" customWidth="1"/>
-    <col min="9" max="9" width="3.50442477876106" style="9" customWidth="1"/>
-    <col min="10" max="10" width="23" style="10" customWidth="1"/>
-    <col min="11" max="11" width="6.75221238938053" style="10" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="11" customWidth="1"/>
+    <col min="2" max="2" width="9.50442477876106" style="11" customWidth="1"/>
+    <col min="3" max="3" width="15.1238938053097" style="11" customWidth="1"/>
+    <col min="4" max="4" width="23" style="11" customWidth="1"/>
+    <col min="5" max="5" width="24.1238938053097" style="11" customWidth="1"/>
+    <col min="6" max="6" width="32.3716814159292" style="11" customWidth="1"/>
+    <col min="7" max="7" width="3.50442477876106" style="11" customWidth="1"/>
+    <col min="8" max="8" width="4.50442477876106" style="11" customWidth="1"/>
+    <col min="9" max="9" width="3.50442477876106" style="11" customWidth="1"/>
+    <col min="10" max="10" width="23" style="12" customWidth="1"/>
+    <col min="11" max="11" width="6.75221238938053" style="12" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:11">
-      <c r="B1" s="12" t="s">
-        <v>60</v>
+      <c r="B1" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="13.9" customHeight="1" spans="1:11">
       <c r="A2" s="1"/>
-      <c r="B2" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="18"/>
+      <c r="B2" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:11">
-      <c r="K3" s="19"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:11">
       <c r="A4" s="1"/>
-      <c r="B4" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="22" t="s">
+      <c r="B4" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="C4" s="23" t="s">
         <v>71</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:11">
       <c r="A5" s="1"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="27"/>
-      <c r="G5" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" s="28" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="27"/>
-      <c r="K5" s="29"/>
-    </row>
-    <row r="6" s="4" customFormat="1" ht="29" customHeight="1" spans="1:11">
+      <c r="D5" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="29"/>
+      <c r="G5" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="J5" s="29"/>
+      <c r="K5" s="31"/>
+    </row>
+    <row r="6" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A6" s="1"/>
-      <c r="B6" s="30">
+      <c r="B6" s="32">
         <v>1</v>
       </c>
-      <c r="C6" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J6" s="35" t="s">
+      <c r="C6" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" s="4" customFormat="1" ht="42.75" customHeight="1" spans="1:11">
+      <c r="D6" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="K6" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A7" s="1"/>
-      <c r="B7" s="37">
+      <c r="B7" s="39">
         <v>2</v>
       </c>
-      <c r="C7" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="40" t="s">
+      <c r="C7" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="F7" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J7" s="35" t="s">
+      <c r="E7" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="K7" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A8" s="1"/>
+      <c r="B8" s="39">
+        <v>3</v>
+      </c>
+      <c r="C8" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:11">
-      <c r="A8" s="1"/>
-      <c r="B8" s="37">
-        <v>3</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J8" s="35" t="s">
+      <c r="D8" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="K8" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A9" s="1"/>
+      <c r="B9" s="39">
+        <v>4</v>
+      </c>
+      <c r="C9" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" s="4" customFormat="1" ht="61.5" customHeight="1" spans="1:11">
-      <c r="A9" s="1"/>
-      <c r="B9" s="37">
-        <v>4</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J9" s="35" t="s">
+      <c r="K9" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="1" ht="51" spans="1:11">
+      <c r="A10" s="1"/>
+      <c r="B10" s="43">
+        <v>5</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="K10" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A11" s="1"/>
+      <c r="B11" s="32">
+        <v>6</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="K11" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" ht="38.25" spans="1:11">
+      <c r="A12" s="1"/>
+      <c r="B12" s="39">
+        <v>7</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="K12" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A13" s="1"/>
+      <c r="B13" s="39">
+        <v>8</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K13" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" ht="38.25" spans="1:11">
+      <c r="A14" s="1"/>
+      <c r="B14" s="39">
+        <v>9</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="K14" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" s="4" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A15" s="1"/>
+      <c r="B15" s="39">
+        <v>10</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H15" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I15" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" s="4" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A16" s="1"/>
+      <c r="B16" s="39">
+        <v>11</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="K16" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" s="4" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A17" s="1"/>
+      <c r="B17" s="47">
+        <v>12</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" s="4" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A18" s="1"/>
+      <c r="B18" s="32">
+        <v>13</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="G18" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I18" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" s="4" customFormat="1" ht="38.25" spans="1:11">
+      <c r="A19" s="1"/>
+      <c r="B19" s="51">
+        <v>14</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="K19" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" s="4" customFormat="1" ht="51" spans="1:11">
+      <c r="A20" s="1"/>
+      <c r="B20" s="39">
+        <v>15</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A21" s="1"/>
+      <c r="B21" s="43">
+        <v>16</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="G21" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I21" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="K21" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" s="4" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A22" s="1"/>
+      <c r="B22" s="39">
+        <v>17</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="G22" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I22" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" s="4" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A23" s="1"/>
+      <c r="B23" s="51">
+        <v>18</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="G23" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I23" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K23" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A24" s="1"/>
+      <c r="B24" s="39">
+        <v>19</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="F24" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="K24" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" s="4" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A25" s="1"/>
+      <c r="B25" s="43">
+        <v>20</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="G25" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I25" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J25" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K25" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" s="4" customFormat="1" ht="13.5" spans="1:11">
+      <c r="A26" s="1"/>
+      <c r="B26" s="47">
+        <v>21</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="G26" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="I26" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K26" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" s="5" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A27" s="56"/>
+      <c r="B27" s="32">
+        <v>22</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E27" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="G27" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H27" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="I27" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K27" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" s="6" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A28" s="57"/>
+      <c r="B28" s="51">
+        <v>23</v>
+      </c>
+      <c r="C28" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="K9" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" s="4" customFormat="1" ht="62" customHeight="1" spans="1:11">
-      <c r="A10" s="1"/>
-      <c r="B10" s="41">
-        <v>5</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="F10" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J10" s="35" t="s">
+      <c r="D28" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E28" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="G28" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="H28" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="I28" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K28" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" s="4" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A29" s="1"/>
+      <c r="B29" s="51">
+        <v>24</v>
+      </c>
+      <c r="C29" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" s="4" customFormat="1" ht="33" customHeight="1" spans="1:11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="30">
-        <v>6</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="F11" s="32" t="s">
+      <c r="D29" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="G29" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="H29" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="I29" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="K29" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" s="4" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A30" s="1"/>
+      <c r="B30" s="60">
+        <v>25</v>
+      </c>
+      <c r="C30" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="E30" s="54" t="s">
+        <v>156</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="G30" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="H30" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="I30" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" s="4" customFormat="1" ht="38.25" spans="1:11">
+      <c r="A31" s="1"/>
+      <c r="B31" s="39">
+        <v>26</v>
+      </c>
+      <c r="C31" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I11" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J11" s="35" t="s">
+      <c r="D31" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="K11" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" s="4" customFormat="1" ht="41" customHeight="1" spans="1:11">
-      <c r="A12" s="1"/>
-      <c r="B12" s="37">
-        <v>7</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I12" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J12" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="K12" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" s="4" customFormat="1" ht="74" customHeight="1" spans="1:11">
-      <c r="A13" s="1"/>
-      <c r="B13" s="37">
-        <v>8</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="F13" s="39" t="s">
+      <c r="E31" s="54" t="s">
+        <v>158</v>
+      </c>
+      <c r="F31" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="G31" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="I31" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="K31" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" s="4" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A32" s="1"/>
+      <c r="B32" s="51">
+        <v>27</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="F32" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="G32" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="H32" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="I32" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" s="4" customFormat="1" ht="38.25" spans="1:11">
+      <c r="A33" s="1"/>
+      <c r="B33" s="39">
+        <v>28</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="F33" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="G33" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="H33" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="I33" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" s="4" customFormat="1" ht="38.25" spans="1:11">
+      <c r="A34" s="1"/>
+      <c r="B34" s="39">
+        <v>29</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="D34" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="E34" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="G34" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="H34" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="I34" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="K34" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" s="4" customFormat="1" ht="38.25" spans="1:11">
+      <c r="A35" s="1"/>
+      <c r="B35" s="32">
+        <v>30</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="E35" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="F35" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="G35" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H35" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I35" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A36" s="1"/>
+      <c r="B36" s="51">
+        <v>31</v>
+      </c>
+      <c r="C36" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="D36" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="E36" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="F36" s="55" t="s">
+        <v>174</v>
+      </c>
+      <c r="G36" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H36" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I36" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K36" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A37" s="1"/>
+      <c r="B37" s="39">
+        <v>32</v>
+      </c>
+      <c r="C37" s="64" t="s">
+        <v>171</v>
+      </c>
+      <c r="D37" s="41" t="s">
+        <v>175</v>
+      </c>
+      <c r="E37" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="F37" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="G37" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H37" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I37" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K37" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" s="6" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A38" s="57"/>
+      <c r="B38" s="39">
+        <v>33</v>
+      </c>
+      <c r="C38" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="D38" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="E38" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="F38" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="G38" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H38" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I38" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J38" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="K38" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" s="7" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A39" s="65"/>
+      <c r="B39" s="32">
+        <v>34</v>
+      </c>
+      <c r="C39" s="64" t="s">
+        <v>171</v>
+      </c>
+      <c r="D39" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="E39" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="F39" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="G39" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H39" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I39" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J39" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K39" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A40" s="1"/>
+      <c r="B40" s="51">
+        <v>35</v>
+      </c>
+      <c r="C40" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="D40" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="E40" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="F40" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="G40" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H40" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I40" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K40" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A41" s="1"/>
+      <c r="B41" s="39">
+        <v>36</v>
+      </c>
+      <c r="C41" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="D41" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="E41" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="F41" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="G41" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H41" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I41" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="K41" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A42" s="1"/>
+      <c r="B42" s="39">
+        <v>37</v>
+      </c>
+      <c r="C42" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="D42" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E42" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="F42" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="G42" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H42" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I42" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J42" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="K42" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A43" s="1"/>
+      <c r="B43" s="32">
+        <v>38</v>
+      </c>
+      <c r="C43" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="F43" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="G43" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H43" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I43" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J43" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="K43" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" s="4" customFormat="1" ht="76.5" spans="1:11">
+      <c r="A44" s="1"/>
+      <c r="B44" s="51">
+        <v>39</v>
+      </c>
+      <c r="C44" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="D44" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E44" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="F44" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="G44" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H44" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I44" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J44" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="K44" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A45" s="1"/>
+      <c r="B45" s="39">
+        <v>40</v>
+      </c>
+      <c r="C45" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="D45" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E45" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="F45" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="G45" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H45" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I45" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J45" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K45" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" s="4" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A46" s="1"/>
+      <c r="B46" s="39">
+        <v>41</v>
+      </c>
+      <c r="C46" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="D46" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="E46" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="F46" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="G46" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H46" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I46" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J46" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K46" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" s="8" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A47" s="66"/>
+      <c r="B47" s="39">
+        <v>42</v>
+      </c>
+      <c r="C47" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="F47" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="G47" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H47" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I47" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J47" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K47" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" s="9" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A48" s="67"/>
+      <c r="B48" s="68">
+        <v>43</v>
+      </c>
+      <c r="C48" s="69" t="s">
+        <v>200</v>
+      </c>
+      <c r="D48" s="70" t="s">
+        <v>210</v>
+      </c>
+      <c r="E48" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="F48" s="70" t="s">
+        <v>212</v>
+      </c>
+      <c r="G48" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H48" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I48" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J48" s="72" t="s">
+        <v>108</v>
+      </c>
+      <c r="K48" s="73" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" ht="76.5" spans="1:11">
+      <c r="A49" s="1"/>
+      <c r="B49" s="39">
+        <v>44</v>
+      </c>
+      <c r="C49" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="D49" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="E49" s="42" t="s">
+        <v>214</v>
+      </c>
+      <c r="F49" s="53" t="s">
+        <v>215</v>
+      </c>
+      <c r="G49" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H49" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I49" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J49" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="K49" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A50" s="1"/>
+      <c r="B50" s="39">
+        <v>45</v>
+      </c>
+      <c r="C50" s="64" t="s">
+        <v>171</v>
+      </c>
+      <c r="D50" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="E50" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="F50" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="G50" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H50" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I50" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J50" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I13" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J13" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="K13" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" s="4" customFormat="1" ht="39.75" customHeight="1" spans="1:11">
-      <c r="A14" s="1"/>
-      <c r="B14" s="37">
-        <v>9</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" s="40" t="s">
+      <c r="K50" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" ht="76.5" spans="1:11">
+      <c r="A51" s="1"/>
+      <c r="B51" s="39">
+        <v>46</v>
+      </c>
+      <c r="C51" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="D51" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="E51" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="F51" s="41" t="s">
+        <v>221</v>
+      </c>
+      <c r="G51" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H51" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I51" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J51" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="K51" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A52" s="1"/>
+      <c r="B52" s="39">
+        <v>47</v>
+      </c>
+      <c r="C52" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="D52" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="E52" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="F52" s="53" t="s">
+        <v>224</v>
+      </c>
+      <c r="G52" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H52" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I52" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J52" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="K52" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" ht="51" spans="1:11">
+      <c r="A53" s="1"/>
+      <c r="B53" s="39">
+        <v>48</v>
+      </c>
+      <c r="C53" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="D53" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="E53" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="F53" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="G53" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H53" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I53" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J53" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="K53" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A54" s="1"/>
+      <c r="B54" s="39">
+        <v>49</v>
+      </c>
+      <c r="C54" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="D54" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="E54" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="F54" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="G54" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H54" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I54" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J54" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="F14" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H14" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J14" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="K14" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" s="4" customFormat="1" ht="42" customHeight="1" spans="1:11">
-      <c r="A15" s="1"/>
-      <c r="B15" s="37">
-        <v>10</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="F15" s="39" t="s">
+      <c r="K54" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" ht="76.5" spans="1:11">
+      <c r="A55" s="1"/>
+      <c r="B55" s="39">
+        <v>50</v>
+      </c>
+      <c r="C55" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="D55" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="E55" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="F55" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="G55" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H55" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I55" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J55" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="G15" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H15" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I15" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J15" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" s="4" customFormat="1" ht="40.5" customHeight="1" spans="1:11">
-      <c r="A16" s="1"/>
-      <c r="B16" s="37">
-        <v>11</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="G16" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I16" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J16" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="K16" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" s="4" customFormat="1" ht="41.25" customHeight="1" spans="1:11">
-      <c r="A17" s="1"/>
-      <c r="B17" s="45">
-        <v>12</v>
-      </c>
-      <c r="C17" s="46" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="48" t="s">
-        <v>114</v>
-      </c>
-      <c r="F17" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I17" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J17" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:11">
-      <c r="A18" s="1"/>
-      <c r="B18" s="30">
-        <v>13</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="G18" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H18" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I18" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J18" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" s="4" customFormat="1" ht="53" customHeight="1" spans="1:11">
-      <c r="A19" s="1"/>
-      <c r="B19" s="49">
-        <v>14</v>
-      </c>
-      <c r="C19" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="E19" s="52" t="s">
-        <v>120</v>
-      </c>
-      <c r="F19" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="G19" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H19" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I19" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J19" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="K19" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" s="4" customFormat="1" ht="36.75" customHeight="1" spans="1:11">
-      <c r="A20" s="1"/>
-      <c r="B20" s="37">
-        <v>15</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H20" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J20" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="K20" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" s="4" customFormat="1" ht="47" customHeight="1" spans="1:11">
-      <c r="A21" s="1"/>
-      <c r="B21" s="41">
-        <v>16</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="F21" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I21" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J21" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="K21" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" s="4" customFormat="1" ht="41.25" customHeight="1" spans="1:11">
-      <c r="A22" s="1"/>
-      <c r="B22" s="37">
-        <v>17</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="F22" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I22" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J22" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="K22" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" s="4" customFormat="1" ht="31" customHeight="1" spans="1:11">
-      <c r="A23" s="1"/>
-      <c r="B23" s="49">
-        <v>18</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="F23" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H23" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I23" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J23" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="K23" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" s="4" customFormat="1" ht="41.25" customHeight="1" spans="1:11">
-      <c r="A24" s="1"/>
-      <c r="B24" s="37">
-        <v>19</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="E24" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="F24" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="G24" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H24" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I24" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J24" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="K24" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" s="4" customFormat="1" ht="51" customHeight="1" spans="1:11">
-      <c r="A25" s="1"/>
-      <c r="B25" s="41">
-        <v>20</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="G25" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H25" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I25" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J25" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="K25" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" s="4" customFormat="1" ht="49.5" customHeight="1" spans="1:11">
-      <c r="A26" s="1"/>
-      <c r="B26" s="45">
-        <v>21</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E26" s="44" t="s">
-        <v>141</v>
-      </c>
-      <c r="F26" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H26" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="I26" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="J26" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="K26" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" s="5" customFormat="1" ht="40.5" customHeight="1" spans="1:11">
-      <c r="A27" s="54"/>
-      <c r="B27" s="30">
-        <v>22</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="F27" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="H27" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I27" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="J27" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="K27" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" s="6" customFormat="1" ht="40.5" customHeight="1" spans="1:11">
-      <c r="A28" s="55"/>
-      <c r="B28" s="49">
-        <v>23</v>
-      </c>
-      <c r="C28" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="E28" s="52" t="s">
-        <v>147</v>
-      </c>
-      <c r="F28" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="G28" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="H28" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="I28" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="J28" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="K28" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" s="4" customFormat="1" ht="52.5" customHeight="1" spans="1:11">
-      <c r="A29" s="1"/>
-      <c r="B29" s="49">
-        <v>24</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="E29" s="52" t="s">
-        <v>149</v>
-      </c>
-      <c r="F29" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="G29" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="H29" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="I29" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="J29" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="K29" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" s="4" customFormat="1" ht="52.5" customHeight="1" spans="1:11">
-      <c r="A30" s="1"/>
-      <c r="B30" s="58">
-        <v>25</v>
-      </c>
-      <c r="C30" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="D30" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="E30" s="52" t="s">
-        <v>151</v>
-      </c>
-      <c r="F30" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="G30" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="H30" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="I30" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="J30" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="K30" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:11">
-      <c r="A31" s="1"/>
-      <c r="B31" s="37">
-        <v>26</v>
-      </c>
-      <c r="C31" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" s="51" t="s">
-        <v>92</v>
-      </c>
-      <c r="E31" s="52" t="s">
-        <v>153</v>
-      </c>
-      <c r="F31" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="G31" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="H31" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="I31" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="J31" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="K31" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" s="4" customFormat="1" ht="48.75" customHeight="1" spans="1:11">
-      <c r="A32" s="1"/>
-      <c r="B32" s="49">
-        <v>27</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="F32" s="53" t="s">
-        <v>156</v>
-      </c>
-      <c r="G32" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="H32" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="I32" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="J32" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="K32" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" s="4" customFormat="1" ht="47" customHeight="1" spans="1:11">
-      <c r="A33" s="1"/>
-      <c r="B33" s="37">
-        <v>28</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="G33" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="H33" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="I33" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="J33" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="K33" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" s="4" customFormat="1" ht="48.75" customHeight="1" spans="1:11">
-      <c r="A34" s="1"/>
-      <c r="B34" s="37">
-        <v>29</v>
-      </c>
-      <c r="C34" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="D34" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="F34" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="G34" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="H34" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="I34" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="J34" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="K34" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" s="4" customFormat="1" ht="37.5" customHeight="1" spans="1:11">
-      <c r="A35" s="1"/>
-      <c r="B35" s="30">
-        <v>30</v>
-      </c>
-      <c r="C35" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D35" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="E35" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="F35" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="G35" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="H35" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="I35" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="J35" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="K35" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" s="4" customFormat="1" ht="50.25" customHeight="1" spans="1:11">
-      <c r="A36" s="1"/>
-      <c r="B36" s="49"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="36"/>
-    </row>
-    <row r="37" s="4" customFormat="1" ht="30" customHeight="1" spans="1:11">
-      <c r="A37" s="1"/>
-      <c r="B37" s="49"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="36"/>
-    </row>
-    <row r="38" s="6" customFormat="1" ht="30" customHeight="1" spans="1:11">
-      <c r="A38" s="55"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="59"/>
-      <c r="J38" s="35"/>
-      <c r="K38" s="36"/>
-    </row>
-    <row r="39" s="7" customFormat="1" ht="39" customHeight="1" spans="1:11">
-      <c r="A39" s="60"/>
-      <c r="B39" s="37"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="59"/>
-      <c r="H39" s="59"/>
-      <c r="I39" s="59"/>
-      <c r="J39" s="35"/>
-      <c r="K39" s="36"/>
-    </row>
-    <row r="40" s="4" customFormat="1" ht="38.25" customHeight="1" spans="1:11">
-      <c r="A40" s="1"/>
-      <c r="B40" s="49"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="36"/>
-    </row>
-    <row r="41" s="4" customFormat="1" ht="36.75" customHeight="1" spans="1:11">
-      <c r="A41" s="1"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="59"/>
-      <c r="H41" s="59"/>
-      <c r="I41" s="59"/>
-      <c r="J41" s="35"/>
-      <c r="K41" s="36"/>
-    </row>
-    <row r="42" s="4" customFormat="1" ht="27.75" customHeight="1" spans="1:11">
-      <c r="A42" s="1"/>
-      <c r="B42" s="49"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="59"/>
-      <c r="H42" s="59"/>
-      <c r="I42" s="59"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="36"/>
-    </row>
-    <row r="43" s="4" customFormat="1" ht="42" customHeight="1" spans="1:11">
-      <c r="A43" s="1"/>
-      <c r="B43" s="37"/>
-      <c r="C43" s="38"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="59"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="36"/>
-    </row>
-    <row r="44" s="4" customFormat="1" ht="29.25" customHeight="1" spans="1:11">
-      <c r="A44" s="1"/>
-      <c r="B44" s="37"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="59"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="59"/>
-      <c r="J44" s="35"/>
-      <c r="K44" s="36"/>
-    </row>
-    <row r="45" s="4" customFormat="1" ht="52.5" customHeight="1" spans="1:11">
-      <c r="A45" s="1"/>
-      <c r="B45" s="37"/>
-      <c r="C45" s="62"/>
-      <c r="D45" s="40"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="59"/>
-      <c r="I45" s="59"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="36"/>
-    </row>
-    <row r="46" s="4" customFormat="1" ht="29.25" customHeight="1" spans="1:11">
-      <c r="A46" s="1"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="63"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="53"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="65"/>
-      <c r="I46" s="65"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="36"/>
-    </row>
-    <row r="47" s="8" customFormat="1" ht="39" customHeight="1" spans="1:11">
-      <c r="A47" s="66"/>
-      <c r="B47" s="45"/>
-      <c r="C47" s="67"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="70"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="70"/>
-      <c r="J47" s="35"/>
-      <c r="K47" s="36"/>
-    </row>
-    <row r="49" spans="2:7">
-      <c r="B49" s="71" t="s">
-        <v>166</v>
-      </c>
-      <c r="C49" s="72"/>
-      <c r="D49" s="72"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="72"/>
-      <c r="G49" s="72"/>
+      <c r="K55" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A56" s="1"/>
+      <c r="B56" s="39">
+        <v>51</v>
+      </c>
+      <c r="C56" s="64" t="s">
+        <v>234</v>
+      </c>
+      <c r="D56" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="E56" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="F56" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="G56" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H56" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I56" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J56" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="K56" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" s="10" customFormat="1" ht="13.5" spans="1:11">
+      <c r="A57" s="74"/>
+      <c r="B57" s="75">
+        <v>52</v>
+      </c>
+      <c r="C57" s="76"/>
+      <c r="D57" s="77"/>
+      <c r="E57" s="78"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H57" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I57" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J57" s="79" t="s">
+        <v>238</v>
+      </c>
+      <c r="K57" s="80" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" ht="13.5" spans="1:11">
+      <c r="A58" s="1"/>
+      <c r="B58" s="39">
+        <v>53</v>
+      </c>
+      <c r="C58" s="63"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H58" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I58" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J58" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="K58" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" ht="13.5" spans="1:11">
+      <c r="A59" s="1"/>
+      <c r="B59" s="39">
+        <v>54</v>
+      </c>
+      <c r="C59" s="64"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H59" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I59" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J59" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="K59" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A60" s="1"/>
+      <c r="B60" s="39">
+        <v>55</v>
+      </c>
+      <c r="C60" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="D60" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E60" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="F60" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="G60" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H60" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I60" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J60" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="K60" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A61" s="1"/>
+      <c r="B61" s="39">
+        <v>56</v>
+      </c>
+      <c r="C61" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="D61" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="E61" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="F61" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="G61" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H61" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I61" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J61" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="K61" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A62" s="1"/>
+      <c r="B62" s="39">
+        <v>57</v>
+      </c>
+      <c r="C62" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="D62" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="E62" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="F62" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="G62" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H62" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I62" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J62" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="K62" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A63" s="1"/>
+      <c r="B63" s="39">
+        <v>58</v>
+      </c>
+      <c r="C63" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="D63" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E63" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="F63" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="G63" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H63" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I63" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J63" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="K63" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A64" s="1"/>
+      <c r="B64" s="39">
+        <v>59</v>
+      </c>
+      <c r="C64" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="D64" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="E64" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="F64" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="G64" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H64" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I64" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J64" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="K64" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A65" s="1"/>
+      <c r="B65" s="39">
+        <v>60</v>
+      </c>
+      <c r="C65" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="D65" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="E65" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="F65" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="G65" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H65" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I65" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J65" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="K65" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A66" s="1"/>
+      <c r="B66" s="39">
+        <v>61</v>
+      </c>
+      <c r="C66" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="D66" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E66" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="F66" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="G66" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H66" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I66" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J66" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="K66" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A67" s="1"/>
+      <c r="B67" s="39">
+        <v>62</v>
+      </c>
+      <c r="C67" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="D67" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="E67" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="F67" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="G67" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H67" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I67" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J67" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="K67" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A68" s="1"/>
+      <c r="B68" s="39">
+        <v>63</v>
+      </c>
+      <c r="C68" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="D68" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="E68" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="F68" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="G68" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="H68" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="I68" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J68" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="K68" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" spans="1:11">
+      <c r="A69" s="1"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="12"/>
+      <c r="K69" s="12"/>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="B71" s="81" t="s">
+        <v>239</v>
+      </c>
+      <c r="C71" s="82"/>
+      <c r="D71" s="82"/>
+      <c r="E71" s="82"/>
+      <c r="F71" s="82"/>
+      <c r="G71" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6342,11 +7578,19 @@
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
   </mergeCells>
-  <conditionalFormatting sqref="G6:I47">
-    <cfRule type="cellIs" dxfId="0" priority="3" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="G69:I69">
+    <cfRule type="cellIs" dxfId="0" priority="21" stopIfTrue="1" operator="equal">
       <formula>"○"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="22" stopIfTrue="1" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6:I68">
+    <cfRule type="cellIs" dxfId="0" priority="33" stopIfTrue="1" operator="equal">
+      <formula>"○"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="34" stopIfTrue="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6354,7 +7598,7 @@
     <dataValidation showInputMessage="1" showErrorMessage="1" prompt="概要设计" sqref="G5"/>
     <dataValidation showInputMessage="1" showErrorMessage="1" prompt="编码" sqref="H5"/>
     <dataValidation showInputMessage="1" showErrorMessage="1" prompt="单体测试" sqref="I5"/>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" prompt="○ ：完成&#10;△ ：进行中&#10;× ：未着手&#10;N/A：不适用" sqref="G6:I47">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" prompt="○ ：完成&#10;△ ：进行中&#10;× ：未着手&#10;N/A：不适用" sqref="G6:I34 G35:I68">
       <formula1>"○,△,×,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
+++ b/docs/第31小组_数字人交互系统_需求跟踪矩阵.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="11055" tabRatio="486" activeTab="1"/>
+    <workbookView windowWidth="24000" windowHeight="11055" tabRatio="486"/>
   </bookViews>
   <sheets>
     <sheet name="需求跟踪矩阵封面" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="243">
   <si>
     <t>密级：</t>
   </si>
@@ -344,7 +344,7 @@
     <t>机密</t>
   </si>
   <si>
-    <t>第   版</t>
+    <t>第  1 版</t>
   </si>
   <si>
     <t>分册名称：无</t>
@@ -365,16 +365,38 @@
     <t>总页数</t>
   </si>
   <si>
+    <r>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>页</t>
+    </r>
+  </si>
+  <si>
     <t>正文</t>
   </si>
   <si>
+    <t>1~3</t>
+  </si>
+  <si>
     <t>附录</t>
   </si>
   <si>
+    <t>4~8</t>
+  </si>
+  <si>
     <t>生效日期</t>
   </si>
   <si>
     <t>编制：</t>
+  </si>
+  <si>
+    <t>第31组</t>
   </si>
   <si>
     <t>审批：</t>
@@ -1067,9 +1089,6 @@
   </si>
   <si>
     <t>支持Edge TTS及OpenAI兼容语音服务，语音配置与聊天模型配置相互独立；外部配置不完整、超时或音频无效时回退Edge，仍失败时交由浏览器播报，均不可用时保留文字提示</t>
-  </si>
-  <si>
-    <t>待确认</t>
   </si>
   <si>
     <t>○：完成（通过评审或测试）   △：进行中   ×：未着手   N/A：不适用（没有此项活动）</t>
@@ -1459,18 +1478,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2325,7 +2338,7 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="38">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="38">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
@@ -2349,16 +2362,16 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="41">
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="41">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="42">
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="42">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="9" borderId="41">
+    <xf numFmtId="0" fontId="40" fillId="8" borderId="41">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="43">
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="43">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="44">
@@ -2367,85 +2380,85 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="45">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="47" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="28" fillId="0" borderId="0"/>
@@ -2482,7 +2495,7 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2497,7 +2510,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2529,29 +2541,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -2641,7 +2653,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="17" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="17" xfId="60" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2671,75 +2683,56 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="60" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="58" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="26" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="27" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="27" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="28" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" xfId="58" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="181" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2767,55 +2760,55 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="183" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="182" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="15" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="15" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2824,7 +2817,7 @@
     <xf numFmtId="182" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="184" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2858,7 +2851,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2873,28 +2866,28 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="17" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="17" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2906,34 +2899,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="15" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2960,7 +2953,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2973,7 +2966,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2991,19 +2984,19 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="22" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="22" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
@@ -3182,18 +3175,104 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>149225</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>556895</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>132715</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1450340" y="4352925"/>
+          <a:ext cx="10085070" cy="5495290"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>169545</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>157480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>27940</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2106930" y="967105"/>
+          <a:ext cx="7378700" cy="4566285"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>469265</xdr:colOff>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>55245</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>417195</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3210,16 +3289,12 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1440815" y="4103370"/>
-          <a:ext cx="10600690" cy="5777865"/>
+          <a:off x="2406650" y="1188720"/>
+          <a:ext cx="6049645" cy="4408170"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -3227,46 +3302,43 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>508635</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>450850</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133985</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>313055</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>122555</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>334645</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>90805</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPr id="2" name="图片 1"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId1"/>
+        <a:srcRect b="42088"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1800225" y="733425"/>
-          <a:ext cx="9491345" cy="5056505"/>
+          <a:off x="6908800" y="1753235"/>
+          <a:ext cx="7633335" cy="3681095"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -3274,20 +3346,20 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>203200</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>511810</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>76835</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>436245</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>55245</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3304,37 +3376,66 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2786380" y="384810"/>
-          <a:ext cx="6331585" cy="5962015"/>
+          <a:off x="1157605" y="1863725"/>
+          <a:ext cx="3153410" cy="3049270"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>65405</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>96520</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>117475</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>92075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>309880</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>124460</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>260985</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4638040" y="1873250"/>
+          <a:ext cx="3372485" cy="3045460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>479425</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>111760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>135890</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>42545</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3344,23 +3445,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip r:embed="rId3"/>
+        <a:srcRect l="7879" b="7774"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8460740" y="420370"/>
-          <a:ext cx="4765040" cy="6019165"/>
+          <a:off x="8228965" y="1892935"/>
+          <a:ext cx="2885440" cy="3007360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -4338,361 +4436,371 @@
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="8.75221238938053" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="9.87610619469027" style="166" customWidth="1"/>
-    <col min="2" max="2" width="10.3716814159292" style="166" customWidth="1"/>
-    <col min="3" max="3" width="9.87610619469027" style="166" customWidth="1"/>
-    <col min="4" max="4" width="8.75221238938053" style="166" customWidth="1"/>
-    <col min="5" max="5" width="10" style="166" customWidth="1"/>
-    <col min="6" max="6" width="9.75221238938053" style="166" customWidth="1"/>
-    <col min="7" max="7" width="9.50442477876106" style="166" customWidth="1"/>
-    <col min="8" max="8" width="16.7522123893805" style="166" customWidth="1"/>
-    <col min="9" max="16384" width="8.75221238938053" style="166" customWidth="1"/>
+    <col min="1" max="1" width="9.87610619469027" style="158" customWidth="1"/>
+    <col min="2" max="2" width="10.3716814159292" style="158" customWidth="1"/>
+    <col min="3" max="3" width="9.87610619469027" style="158" customWidth="1"/>
+    <col min="4" max="4" width="8.75221238938053" style="158" customWidth="1"/>
+    <col min="5" max="5" width="10" style="158" customWidth="1"/>
+    <col min="6" max="6" width="9.75221238938053" style="158" customWidth="1"/>
+    <col min="7" max="7" width="9.50442477876106" style="158" customWidth="1"/>
+    <col min="8" max="8" width="16.7522123893805" style="158" customWidth="1"/>
+    <col min="9" max="16384" width="8.75221238938053" style="158" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.75" customHeight="1" spans="1:8">
-      <c r="A1" s="167"/>
+      <c r="A1" s="159"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="167"/>
-    </row>
-    <row r="3" s="165" customFormat="1" ht="24" customHeight="1" spans="1:8">
-      <c r="A3" s="168" t="s">
+      <c r="A2" s="159"/>
+    </row>
+    <row r="3" s="157" customFormat="1" ht="24" customHeight="1" spans="1:8">
+      <c r="A3" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="161" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="170"/>
-      <c r="E3" s="170"/>
-      <c r="F3" s="170"/>
-      <c r="G3" s="170"/>
-      <c r="H3" s="171"/>
-    </row>
-    <row r="4" s="165" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
-      <c r="A4" s="172"/>
-      <c r="H4" s="173" t="s">
+      <c r="C3" s="162"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="163"/>
+    </row>
+    <row r="4" s="157" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
+      <c r="A4" s="164"/>
+      <c r="H4" s="165" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="165" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
-      <c r="A5" s="172" t="s">
+    <row r="5" s="157" customFormat="1" ht="23.25" customHeight="1" spans="1:8">
+      <c r="A5" s="164" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="170"/>
-      <c r="G5" s="174" t="s">
+      <c r="F5" s="162"/>
+      <c r="G5" s="166" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A6" s="175"/>
-      <c r="B6" s="176"/>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="176"/>
-    </row>
-    <row r="7" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A7" s="177"/>
-      <c r="B7" s="171"/>
-      <c r="C7" s="171"/>
-      <c r="D7" s="171"/>
-      <c r="E7" s="171"/>
-      <c r="F7" s="171"/>
-      <c r="G7" s="171"/>
-      <c r="H7" s="171"/>
-    </row>
-    <row r="8" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A8" s="177"/>
-      <c r="B8" s="171"/>
-      <c r="C8" s="171"/>
-      <c r="D8" s="171"/>
-      <c r="E8" s="171"/>
-      <c r="F8" s="171"/>
-      <c r="G8" s="171"/>
-      <c r="H8" s="171"/>
-    </row>
-    <row r="9" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A9" s="177"/>
-      <c r="B9" s="171"/>
-      <c r="C9" s="171"/>
-      <c r="D9" s="171"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="171"/>
-      <c r="G9" s="171"/>
-      <c r="H9" s="171"/>
-    </row>
-    <row r="10" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A10" s="177"/>
-      <c r="B10" s="171"/>
-      <c r="C10" s="171"/>
-      <c r="D10" s="171"/>
-      <c r="E10" s="171"/>
-      <c r="F10" s="171"/>
-      <c r="G10" s="171"/>
-      <c r="H10" s="171"/>
-    </row>
-    <row r="11" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A11" s="177"/>
-      <c r="B11" s="171"/>
-      <c r="C11" s="171"/>
-      <c r="D11" s="171"/>
-      <c r="E11" s="171"/>
-      <c r="F11" s="171"/>
-      <c r="G11" s="171"/>
-      <c r="H11" s="171"/>
-    </row>
-    <row r="12" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A12" s="177"/>
-      <c r="B12" s="171"/>
-      <c r="C12" s="171"/>
-      <c r="D12" s="171"/>
-      <c r="E12" s="171"/>
-      <c r="F12" s="171"/>
-      <c r="G12" s="171"/>
-      <c r="H12" s="171"/>
-    </row>
-    <row r="13" s="165" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
-      <c r="A13" s="178" t="s">
+      <c r="A6" s="167"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="168"/>
+      <c r="D6" s="168"/>
+      <c r="E6" s="168"/>
+    </row>
+    <row r="7" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A7" s="169"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="163"/>
+      <c r="D7" s="163"/>
+      <c r="E7" s="163"/>
+      <c r="F7" s="163"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="163"/>
+    </row>
+    <row r="8" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A8" s="169"/>
+      <c r="B8" s="163"/>
+      <c r="C8" s="163"/>
+      <c r="D8" s="163"/>
+      <c r="E8" s="163"/>
+      <c r="F8" s="163"/>
+      <c r="G8" s="163"/>
+      <c r="H8" s="163"/>
+    </row>
+    <row r="9" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A9" s="169"/>
+      <c r="B9" s="163"/>
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="163"/>
+      <c r="G9" s="163"/>
+      <c r="H9" s="163"/>
+    </row>
+    <row r="10" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A10" s="169"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="163"/>
+      <c r="G10" s="163"/>
+      <c r="H10" s="163"/>
+    </row>
+    <row r="11" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A11" s="169"/>
+      <c r="B11" s="163"/>
+      <c r="C11" s="163"/>
+      <c r="D11" s="163"/>
+      <c r="E11" s="163"/>
+      <c r="F11" s="163"/>
+      <c r="G11" s="163"/>
+      <c r="H11" s="163"/>
+    </row>
+    <row r="12" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A12" s="169"/>
+      <c r="B12" s="163"/>
+      <c r="C12" s="163"/>
+      <c r="D12" s="163"/>
+      <c r="E12" s="163"/>
+      <c r="F12" s="163"/>
+      <c r="G12" s="163"/>
+      <c r="H12" s="163"/>
+    </row>
+    <row r="13" s="157" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
+      <c r="A13" s="170" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A14" s="177"/>
-      <c r="B14" s="179"/>
-      <c r="C14" s="171"/>
-      <c r="D14" s="171"/>
-      <c r="E14" s="171"/>
-      <c r="F14" s="171"/>
-      <c r="G14" s="171"/>
-      <c r="H14" s="171"/>
-    </row>
-    <row r="15" s="165" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
-      <c r="A15" s="180" t="s">
+    <row r="14" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A14" s="169"/>
+      <c r="B14" s="171"/>
+      <c r="C14" s="163"/>
+      <c r="D14" s="163"/>
+      <c r="E14" s="163"/>
+      <c r="F14" s="163"/>
+      <c r="G14" s="163"/>
+      <c r="H14" s="163"/>
+    </row>
+    <row r="15" s="157" customFormat="1" ht="46.5" customHeight="1" spans="1:8">
+      <c r="A15" s="172" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A16" s="177"/>
-      <c r="B16" s="171"/>
-      <c r="C16" s="171"/>
-      <c r="D16" s="171"/>
-      <c r="E16" s="171"/>
-      <c r="F16" s="171"/>
-      <c r="G16" s="171"/>
-      <c r="H16" s="171"/>
-    </row>
-    <row r="17" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A17" s="177"/>
-      <c r="B17" s="171"/>
-      <c r="C17" s="171"/>
-      <c r="D17" s="171"/>
-      <c r="E17" s="171"/>
-      <c r="F17" s="171"/>
-      <c r="G17" s="171"/>
-      <c r="H17" s="171"/>
-    </row>
-    <row r="18" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A18" s="177"/>
-      <c r="B18" s="171"/>
-      <c r="C18" s="171"/>
-      <c r="D18" s="171"/>
-      <c r="E18" s="171"/>
-      <c r="F18" s="171"/>
-      <c r="G18" s="171"/>
-      <c r="H18" s="171"/>
-    </row>
-    <row r="19" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A19" s="177"/>
-      <c r="B19" s="171"/>
-      <c r="C19" s="171"/>
-      <c r="D19" s="171"/>
-      <c r="E19" s="171"/>
-      <c r="F19" s="171"/>
-      <c r="G19" s="171"/>
-      <c r="H19" s="171"/>
-    </row>
-    <row r="20" s="165" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A20" s="181" t="s">
+    <row r="16" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A16" s="169"/>
+      <c r="B16" s="163"/>
+      <c r="C16" s="163"/>
+      <c r="D16" s="163"/>
+      <c r="E16" s="163"/>
+      <c r="F16" s="163"/>
+      <c r="G16" s="163"/>
+      <c r="H16" s="163"/>
+    </row>
+    <row r="17" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A17" s="169"/>
+      <c r="B17" s="163"/>
+      <c r="C17" s="163"/>
+      <c r="D17" s="163"/>
+      <c r="E17" s="163"/>
+      <c r="F17" s="163"/>
+      <c r="G17" s="163"/>
+      <c r="H17" s="163"/>
+    </row>
+    <row r="18" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A18" s="169"/>
+      <c r="B18" s="163"/>
+      <c r="C18" s="163"/>
+      <c r="D18" s="163"/>
+      <c r="E18" s="163"/>
+      <c r="F18" s="163"/>
+      <c r="G18" s="163"/>
+      <c r="H18" s="163"/>
+    </row>
+    <row r="19" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A19" s="169"/>
+      <c r="B19" s="163"/>
+      <c r="C19" s="163"/>
+      <c r="D19" s="163"/>
+      <c r="E19" s="163"/>
+      <c r="F19" s="163"/>
+      <c r="G19" s="163"/>
+      <c r="H19" s="163"/>
+    </row>
+    <row r="20" s="157" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
+      <c r="A20" s="173" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A21" s="177"/>
-      <c r="B21" s="171"/>
-      <c r="C21" s="171"/>
-      <c r="D21" s="171"/>
-      <c r="E21" s="171"/>
-      <c r="F21" s="171"/>
-      <c r="G21" s="171"/>
-      <c r="H21" s="171"/>
-    </row>
-    <row r="22" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A22" s="177"/>
-      <c r="B22" s="171"/>
-      <c r="C22" s="171"/>
-      <c r="D22" s="171"/>
-      <c r="E22" s="171"/>
-      <c r="F22" s="171"/>
-      <c r="G22" s="171"/>
-      <c r="H22" s="171"/>
-    </row>
-    <row r="23" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A23" s="177"/>
-      <c r="B23" s="171"/>
-      <c r="C23" s="171"/>
-      <c r="D23" s="171"/>
-      <c r="E23" s="171"/>
-      <c r="F23" s="171"/>
-      <c r="G23" s="171"/>
-      <c r="H23" s="171"/>
-    </row>
-    <row r="24" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A24" s="177"/>
-      <c r="B24" s="171"/>
-      <c r="C24" s="171"/>
-      <c r="D24" s="171"/>
-      <c r="E24" s="171"/>
-      <c r="F24" s="171"/>
-      <c r="G24" s="171"/>
-      <c r="H24" s="171"/>
-    </row>
-    <row r="25" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A25" s="177"/>
-      <c r="B25" s="171"/>
-      <c r="C25" s="171"/>
-      <c r="D25" s="171"/>
-      <c r="E25" s="171"/>
-      <c r="F25" s="171"/>
-      <c r="G25" s="171"/>
-      <c r="H25" s="171"/>
-    </row>
-    <row r="26" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A26" s="177"/>
-      <c r="B26" s="171"/>
-      <c r="C26" s="171"/>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="171"/>
-      <c r="G26" s="171"/>
-      <c r="H26" s="171"/>
-    </row>
-    <row r="27" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A27" s="177"/>
-      <c r="B27" s="171"/>
-      <c r="C27" s="171"/>
-      <c r="D27" s="171"/>
-      <c r="E27" s="171"/>
-      <c r="F27" s="171"/>
-      <c r="G27" s="171"/>
-      <c r="H27" s="171"/>
-    </row>
-    <row r="28" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A28" s="177"/>
-      <c r="B28" s="171"/>
-      <c r="C28" s="171"/>
-      <c r="D28" s="171"/>
-      <c r="E28" s="171"/>
-      <c r="F28" s="171"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="171"/>
-    </row>
-    <row r="29" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A29" s="177"/>
-      <c r="B29" s="171"/>
-      <c r="C29" s="171"/>
-      <c r="D29" s="171"/>
-      <c r="E29" s="171"/>
-      <c r="F29" s="171"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="171"/>
-    </row>
-    <row r="30" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A30" s="177"/>
-      <c r="B30" s="171"/>
-      <c r="C30" s="171"/>
-      <c r="D30" s="171"/>
-      <c r="E30" s="171"/>
-      <c r="F30" s="171"/>
-      <c r="G30" s="171"/>
-      <c r="H30" s="171"/>
-    </row>
-    <row r="31" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A31" s="177"/>
-      <c r="B31" s="171"/>
-      <c r="C31" s="171"/>
-      <c r="D31" s="171"/>
-      <c r="E31" s="171"/>
-      <c r="F31" s="171"/>
-      <c r="G31" s="171"/>
-      <c r="H31" s="171"/>
-    </row>
-    <row r="32" s="165" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A32" s="182"/>
-    </row>
-    <row r="33" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A33" s="177"/>
-      <c r="B33" s="171"/>
-      <c r="C33" s="171"/>
-      <c r="D33" s="171"/>
-      <c r="E33" s="171"/>
-      <c r="F33" s="171"/>
-      <c r="G33" s="171"/>
-      <c r="H33" s="171"/>
-    </row>
-    <row r="34" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A34" s="177"/>
-      <c r="B34" s="171"/>
-      <c r="C34" s="171"/>
-      <c r="D34" s="171"/>
-      <c r="E34" s="171"/>
-      <c r="F34" s="171"/>
-      <c r="G34" s="171"/>
-      <c r="H34" s="171"/>
-    </row>
-    <row r="35" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A35" s="177"/>
-      <c r="B35" s="171"/>
-      <c r="C35" s="171"/>
-      <c r="D35" s="171"/>
-      <c r="E35" s="171"/>
-      <c r="F35" s="171"/>
-      <c r="G35" s="171"/>
-      <c r="H35" s="171"/>
-    </row>
-    <row r="36" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A36" s="183" t="s">
+    <row r="21" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A21" s="169"/>
+      <c r="B21" s="163"/>
+      <c r="C21" s="163"/>
+      <c r="D21" s="163"/>
+      <c r="E21" s="163"/>
+      <c r="F21" s="163"/>
+      <c r="G21" s="163"/>
+      <c r="H21" s="163"/>
+    </row>
+    <row r="22" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A22" s="169"/>
+      <c r="B22" s="163"/>
+      <c r="C22" s="163"/>
+      <c r="D22" s="163"/>
+      <c r="E22" s="163"/>
+      <c r="F22" s="163"/>
+      <c r="G22" s="163"/>
+      <c r="H22" s="163"/>
+    </row>
+    <row r="23" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A23" s="169"/>
+      <c r="B23" s="163"/>
+      <c r="C23" s="163"/>
+      <c r="D23" s="163"/>
+      <c r="E23" s="163"/>
+      <c r="F23" s="163"/>
+      <c r="G23" s="163"/>
+      <c r="H23" s="163"/>
+    </row>
+    <row r="24" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A24" s="169"/>
+      <c r="B24" s="163"/>
+      <c r="C24" s="163"/>
+      <c r="D24" s="163"/>
+      <c r="E24" s="163"/>
+      <c r="F24" s="163"/>
+      <c r="G24" s="163"/>
+      <c r="H24" s="163"/>
+    </row>
+    <row r="25" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A25" s="169"/>
+      <c r="B25" s="163"/>
+      <c r="C25" s="163"/>
+      <c r="D25" s="163"/>
+      <c r="E25" s="163"/>
+      <c r="F25" s="163"/>
+      <c r="G25" s="163"/>
+      <c r="H25" s="163"/>
+    </row>
+    <row r="26" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A26" s="169"/>
+      <c r="B26" s="163"/>
+      <c r="C26" s="163"/>
+      <c r="D26" s="163"/>
+      <c r="E26" s="163"/>
+      <c r="F26" s="163"/>
+      <c r="G26" s="163"/>
+      <c r="H26" s="163"/>
+    </row>
+    <row r="27" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A27" s="169"/>
+      <c r="B27" s="163"/>
+      <c r="C27" s="163"/>
+      <c r="D27" s="163"/>
+      <c r="E27" s="163"/>
+      <c r="F27" s="163"/>
+      <c r="G27" s="163"/>
+      <c r="H27" s="163"/>
+    </row>
+    <row r="28" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A28" s="169"/>
+      <c r="B28" s="163"/>
+      <c r="C28" s="163"/>
+      <c r="D28" s="163"/>
+      <c r="E28" s="163"/>
+      <c r="F28" s="163"/>
+      <c r="G28" s="163"/>
+      <c r="H28" s="163"/>
+    </row>
+    <row r="29" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A29" s="169"/>
+      <c r="B29" s="163"/>
+      <c r="C29" s="163"/>
+      <c r="D29" s="163"/>
+      <c r="E29" s="163"/>
+      <c r="F29" s="163"/>
+      <c r="G29" s="163"/>
+      <c r="H29" s="163"/>
+    </row>
+    <row r="30" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A30" s="169"/>
+      <c r="B30" s="163"/>
+      <c r="C30" s="163"/>
+      <c r="D30" s="163"/>
+      <c r="E30" s="163"/>
+      <c r="F30" s="163"/>
+      <c r="G30" s="163"/>
+      <c r="H30" s="163"/>
+    </row>
+    <row r="31" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A31" s="169"/>
+      <c r="B31" s="163"/>
+      <c r="C31" s="163"/>
+      <c r="D31" s="163"/>
+      <c r="E31" s="163"/>
+      <c r="F31" s="163"/>
+      <c r="G31" s="163"/>
+      <c r="H31" s="163"/>
+    </row>
+    <row r="32" s="157" customFormat="1" ht="22.5" customHeight="1" spans="1:8">
+      <c r="A32" s="174"/>
+    </row>
+    <row r="33" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A33" s="169"/>
+      <c r="B33" s="163"/>
+      <c r="C33" s="163"/>
+      <c r="D33" s="163"/>
+      <c r="E33" s="163"/>
+      <c r="F33" s="163"/>
+      <c r="G33" s="163"/>
+      <c r="H33" s="163"/>
+    </row>
+    <row r="34" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A34" s="169"/>
+      <c r="B34" s="163"/>
+      <c r="C34" s="163"/>
+      <c r="D34" s="163"/>
+      <c r="E34" s="163"/>
+      <c r="F34" s="163"/>
+      <c r="G34" s="163"/>
+      <c r="H34" s="163"/>
+    </row>
+    <row r="35" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A35" s="169"/>
+      <c r="B35" s="163"/>
+      <c r="C35" s="163"/>
+      <c r="D35" s="163"/>
+      <c r="E35" s="163"/>
+      <c r="F35" s="163"/>
+      <c r="G35" s="163"/>
+      <c r="H35" s="163"/>
+    </row>
+    <row r="36" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A36" s="175" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="184"/>
-      <c r="C36" s="183" t="s">
+      <c r="B36" s="176" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="184"/>
-      <c r="E36" s="183" t="s">
+      <c r="C36" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="185"/>
-      <c r="G36" s="183" t="s">
+      <c r="D36" s="177" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="186"/>
-    </row>
-    <row r="37" s="165" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A37" s="187" t="s">
+      <c r="E36" s="175" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="188"/>
-      <c r="C37" s="189"/>
-      <c r="D37" s="190"/>
-      <c r="E37" s="187" t="s">
+      <c r="F36" s="177" t="s">
         <v>13</v>
       </c>
-      <c r="F37" s="191"/>
-      <c r="G37" s="189"/>
-      <c r="H37" s="190"/>
+      <c r="G36" s="175" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="178">
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="37" s="157" customFormat="1" ht="15.75" customHeight="1" spans="1:8">
+      <c r="A37" s="179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="181"/>
+      <c r="D37" s="182"/>
+      <c r="E37" s="179" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="183"/>
+      <c r="G37" s="181"/>
+      <c r="H37" s="182"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="167"/>
+      <c r="A38" s="159"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4720,665 +4828,665 @@
   <dimension ref="B1:P30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="0.876106194690266" style="89" customWidth="1"/>
-    <col min="2" max="2" width="3.3716814159292" style="89" customWidth="1"/>
-    <col min="3" max="3" width="10.7522123893805" style="90" customWidth="1"/>
-    <col min="4" max="4" width="23.3716814159292" style="89" customWidth="1"/>
-    <col min="5" max="5" width="9.55752212389381" style="89" customWidth="1"/>
-    <col min="6" max="6" width="12.7522123893805" style="89" customWidth="1"/>
-    <col min="7" max="7" width="9.3716814159292" style="89" customWidth="1"/>
-    <col min="8" max="8" width="6.87610619469027" style="89" customWidth="1"/>
-    <col min="9" max="10" width="6.87610619469027" style="88" customWidth="1"/>
-    <col min="11" max="13" width="6.87610619469027" style="89" customWidth="1"/>
-    <col min="14" max="14" width="36.1150442477876" style="89" customWidth="1"/>
-    <col min="15" max="15" width="27.4159292035398" style="89" customWidth="1"/>
-    <col min="16" max="16" width="12" style="89" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="89" customWidth="1"/>
+    <col min="1" max="1" width="0.876106194690266" style="81" customWidth="1"/>
+    <col min="2" max="2" width="3.3716814159292" style="81" customWidth="1"/>
+    <col min="3" max="3" width="10.7522123893805" style="82" customWidth="1"/>
+    <col min="4" max="4" width="23.3716814159292" style="81" customWidth="1"/>
+    <col min="5" max="5" width="9.55752212389381" style="81" customWidth="1"/>
+    <col min="6" max="6" width="12.7522123893805" style="81" customWidth="1"/>
+    <col min="7" max="7" width="9.3716814159292" style="81" customWidth="1"/>
+    <col min="8" max="8" width="6.87610619469027" style="81" customWidth="1"/>
+    <col min="9" max="10" width="6.87610619469027" style="80" customWidth="1"/>
+    <col min="11" max="13" width="6.87610619469027" style="81" customWidth="1"/>
+    <col min="14" max="14" width="36.1150442477876" style="81" customWidth="1"/>
+    <col min="15" max="15" width="27.4159292035398" style="81" customWidth="1"/>
+    <col min="16" max="16" width="12" style="81" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="81" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="83" customFormat="1" ht="29.25" customHeight="1" spans="2:16">
-      <c r="B1" s="91" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="93"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-    </row>
-    <row r="2" s="84" customFormat="1" ht="24.75" customHeight="1" spans="2:16">
-      <c r="B2" s="94" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="95" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="95" t="s">
+    <row r="1" s="75" customFormat="1" ht="29.25" customHeight="1" spans="2:16">
+      <c r="B1" s="83" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+    </row>
+    <row r="2" s="76" customFormat="1" ht="24.75" customHeight="1" spans="2:16">
+      <c r="B2" s="86" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="87" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="87" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="87" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="87" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="87" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="87" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="87" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="87" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="87" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="88" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="89" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" s="77" customFormat="1" ht="14.25" customHeight="1" spans="2:16">
+      <c r="B3" s="90">
+        <v>1</v>
+      </c>
+      <c r="C3" s="91" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="93" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="95" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="94">
+        <v>0</v>
+      </c>
+      <c r="I3" s="94">
         <v>17</v>
       </c>
-      <c r="E2" s="95" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="95" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="95" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="95" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="95" t="s">
+      <c r="J3" s="94">
+        <v>0</v>
+      </c>
+      <c r="K3" s="94">
+        <v>0</v>
+      </c>
+      <c r="L3" s="96">
+        <v>17</v>
+      </c>
+      <c r="M3" s="97" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="98" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="98" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="99">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B4" s="100">
+        <v>2</v>
+      </c>
+      <c r="C4" s="101">
+        <v>46272</v>
+      </c>
+      <c r="D4" s="102" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="103" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="104" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="105">
+        <v>17</v>
+      </c>
+      <c r="I4" s="106">
         <v>22</v>
       </c>
-      <c r="J2" s="95" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="95" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="95" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="95" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="96" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="96" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="97" t="s">
+      <c r="J4" s="106">
+        <v>0</v>
+      </c>
+      <c r="K4" s="106">
+        <v>0</v>
+      </c>
+      <c r="L4" s="96">
+        <v>22</v>
+      </c>
+      <c r="M4" s="107">
+        <v>0.2941</v>
+      </c>
+      <c r="N4" s="98" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" s="98" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" s="108">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="5" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B5" s="100">
+        <v>3</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="102" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="103" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="106" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="104" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="105">
+        <v>22</v>
+      </c>
+      <c r="I5" s="106">
+        <v>0</v>
+      </c>
+      <c r="J5" s="106">
+        <v>0</v>
+      </c>
+      <c r="K5" s="106">
+        <v>1</v>
+      </c>
+      <c r="L5" s="96">
+        <v>22</v>
+      </c>
+      <c r="M5" s="107">
+        <v>0.045</v>
+      </c>
+      <c r="N5" s="104" t="s">
+        <v>51</v>
+      </c>
+      <c r="O5" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="P5" s="108">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" s="77" customFormat="1" ht="13" customHeight="1" spans="2:16">
+      <c r="B6" s="110">
+        <v>4</v>
+      </c>
+      <c r="C6" s="111">
+        <v>46283</v>
+      </c>
+      <c r="D6" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="113" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="114" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="115" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="116">
+        <v>22</v>
+      </c>
+      <c r="I6" s="114">
+        <v>8</v>
+      </c>
+      <c r="J6" s="114">
+        <v>0</v>
+      </c>
+      <c r="K6" s="114">
+        <v>3</v>
+      </c>
+      <c r="L6" s="117">
+        <v>30</v>
+      </c>
+      <c r="M6" s="118">
+        <v>0.5</v>
+      </c>
+      <c r="N6" s="115" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" s="115" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" s="119">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B7" s="100">
+        <v>5</v>
+      </c>
+      <c r="C7" s="111">
+        <v>46303</v>
+      </c>
+      <c r="D7" s="102" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="103" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="104" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="105">
+        <v>30</v>
+      </c>
+      <c r="I7" s="106">
+        <v>0</v>
+      </c>
+      <c r="J7" s="106">
+        <v>1</v>
+      </c>
+      <c r="K7" s="106">
+        <v>0</v>
+      </c>
+      <c r="L7" s="96">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" s="85" customFormat="1" ht="14.25" customHeight="1" spans="2:16">
-      <c r="B3" s="98">
-        <v>1</v>
-      </c>
-      <c r="C3" s="99" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="102" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="103" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="102">
-        <v>0</v>
-      </c>
-      <c r="I3" s="102">
-        <v>17</v>
-      </c>
-      <c r="J3" s="102">
-        <v>0</v>
-      </c>
-      <c r="K3" s="102">
-        <v>0</v>
-      </c>
-      <c r="L3" s="104">
-        <v>17</v>
-      </c>
-      <c r="M3" s="105" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3" s="106" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" s="106" t="s">
-        <v>37</v>
-      </c>
-      <c r="P3" s="107">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="4" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B4" s="108">
-        <v>2</v>
-      </c>
-      <c r="C4" s="109">
-        <v>46272</v>
-      </c>
-      <c r="D4" s="110" t="s">
+      <c r="M7" s="107">
+        <v>0.033</v>
+      </c>
+      <c r="N7" s="115" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7" s="104" t="s">
+        <v>62</v>
+      </c>
+      <c r="P7" s="108">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B8" s="100">
+        <v>6</v>
+      </c>
+      <c r="C8" s="120">
+        <v>46318</v>
+      </c>
+      <c r="D8" s="121" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="122" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="124" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="111" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="102" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="112" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="113">
-        <v>17</v>
-      </c>
-      <c r="I4" s="114">
-        <v>22</v>
-      </c>
-      <c r="J4" s="114">
-        <v>0</v>
-      </c>
-      <c r="K4" s="114">
-        <v>0</v>
-      </c>
-      <c r="L4" s="104">
-        <v>22</v>
-      </c>
-      <c r="M4" s="115">
-        <v>0.2941</v>
-      </c>
-      <c r="N4" s="106" t="s">
-        <v>41</v>
-      </c>
-      <c r="O4" s="106" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" s="116">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="5" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B5" s="108">
-        <v>3</v>
-      </c>
-      <c r="C5" s="117" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="110" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="111" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="114" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="112" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="113">
-        <v>22</v>
-      </c>
-      <c r="I5" s="114">
-        <v>0</v>
-      </c>
-      <c r="J5" s="114">
-        <v>0</v>
-      </c>
-      <c r="K5" s="114">
-        <v>1</v>
-      </c>
-      <c r="L5" s="104">
-        <v>22</v>
-      </c>
-      <c r="M5" s="115">
-        <v>0.045</v>
-      </c>
-      <c r="N5" s="112" t="s">
-        <v>47</v>
-      </c>
-      <c r="O5" s="112" t="s">
-        <v>48</v>
-      </c>
-      <c r="P5" s="116">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="6" s="85" customFormat="1" ht="13" customHeight="1" spans="2:16">
-      <c r="B6" s="118">
-        <v>4</v>
-      </c>
-      <c r="C6" s="119">
-        <v>46280</v>
-      </c>
-      <c r="D6" s="120" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="121" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="122" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="123" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="124">
-        <v>22</v>
-      </c>
-      <c r="I6" s="122">
-        <v>8</v>
-      </c>
-      <c r="J6" s="122">
-        <v>0</v>
-      </c>
-      <c r="K6" s="122">
-        <v>3</v>
-      </c>
-      <c r="L6" s="125">
-        <v>30</v>
-      </c>
-      <c r="M6" s="126">
-        <v>0.5</v>
-      </c>
-      <c r="N6" s="123" t="s">
-        <v>52</v>
-      </c>
-      <c r="O6" s="123" t="s">
-        <v>53</v>
-      </c>
-      <c r="P6" s="127">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B7" s="108">
-        <v>5</v>
-      </c>
-      <c r="C7" s="119">
-        <v>46294</v>
-      </c>
-      <c r="D7" s="110" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="111" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="114" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="112" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="113">
-        <v>30</v>
-      </c>
-      <c r="I7" s="114">
-        <v>0</v>
-      </c>
-      <c r="J7" s="114">
-        <v>1</v>
-      </c>
-      <c r="K7" s="114">
-        <v>0</v>
-      </c>
-      <c r="L7" s="104">
-        <v>29</v>
-      </c>
-      <c r="M7" s="115">
-        <v>0.033</v>
-      </c>
-      <c r="N7" s="123" t="s">
-        <v>57</v>
-      </c>
-      <c r="O7" s="112" t="s">
-        <v>58</v>
-      </c>
-      <c r="P7" s="116">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="8" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B8" s="108">
-        <v>6</v>
-      </c>
-      <c r="C8" s="128">
-        <v>46303</v>
-      </c>
-      <c r="D8" s="129" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="130" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="131" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="132" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="133">
+      <c r="H8" s="125">
         <f>L7</f>
         <v>29</v>
       </c>
-      <c r="I8" s="131">
+      <c r="I8" s="123">
         <v>21</v>
       </c>
-      <c r="J8" s="131">
+      <c r="J8" s="123">
         <v>0</v>
       </c>
-      <c r="K8" s="131">
+      <c r="K8" s="123">
         <v>7</v>
       </c>
-      <c r="L8" s="134">
+      <c r="L8" s="126">
         <f>H8+I8-J8</f>
         <v>50</v>
       </c>
-      <c r="M8" s="135">
+      <c r="M8" s="127">
         <f>(I8+J8+K8)/H8</f>
         <v>0.96551724137931</v>
       </c>
-      <c r="N8" s="123" t="s">
-        <v>62</v>
-      </c>
-      <c r="O8" s="136" t="s">
-        <v>63</v>
-      </c>
-      <c r="P8" s="137">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="9" s="86" customFormat="1" ht="12" customHeight="1" spans="2:16">
-      <c r="B9" s="138">
+      <c r="N8" s="115" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" s="128" t="s">
+        <v>67</v>
+      </c>
+      <c r="P8" s="129">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="9" s="78" customFormat="1" ht="12" customHeight="1" spans="2:16">
+      <c r="B9" s="130">
         <v>7</v>
       </c>
-      <c r="C9" s="139"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="140"/>
-      <c r="F9" s="141"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="102"/>
-      <c r="I9" s="141"/>
-      <c r="J9" s="141"/>
-      <c r="K9" s="141"/>
-      <c r="L9" s="104"/>
-      <c r="M9" s="115"/>
-      <c r="N9" s="142"/>
-      <c r="O9" s="142"/>
-      <c r="P9" s="143"/>
-    </row>
-    <row r="10" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B10" s="108">
+      <c r="C9" s="131"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="107"/>
+      <c r="N9" s="134"/>
+      <c r="O9" s="134"/>
+      <c r="P9" s="135"/>
+    </row>
+    <row r="10" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B10" s="100">
         <v>8</v>
       </c>
-      <c r="C10" s="144"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="114"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="102"/>
-      <c r="I10" s="114"/>
-      <c r="J10" s="114"/>
-      <c r="K10" s="114"/>
-      <c r="L10" s="104"/>
-      <c r="M10" s="115"/>
-      <c r="N10" s="142"/>
-      <c r="O10" s="145"/>
-      <c r="P10" s="143"/>
-    </row>
-    <row r="11" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B11" s="108">
+      <c r="C10" s="136"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="106"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="106"/>
+      <c r="K10" s="106"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="107"/>
+      <c r="N10" s="134"/>
+      <c r="O10" s="137"/>
+      <c r="P10" s="135"/>
+    </row>
+    <row r="11" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B11" s="100">
         <v>9</v>
       </c>
-      <c r="C11" s="144"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="111"/>
-      <c r="F11" s="114"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
-      <c r="K11" s="114"/>
-      <c r="L11" s="104"/>
-      <c r="M11" s="115"/>
-      <c r="N11" s="142"/>
-      <c r="O11" s="145"/>
-      <c r="P11" s="143"/>
-    </row>
-    <row r="12" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B12" s="108">
+      <c r="C11" s="136"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="106"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="106"/>
+      <c r="J11" s="106"/>
+      <c r="K11" s="106"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="107"/>
+      <c r="N11" s="134"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="135"/>
+    </row>
+    <row r="12" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B12" s="100">
         <v>10</v>
       </c>
-      <c r="C12" s="144"/>
-      <c r="D12" s="110"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="114"/>
-      <c r="G12" s="112"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="114"/>
-      <c r="J12" s="114"/>
-      <c r="K12" s="114"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="115"/>
-      <c r="N12" s="142"/>
-      <c r="O12" s="145"/>
-      <c r="P12" s="143"/>
-    </row>
-    <row r="13" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B13" s="108">
+      <c r="C12" s="136"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="106"/>
+      <c r="J12" s="106"/>
+      <c r="K12" s="106"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="107"/>
+      <c r="N12" s="134"/>
+      <c r="O12" s="137"/>
+      <c r="P12" s="135"/>
+    </row>
+    <row r="13" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B13" s="100">
         <v>11</v>
       </c>
-      <c r="C13" s="146"/>
-      <c r="D13" s="147"/>
-      <c r="E13" s="148"/>
-      <c r="F13" s="149"/>
-      <c r="G13" s="150"/>
-      <c r="H13" s="151"/>
-      <c r="I13" s="149"/>
-      <c r="J13" s="149"/>
-      <c r="K13" s="149"/>
-      <c r="L13" s="152"/>
-      <c r="M13" s="153"/>
-      <c r="N13" s="154"/>
-      <c r="O13" s="155"/>
-      <c r="P13" s="156"/>
-    </row>
-    <row r="14" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B14" s="108">
+      <c r="C13" s="138"/>
+      <c r="D13" s="139"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="141"/>
+      <c r="G13" s="142"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="141"/>
+      <c r="J13" s="141"/>
+      <c r="K13" s="141"/>
+      <c r="L13" s="144"/>
+      <c r="M13" s="145"/>
+      <c r="N13" s="146"/>
+      <c r="O13" s="147"/>
+      <c r="P13" s="148"/>
+    </row>
+    <row r="14" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B14" s="100">
         <v>12</v>
       </c>
-      <c r="C14" s="146"/>
-      <c r="D14" s="147"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="149"/>
-      <c r="G14" s="150"/>
-      <c r="H14" s="151"/>
-      <c r="I14" s="149"/>
-      <c r="J14" s="149"/>
-      <c r="K14" s="149"/>
-      <c r="L14" s="152"/>
-      <c r="M14" s="153"/>
-      <c r="N14" s="155"/>
-      <c r="O14" s="155"/>
-      <c r="P14" s="156"/>
-    </row>
-    <row r="15" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B15" s="108">
+      <c r="C14" s="138"/>
+      <c r="D14" s="139"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="141"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="141"/>
+      <c r="J14" s="141"/>
+      <c r="K14" s="141"/>
+      <c r="L14" s="144"/>
+      <c r="M14" s="145"/>
+      <c r="N14" s="147"/>
+      <c r="O14" s="147"/>
+      <c r="P14" s="148"/>
+    </row>
+    <row r="15" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B15" s="100">
         <v>13</v>
       </c>
-      <c r="C15" s="117"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="112"/>
-      <c r="H15" s="113"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="114"/>
-      <c r="K15" s="114"/>
-      <c r="L15" s="104"/>
-      <c r="M15" s="115"/>
-      <c r="N15" s="157"/>
-      <c r="O15" s="157"/>
-      <c r="P15" s="158"/>
-    </row>
-    <row r="16" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B16" s="108">
+      <c r="C15" s="109"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="106"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="96"/>
+      <c r="M15" s="107"/>
+      <c r="N15" s="149"/>
+      <c r="O15" s="149"/>
+      <c r="P15" s="150"/>
+    </row>
+    <row r="16" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B16" s="100">
         <v>14</v>
       </c>
-      <c r="C16" s="117"/>
-      <c r="D16" s="110"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="114"/>
-      <c r="G16" s="112"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="114"/>
-      <c r="J16" s="114"/>
-      <c r="K16" s="114"/>
-      <c r="L16" s="104"/>
-      <c r="M16" s="115"/>
-      <c r="N16" s="157"/>
-      <c r="O16" s="157"/>
-      <c r="P16" s="158"/>
-    </row>
-    <row r="17" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B17" s="108">
+      <c r="C16" s="109"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="106"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="107"/>
+      <c r="N16" s="149"/>
+      <c r="O16" s="149"/>
+      <c r="P16" s="150"/>
+    </row>
+    <row r="17" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B17" s="100">
         <v>15</v>
       </c>
-      <c r="C17" s="117"/>
-      <c r="D17" s="110"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="112"/>
-      <c r="H17" s="113"/>
-      <c r="I17" s="114"/>
-      <c r="J17" s="114"/>
-      <c r="K17" s="114"/>
-      <c r="L17" s="104"/>
-      <c r="M17" s="115"/>
-      <c r="N17" s="159"/>
-      <c r="O17" s="159"/>
-      <c r="P17" s="158"/>
-    </row>
-    <row r="18" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B18" s="108">
+      <c r="C17" s="109"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="105"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="107"/>
+      <c r="N17" s="151"/>
+      <c r="O17" s="151"/>
+      <c r="P17" s="150"/>
+    </row>
+    <row r="18" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B18" s="100">
         <v>16</v>
       </c>
-      <c r="C18" s="117"/>
-      <c r="D18" s="110"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="114"/>
-      <c r="G18" s="112"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="114"/>
-      <c r="J18" s="114"/>
-      <c r="K18" s="114"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="115"/>
-      <c r="N18" s="159"/>
-      <c r="O18" s="159"/>
-      <c r="P18" s="158"/>
-    </row>
-    <row r="19" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B19" s="108">
+      <c r="C18" s="109"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="106"/>
+      <c r="L18" s="96"/>
+      <c r="M18" s="107"/>
+      <c r="N18" s="151"/>
+      <c r="O18" s="151"/>
+      <c r="P18" s="150"/>
+    </row>
+    <row r="19" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B19" s="100">
         <v>17</v>
       </c>
-      <c r="C19" s="117"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="114"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="113"/>
-      <c r="I19" s="114"/>
-      <c r="J19" s="114"/>
-      <c r="K19" s="114"/>
-      <c r="L19" s="104"/>
-      <c r="M19" s="115"/>
-      <c r="N19" s="159"/>
-      <c r="O19" s="159"/>
-      <c r="P19" s="158"/>
-    </row>
-    <row r="20" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B20" s="108">
+      <c r="C19" s="109"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="106"/>
+      <c r="L19" s="96"/>
+      <c r="M19" s="107"/>
+      <c r="N19" s="151"/>
+      <c r="O19" s="151"/>
+      <c r="P19" s="150"/>
+    </row>
+    <row r="20" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B20" s="100">
         <v>18</v>
       </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="110"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="114"/>
-      <c r="G20" s="112"/>
-      <c r="H20" s="113"/>
-      <c r="I20" s="114"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="114"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="115"/>
-      <c r="N20" s="159"/>
-      <c r="O20" s="159"/>
-      <c r="P20" s="158"/>
-    </row>
-    <row r="21" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B21" s="108">
+      <c r="C20" s="109"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
+      <c r="L20" s="96"/>
+      <c r="M20" s="107"/>
+      <c r="N20" s="151"/>
+      <c r="O20" s="151"/>
+      <c r="P20" s="150"/>
+    </row>
+    <row r="21" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B21" s="100">
         <v>19</v>
       </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="114"/>
-      <c r="G21" s="112"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="114"/>
-      <c r="K21" s="114"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="115"/>
-      <c r="N21" s="159"/>
-      <c r="O21" s="159"/>
-      <c r="P21" s="158"/>
-    </row>
-    <row r="22" s="85" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
-      <c r="B22" s="108">
+      <c r="C21" s="109"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="106"/>
+      <c r="K21" s="106"/>
+      <c r="L21" s="96"/>
+      <c r="M21" s="107"/>
+      <c r="N21" s="151"/>
+      <c r="O21" s="151"/>
+      <c r="P21" s="150"/>
+    </row>
+    <row r="22" s="77" customFormat="1" ht="12.75" customHeight="1" spans="2:16">
+      <c r="B22" s="100">
         <v>20</v>
       </c>
-      <c r="C22" s="117"/>
-      <c r="D22" s="110"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="114"/>
-      <c r="G22" s="112"/>
-      <c r="H22" s="113"/>
-      <c r="I22" s="114"/>
-      <c r="J22" s="114"/>
-      <c r="K22" s="114"/>
-      <c r="L22" s="104"/>
-      <c r="M22" s="115"/>
-      <c r="N22" s="159"/>
-      <c r="O22" s="159"/>
-      <c r="P22" s="158"/>
-    </row>
-    <row r="23" s="87" customFormat="1" ht="13.9" customHeight="1" spans="2:16">
-      <c r="B23" s="160" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="161"/>
-      <c r="D23" s="161"/>
-      <c r="E23" s="161"/>
-      <c r="F23" s="161"/>
-      <c r="G23" s="161"/>
-      <c r="H23" s="162"/>
-      <c r="I23" s="162"/>
-      <c r="J23" s="162"/>
-      <c r="K23" s="162"/>
-      <c r="L23" s="162"/>
-      <c r="M23" s="163"/>
-      <c r="N23" s="162"/>
-      <c r="O23" s="162"/>
-      <c r="P23" s="164"/>
-    </row>
-    <row r="24" s="88" customFormat="1"/>
-    <row r="25" s="88" customFormat="1"/>
-    <row r="26" s="88" customFormat="1"/>
-    <row r="27" s="88" customFormat="1"/>
-    <row r="28" s="88" customFormat="1"/>
-    <row r="29" s="88" customFormat="1"/>
-    <row r="30" s="88" customFormat="1"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="106"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="106"/>
+      <c r="K22" s="106"/>
+      <c r="L22" s="96"/>
+      <c r="M22" s="107"/>
+      <c r="N22" s="151"/>
+      <c r="O22" s="151"/>
+      <c r="P22" s="150"/>
+    </row>
+    <row r="23" s="79" customFormat="1" ht="13.9" customHeight="1" spans="2:16">
+      <c r="B23" s="152" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="153"/>
+      <c r="D23" s="153"/>
+      <c r="E23" s="153"/>
+      <c r="F23" s="153"/>
+      <c r="G23" s="153"/>
+      <c r="H23" s="154"/>
+      <c r="I23" s="154"/>
+      <c r="J23" s="154"/>
+      <c r="K23" s="154"/>
+      <c r="L23" s="154"/>
+      <c r="M23" s="155"/>
+      <c r="N23" s="154"/>
+      <c r="O23" s="154"/>
+      <c r="P23" s="156"/>
+    </row>
+    <row r="24" s="80" customFormat="1"/>
+    <row r="25" s="80" customFormat="1"/>
+    <row r="26" s="80" customFormat="1"/>
+    <row r="27" s="80" customFormat="1"/>
+    <row r="28" s="80" customFormat="1"/>
+    <row r="29" s="80" customFormat="1"/>
+    <row r="30" s="80" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="99" fitToHeight="0" orientation="landscape"/>
@@ -5395,2181 +5503,1809 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
     <col min="1" max="1" width="0.876106194690266" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.50442477876106" style="11" customWidth="1"/>
-    <col min="3" max="3" width="15.1238938053097" style="11" customWidth="1"/>
-    <col min="4" max="4" width="23" style="11" customWidth="1"/>
-    <col min="5" max="5" width="24.1238938053097" style="11" customWidth="1"/>
-    <col min="6" max="6" width="32.3716814159292" style="11" customWidth="1"/>
-    <col min="7" max="7" width="3.50442477876106" style="11" customWidth="1"/>
-    <col min="8" max="8" width="4.50442477876106" style="11" customWidth="1"/>
-    <col min="9" max="9" width="3.50442477876106" style="11" customWidth="1"/>
-    <col min="10" max="10" width="23" style="12" customWidth="1"/>
-    <col min="11" max="11" width="6.75221238938053" style="12" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="13" customWidth="1"/>
+    <col min="2" max="2" width="9.50442477876106" style="10" customWidth="1"/>
+    <col min="3" max="3" width="15.1238938053097" style="10" customWidth="1"/>
+    <col min="4" max="4" width="23" style="10" customWidth="1"/>
+    <col min="5" max="5" width="24.1238938053097" style="10" customWidth="1"/>
+    <col min="6" max="6" width="32.3716814159292" style="10" customWidth="1"/>
+    <col min="7" max="7" width="3.50442477876106" style="10" customWidth="1"/>
+    <col min="8" max="8" width="4.50442477876106" style="10" customWidth="1"/>
+    <col min="9" max="9" width="3.50442477876106" style="10" customWidth="1"/>
+    <col min="10" max="10" width="23" style="11" customWidth="1"/>
+    <col min="11" max="11" width="6.75221238938053" style="11" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:11">
-      <c r="B1" s="14" t="s">
-        <v>65</v>
+      <c r="B1" s="13" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="13.9" customHeight="1" spans="1:11">
       <c r="A2" s="1"/>
-      <c r="B2" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="20"/>
+      <c r="B2" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="19"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:11">
-      <c r="K3" s="21"/>
+      <c r="K3" s="20"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:11">
       <c r="A4" s="1"/>
-      <c r="B4" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="24" t="s">
+      <c r="B4" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="24" t="s">
+      <c r="C4" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="D4" s="22" t="s">
         <v>76</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:11">
       <c r="A5" s="1"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="30" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="I5" s="30" t="s">
+      <c r="D5" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="J5" s="29"/>
-      <c r="K5" s="31"/>
+      <c r="E5" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="28"/>
+      <c r="K5" s="30"/>
     </row>
     <row r="6" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A6" s="1"/>
-      <c r="B6" s="32">
+      <c r="B6" s="31">
         <v>1</v>
       </c>
-      <c r="C6" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" s="36" t="s">
+      <c r="C6" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J6" s="37" t="s">
+      <c r="D6" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="K6" s="38" t="s">
-        <v>34</v>
+      <c r="E6" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="K6" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A7" s="1"/>
-      <c r="B7" s="39">
+      <c r="B7" s="38">
         <v>2</v>
       </c>
-      <c r="C7" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="36" t="s">
+      <c r="C7" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="H7" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I7" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J7" s="37" t="s">
+      <c r="D7" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="K7" s="38" t="s">
-        <v>34</v>
+      <c r="E7" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I7" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J7" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="K7" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A8" s="1"/>
-      <c r="B8" s="39">
+      <c r="B8" s="38">
         <v>3</v>
       </c>
-      <c r="C8" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="F8" s="41" t="s">
+      <c r="C8" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="G8" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H8" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="K8" s="38" t="s">
-        <v>34</v>
+      <c r="K8" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A9" s="1"/>
-      <c r="B9" s="39">
+      <c r="B9" s="38">
         <v>4</v>
       </c>
-      <c r="C9" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="G9" s="36" t="s">
+      <c r="C9" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="H9" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="K9" s="38" t="s">
-        <v>34</v>
+      <c r="D9" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J9" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="K9" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" s="4" customFormat="1" ht="51" spans="1:11">
       <c r="A10" s="1"/>
-      <c r="B10" s="43">
+      <c r="B10" s="42">
         <v>5</v>
       </c>
-      <c r="C10" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H10" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="K10" s="38" t="s">
-        <v>34</v>
+      <c r="C10" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J10" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A11" s="1"/>
-      <c r="B11" s="32">
+      <c r="B11" s="31">
         <v>6</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="35" t="s">
+      <c r="C11" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="34" t="s">
+      <c r="D11" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="G11" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J11" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="K11" s="38" t="s">
-        <v>34</v>
+      <c r="E11" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J11" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" s="4" customFormat="1" ht="38.25" spans="1:11">
       <c r="A12" s="1"/>
-      <c r="B12" s="39">
+      <c r="B12" s="38">
         <v>7</v>
       </c>
-      <c r="C12" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H12" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I12" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J12" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="K12" s="38" t="s">
-        <v>34</v>
+      <c r="C12" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="13" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A13" s="1"/>
-      <c r="B13" s="39">
+      <c r="B13" s="38">
         <v>8</v>
       </c>
-      <c r="C13" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="F13" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="G13" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I13" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J13" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K13" s="38" t="s">
-        <v>34</v>
+      <c r="C13" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I13" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J13" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14" s="4" customFormat="1" ht="38.25" spans="1:11">
       <c r="A14" s="1"/>
-      <c r="B14" s="39">
+      <c r="B14" s="38">
         <v>9</v>
       </c>
-      <c r="C14" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="F14" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="K14" s="38" t="s">
-        <v>34</v>
+      <c r="C14" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J14" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="15" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A15" s="1"/>
-      <c r="B15" s="39">
+      <c r="B15" s="38">
         <v>10</v>
       </c>
-      <c r="C15" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="F15" s="41" t="s">
+      <c r="C15" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="G15" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H15" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I15" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="K15" s="38" t="s">
-        <v>34</v>
+      <c r="E15" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J15" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="16" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A16" s="1"/>
-      <c r="B16" s="39">
+      <c r="B16" s="38">
         <v>11</v>
       </c>
-      <c r="C16" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I16" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="K16" s="38" t="s">
-        <v>34</v>
+      <c r="C16" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J16" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A17" s="1"/>
-      <c r="B17" s="47">
+      <c r="B17" s="46">
         <v>12</v>
       </c>
-      <c r="C17" s="48" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="F17" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="G17" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H17" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I17" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J17" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" s="38" t="s">
-        <v>34</v>
+      <c r="C17" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J17" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A18" s="1"/>
-      <c r="B18" s="32">
+      <c r="B18" s="31">
         <v>13</v>
       </c>
-      <c r="C18" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" s="34" t="s">
+      <c r="C18" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="E18" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="F18" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="G18" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H18" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J18" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" s="38" t="s">
-        <v>34</v>
+      <c r="D18" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J18" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="38.25" spans="1:11">
       <c r="A19" s="1"/>
-      <c r="B19" s="51">
+      <c r="B19" s="50">
         <v>14</v>
       </c>
-      <c r="C19" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="F19" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="G19" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H19" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J19" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="K19" s="38" t="s">
-        <v>34</v>
+      <c r="C19" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J19" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="1" ht="51" spans="1:11">
       <c r="A20" s="1"/>
-      <c r="B20" s="39">
+      <c r="B20" s="38">
         <v>15</v>
       </c>
-      <c r="C20" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="F20" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H20" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I20" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K20" s="38" t="s">
-        <v>34</v>
+      <c r="C20" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="G20" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J20" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A21" s="1"/>
-      <c r="B21" s="43">
+      <c r="B21" s="42">
         <v>16</v>
       </c>
-      <c r="C21" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="F21" s="53" t="s">
-        <v>132</v>
-      </c>
-      <c r="G21" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I21" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J21" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="K21" s="38" t="s">
-        <v>34</v>
+      <c r="C21" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="F21" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J21" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A22" s="1"/>
-      <c r="B22" s="39">
+      <c r="B22" s="38">
         <v>17</v>
       </c>
-      <c r="C22" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" s="42" t="s">
+      <c r="C22" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="F22" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="G22" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H22" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I22" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J22" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K22" s="38" t="s">
-        <v>34</v>
+      <c r="E22" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="F22" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I22" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J22" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="23" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A23" s="1"/>
-      <c r="B23" s="51">
+      <c r="B23" s="50">
         <v>18</v>
       </c>
-      <c r="C23" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="E23" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="F23" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="G23" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H23" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I23" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J23" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K23" s="38" t="s">
-        <v>34</v>
+      <c r="C23" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="52" t="s">
+        <v>141</v>
+      </c>
+      <c r="G23" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J23" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A24" s="1"/>
-      <c r="B24" s="39">
+      <c r="B24" s="38">
         <v>19</v>
       </c>
-      <c r="C24" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="E24" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="F24" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="G24" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H24" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="K24" s="38" t="s">
-        <v>34</v>
+      <c r="C24" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="F24" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J24" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="25" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A25" s="1"/>
-      <c r="B25" s="43">
+      <c r="B25" s="42">
         <v>20</v>
       </c>
-      <c r="C25" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="D25" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="F25" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="G25" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H25" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I25" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K25" s="38" t="s">
-        <v>34</v>
+      <c r="C25" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="D25" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="F25" s="52" t="s">
+        <v>148</v>
+      </c>
+      <c r="G25" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I25" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J25" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="26" s="4" customFormat="1" ht="13.5" spans="1:11">
       <c r="A26" s="1"/>
-      <c r="B26" s="47">
+      <c r="B26" s="46">
         <v>21</v>
       </c>
-      <c r="C26" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" s="45" t="s">
+      <c r="C26" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="E26" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="F26" s="55" t="s">
-        <v>147</v>
-      </c>
-      <c r="G26" s="36" t="s">
+      <c r="D26" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F26" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="G26" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="I26" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="J26" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" s="5" customFormat="1" ht="25.5" spans="1:11">
+      <c r="A27" s="55"/>
+      <c r="B27" s="31">
+        <v>22</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="G27" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I27" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J27" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K27" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" s="6" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A28" s="56"/>
+      <c r="B28" s="50">
+        <v>23</v>
+      </c>
+      <c r="C28" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="H26" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="I26" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="J26" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K26" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" s="5" customFormat="1" ht="25.5" spans="1:11">
-      <c r="A27" s="56"/>
-      <c r="B27" s="32">
-        <v>22</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="D27" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="E27" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="G27" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H27" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I27" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K27" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" s="6" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A28" s="57"/>
-      <c r="B28" s="51">
-        <v>23</v>
-      </c>
-      <c r="C28" s="58" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="E28" s="54" t="s">
-        <v>152</v>
-      </c>
-      <c r="F28" s="53" t="s">
-        <v>153</v>
-      </c>
-      <c r="G28" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="H28" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="I28" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K28" s="38" t="s">
-        <v>34</v>
+      <c r="D28" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="G28" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="I28" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="J28" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="29" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A29" s="1"/>
-      <c r="B29" s="51">
+      <c r="B29" s="50">
         <v>24</v>
       </c>
-      <c r="C29" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="E29" s="54" t="s">
-        <v>154</v>
-      </c>
-      <c r="F29" s="53" t="s">
+      <c r="C29" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="G29" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="H29" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="I29" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="K29" s="38" t="s">
-        <v>34</v>
+      <c r="E29" s="53" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="G29" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="J29" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="30" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A30" s="1"/>
-      <c r="B30" s="60">
+      <c r="B30" s="59">
         <v>25</v>
       </c>
-      <c r="C30" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="E30" s="54" t="s">
-        <v>156</v>
-      </c>
-      <c r="F30" s="53" t="s">
-        <v>157</v>
-      </c>
-      <c r="G30" s="59" t="s">
+      <c r="C30" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="H30" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="I30" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="J30" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K30" s="38" t="s">
-        <v>34</v>
+      <c r="D30" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" s="52" t="s">
+        <v>161</v>
+      </c>
+      <c r="G30" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="I30" s="58" t="s">
+        <v>91</v>
+      </c>
+      <c r="J30" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K30" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="31" s="4" customFormat="1" ht="38.25" spans="1:11">
       <c r="A31" s="1"/>
-      <c r="B31" s="39">
+      <c r="B31" s="38">
         <v>26</v>
       </c>
-      <c r="C31" s="52" t="s">
-        <v>96</v>
-      </c>
-      <c r="D31" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31" s="54" t="s">
-        <v>158</v>
-      </c>
-      <c r="F31" s="53" t="s">
-        <v>159</v>
-      </c>
-      <c r="G31" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="H31" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="I31" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="J31" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="K31" s="38" t="s">
-        <v>34</v>
+      <c r="C31" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="F31" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="G31" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="H31" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="I31" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="J31" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="32" s="4" customFormat="1" ht="25.5" spans="1:11">
       <c r="A32" s="1"/>
-      <c r="B32" s="51">
+      <c r="B32" s="50">
         <v>27</v>
       </c>
-      <c r="C32" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D32" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="E32" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="F32" s="55" t="s">
-        <v>161</v>
-      </c>
-      <c r="G32" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="H32" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="I32" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K32" s="38" t="s">
-        <v>34</v>
+      <c r="C32" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="G32" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="H32" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="I32" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="J32" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K32" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="33" s="4" customFormat="1" ht="38.25" spans="1:11">
       <c r="A33" s="1"/>
-      <c r="B33" s="39">
+      <c r="B33" s="38">
         <v>28</v>
       </c>
-      <c r="C33" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="D33" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="E33" s="42" t="s">
-        <v>162</v>
-      </c>
-      <c r="F33" s="41" t="s">
-        <v>163</v>
-      </c>
-      <c r="G33" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="H33" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="I33" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="J33" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K33" s="38" t="s">
-        <v>34</v>
+      <c r="C33" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="D33" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="41" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="G33" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="I33" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="J33" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="34" s="4" customFormat="1" ht="38.25" spans="1:11">
       <c r="A34" s="1"/>
-      <c r="B34" s="39">
+      <c r="B34" s="38">
         <v>29</v>
       </c>
-      <c r="C34" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="D34" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="E34" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="F34" s="53" t="s">
-        <v>166</v>
-      </c>
-      <c r="G34" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="H34" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="I34" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="J34" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="K34" s="38" t="s">
-        <v>34</v>
+      <c r="C34" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="E34" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="F34" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="H34" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="I34" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="J34" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="K34" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="35" s="4" customFormat="1" ht="38.25" spans="1:11">
       <c r="A35" s="1"/>
-      <c r="B35" s="32">
+      <c r="B35" s="31">
         <v>30</v>
       </c>
-      <c r="C35" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="D35" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="E35" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="F35" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="G35" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H35" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I35" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K35" s="38" t="s">
-        <v>34</v>
+      <c r="C35" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E35" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="G35" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I35" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J35" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K35" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A36" s="1"/>
-      <c r="B36" s="51">
+      <c r="B36" s="50">
         <v>31</v>
       </c>
-      <c r="C36" s="63" t="s">
-        <v>171</v>
-      </c>
-      <c r="D36" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>173</v>
-      </c>
-      <c r="F36" s="55" t="s">
-        <v>174</v>
-      </c>
-      <c r="G36" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H36" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I36" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J36" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K36" s="38" t="s">
-        <v>34</v>
+      <c r="C36" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="D36" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="E36" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="F36" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="G36" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I36" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J36" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="37" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A37" s="1"/>
-      <c r="B37" s="39">
+      <c r="B37" s="38">
         <v>32</v>
       </c>
-      <c r="C37" s="64" t="s">
-        <v>171</v>
-      </c>
-      <c r="D37" s="41" t="s">
+      <c r="C37" s="63" t="s">
         <v>175</v>
       </c>
-      <c r="E37" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="F37" s="41" t="s">
-        <v>177</v>
-      </c>
-      <c r="G37" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H37" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I37" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J37" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K37" s="38" t="s">
+      <c r="D37" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="E37" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="F37" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="G37" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H37" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I37" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J37" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K37" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" s="6" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A38" s="56"/>
+      <c r="B38" s="38">
+        <v>33</v>
+      </c>
+      <c r="C38" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="D38" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="E38" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="F38" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="G38" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H38" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I38" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J38" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="K38" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" s="7" customFormat="1" ht="63.75" spans="1:11">
+      <c r="A39" s="64"/>
+      <c r="B39" s="31">
         <v>34</v>
       </c>
-    </row>
-    <row r="38" s="6" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A38" s="57"/>
-      <c r="B38" s="39">
-        <v>33</v>
-      </c>
-      <c r="C38" s="63" t="s">
-        <v>171</v>
-      </c>
-      <c r="D38" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="E38" s="42" t="s">
-        <v>179</v>
-      </c>
-      <c r="F38" s="53" t="s">
-        <v>180</v>
-      </c>
-      <c r="G38" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H38" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I38" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J38" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="K38" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" s="7" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A39" s="65"/>
-      <c r="B39" s="32">
-        <v>34</v>
-      </c>
-      <c r="C39" s="64" t="s">
-        <v>171</v>
-      </c>
-      <c r="D39" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="E39" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="F39" s="34" t="s">
-        <v>184</v>
-      </c>
-      <c r="G39" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H39" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I39" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J39" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K39" s="38" t="s">
-        <v>34</v>
+      <c r="C39" s="63" t="s">
+        <v>175</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="E39" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="G39" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H39" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I39" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J39" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="40" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A40" s="1"/>
-      <c r="B40" s="51">
+      <c r="B40" s="50">
         <v>35</v>
       </c>
-      <c r="C40" s="63" t="s">
-        <v>185</v>
-      </c>
-      <c r="D40" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="E40" s="42" t="s">
-        <v>187</v>
-      </c>
-      <c r="F40" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="G40" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H40" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I40" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K40" s="38" t="s">
-        <v>34</v>
+      <c r="C40" s="62" t="s">
+        <v>189</v>
+      </c>
+      <c r="D40" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="E40" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="F40" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="G40" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H40" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I40" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J40" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K40" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="41" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A41" s="1"/>
-      <c r="B41" s="39">
+      <c r="B41" s="38">
         <v>36</v>
       </c>
-      <c r="C41" s="64" t="s">
-        <v>185</v>
-      </c>
-      <c r="D41" s="41" t="s">
+      <c r="C41" s="63" t="s">
         <v>189</v>
       </c>
-      <c r="E41" s="42" t="s">
-        <v>190</v>
-      </c>
-      <c r="F41" s="41" t="s">
-        <v>191</v>
-      </c>
-      <c r="G41" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H41" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I41" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J41" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="K41" s="38" t="s">
-        <v>34</v>
+      <c r="D41" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="E41" s="41" t="s">
+        <v>194</v>
+      </c>
+      <c r="F41" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="G41" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I41" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J41" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="K41" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="42" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A42" s="1"/>
-      <c r="B42" s="39">
+      <c r="B42" s="38">
         <v>37</v>
       </c>
-      <c r="C42" s="63" t="s">
-        <v>185</v>
-      </c>
-      <c r="D42" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="E42" s="42" t="s">
-        <v>193</v>
-      </c>
-      <c r="F42" s="53" t="s">
-        <v>194</v>
-      </c>
-      <c r="G42" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H42" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I42" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J42" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="K42" s="38" t="s">
-        <v>34</v>
+      <c r="C42" s="62" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="E42" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="F42" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="G42" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H42" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I42" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J42" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="K42" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="43" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A43" s="1"/>
-      <c r="B43" s="32">
+      <c r="B43" s="31">
         <v>38</v>
       </c>
-      <c r="C43" s="64" t="s">
-        <v>185</v>
-      </c>
-      <c r="D43" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="E43" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="F43" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="G43" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H43" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I43" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J43" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K43" s="38" t="s">
-        <v>34</v>
+      <c r="C43" s="63" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="F43" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="G43" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I43" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J43" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K43" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="44" s="4" customFormat="1" ht="76.5" spans="1:11">
       <c r="A44" s="1"/>
-      <c r="B44" s="51">
+      <c r="B44" s="50">
         <v>39</v>
       </c>
-      <c r="C44" s="63" t="s">
-        <v>185</v>
-      </c>
-      <c r="D44" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="E44" s="42" t="s">
-        <v>198</v>
-      </c>
-      <c r="F44" s="55" t="s">
+      <c r="C44" s="62" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="G44" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H44" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I44" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J44" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="K44" s="38" t="s">
-        <v>34</v>
+      <c r="E44" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="F44" s="54" t="s">
+        <v>203</v>
+      </c>
+      <c r="G44" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H44" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I44" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J44" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="K44" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="45" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A45" s="1"/>
-      <c r="B45" s="39">
+      <c r="B45" s="38">
         <v>40</v>
       </c>
-      <c r="C45" s="63" t="s">
-        <v>200</v>
-      </c>
-      <c r="D45" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="E45" s="42" t="s">
-        <v>202</v>
-      </c>
-      <c r="F45" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="G45" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H45" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I45" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J45" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K45" s="38" t="s">
-        <v>34</v>
+      <c r="C45" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="D45" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="E45" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="F45" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="G45" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H45" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I45" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J45" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K45" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="46" s="4" customFormat="1" ht="63.75" spans="1:11">
       <c r="A46" s="1"/>
-      <c r="B46" s="39">
+      <c r="B46" s="38">
         <v>41</v>
       </c>
-      <c r="C46" s="63" t="s">
-        <v>200</v>
-      </c>
-      <c r="D46" s="41" t="s">
+      <c r="C46" s="62" t="s">
         <v>204</v>
       </c>
-      <c r="E46" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="F46" s="53" t="s">
-        <v>206</v>
-      </c>
-      <c r="G46" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H46" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I46" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J46" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K46" s="38" t="s">
-        <v>34</v>
+      <c r="D46" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="E46" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="F46" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="G46" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H46" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I46" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J46" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K46" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="47" s="8" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A47" s="66"/>
-      <c r="B47" s="39">
+      <c r="A47" s="65"/>
+      <c r="B47" s="38">
         <v>42</v>
       </c>
-      <c r="C47" s="64" t="s">
-        <v>200</v>
-      </c>
-      <c r="D47" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="E47" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="F47" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="G47" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H47" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I47" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J47" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K47" s="38" t="s">
-        <v>34</v>
+      <c r="C47" s="63" t="s">
+        <v>204</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E47" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="F47" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="G47" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I47" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J47" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K47" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="48" s="9" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A48" s="67"/>
-      <c r="B48" s="68">
+      <c r="A48" s="66"/>
+      <c r="B48" s="67">
         <v>43</v>
       </c>
-      <c r="C48" s="69" t="s">
-        <v>200</v>
-      </c>
-      <c r="D48" s="70" t="s">
-        <v>210</v>
-      </c>
-      <c r="E48" s="71" t="s">
-        <v>211</v>
-      </c>
-      <c r="F48" s="70" t="s">
-        <v>212</v>
-      </c>
-      <c r="G48" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H48" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I48" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J48" s="72" t="s">
-        <v>108</v>
-      </c>
-      <c r="K48" s="73" t="s">
-        <v>34</v>
+      <c r="C48" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="D48" s="69" t="s">
+        <v>214</v>
+      </c>
+      <c r="E48" s="70" t="s">
+        <v>215</v>
+      </c>
+      <c r="F48" s="69" t="s">
+        <v>216</v>
+      </c>
+      <c r="G48" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H48" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I48" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J48" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="K48" s="72" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="49" customFormat="1" ht="76.5" spans="1:11">
       <c r="A49" s="1"/>
-      <c r="B49" s="39">
+      <c r="B49" s="38">
         <v>44</v>
       </c>
-      <c r="C49" s="63" t="s">
-        <v>200</v>
-      </c>
-      <c r="D49" s="41" t="s">
-        <v>213</v>
-      </c>
-      <c r="E49" s="42" t="s">
-        <v>214</v>
-      </c>
-      <c r="F49" s="53" t="s">
-        <v>215</v>
-      </c>
-      <c r="G49" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H49" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I49" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J49" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K49" s="38" t="s">
-        <v>34</v>
+      <c r="C49" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="D49" s="40" t="s">
+        <v>217</v>
+      </c>
+      <c r="E49" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="F49" s="52" t="s">
+        <v>219</v>
+      </c>
+      <c r="G49" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H49" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I49" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J49" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K49" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="50" customFormat="1" ht="63.75" spans="1:11">
       <c r="A50" s="1"/>
-      <c r="B50" s="39">
+      <c r="B50" s="38">
         <v>45</v>
       </c>
-      <c r="C50" s="64" t="s">
-        <v>171</v>
-      </c>
-      <c r="D50" s="34" t="s">
-        <v>216</v>
-      </c>
-      <c r="E50" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="F50" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="G50" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H50" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I50" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J50" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="K50" s="38" t="s">
-        <v>34</v>
+      <c r="C50" s="63" t="s">
+        <v>175</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E50" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="F50" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="G50" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H50" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I50" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J50" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="K50" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="51" customFormat="1" ht="76.5" spans="1:11">
       <c r="A51" s="1"/>
-      <c r="B51" s="39">
+      <c r="B51" s="38">
         <v>46</v>
       </c>
-      <c r="C51" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="D51" s="41" t="s">
-        <v>219</v>
-      </c>
-      <c r="E51" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="F51" s="41" t="s">
-        <v>221</v>
-      </c>
-      <c r="G51" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H51" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I51" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J51" s="37" t="s">
-        <v>222</v>
-      </c>
-      <c r="K51" s="38" t="s">
-        <v>34</v>
+      <c r="C51" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="E51" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="F51" s="40" t="s">
+        <v>225</v>
+      </c>
+      <c r="G51" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H51" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I51" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J51" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="K51" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="52" customFormat="1" ht="63.75" spans="1:11">
       <c r="A52" s="1"/>
-      <c r="B52" s="39">
+      <c r="B52" s="38">
         <v>47</v>
       </c>
-      <c r="C52" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="D52" s="41" t="s">
-        <v>219</v>
-      </c>
-      <c r="E52" s="42" t="s">
+      <c r="C52" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="D52" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="F52" s="53" t="s">
-        <v>224</v>
-      </c>
-      <c r="G52" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H52" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I52" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J52" s="37" t="s">
-        <v>222</v>
-      </c>
-      <c r="K52" s="38" t="s">
-        <v>34</v>
+      <c r="E52" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="F52" s="52" t="s">
+        <v>228</v>
+      </c>
+      <c r="G52" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H52" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I52" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J52" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="K52" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="53" customFormat="1" ht="51" spans="1:11">
       <c r="A53" s="1"/>
-      <c r="B53" s="39">
+      <c r="B53" s="38">
         <v>48</v>
       </c>
-      <c r="C53" s="64" t="s">
-        <v>96</v>
-      </c>
-      <c r="D53" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="E53" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="F53" s="34" t="s">
-        <v>227</v>
-      </c>
-      <c r="G53" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H53" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I53" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J53" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K53" s="38" t="s">
-        <v>34</v>
+      <c r="C53" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E53" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="G53" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H53" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I53" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J53" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K53" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="63.75" spans="1:11">
       <c r="A54" s="1"/>
-      <c r="B54" s="39">
+      <c r="B54" s="38">
         <v>49</v>
       </c>
-      <c r="C54" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="D54" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="E54" s="42" t="s">
-        <v>228</v>
-      </c>
-      <c r="F54" s="41" t="s">
-        <v>229</v>
-      </c>
-      <c r="G54" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H54" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I54" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J54" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="K54" s="38" t="s">
-        <v>34</v>
+      <c r="C54" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="D54" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="F54" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="G54" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H54" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I54" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J54" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="K54" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="55" customFormat="1" ht="76.5" spans="1:11">
       <c r="A55" s="1"/>
-      <c r="B55" s="39">
+      <c r="B55" s="38">
         <v>50</v>
       </c>
-      <c r="C55" s="63" t="s">
-        <v>230</v>
-      </c>
-      <c r="D55" s="41" t="s">
-        <v>231</v>
-      </c>
-      <c r="E55" s="42" t="s">
-        <v>232</v>
-      </c>
-      <c r="F55" s="53" t="s">
-        <v>233</v>
-      </c>
-      <c r="G55" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H55" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I55" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J55" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K55" s="38" t="s">
-        <v>34</v>
+      <c r="C55" s="62" t="s">
+        <v>234</v>
+      </c>
+      <c r="D55" s="40" t="s">
+        <v>235</v>
+      </c>
+      <c r="E55" s="41" t="s">
+        <v>236</v>
+      </c>
+      <c r="F55" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="G55" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H55" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I55" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J55" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K55" s="37" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="56" customFormat="1" ht="63.75" spans="1:11">
       <c r="A56" s="1"/>
-      <c r="B56" s="39">
+      <c r="B56" s="38">
         <v>51</v>
       </c>
-      <c r="C56" s="64" t="s">
-        <v>234</v>
-      </c>
-      <c r="D56" s="34" t="s">
-        <v>235</v>
-      </c>
-      <c r="E56" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="F56" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="G56" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H56" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I56" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J56" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="K56" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="57" s="10" customFormat="1" ht="13.5" spans="1:11">
-      <c r="A57" s="74"/>
-      <c r="B57" s="75">
-        <v>52</v>
-      </c>
-      <c r="C57" s="76"/>
-      <c r="D57" s="77"/>
-      <c r="E57" s="78"/>
-      <c r="F57" s="77"/>
-      <c r="G57" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H57" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I57" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J57" s="79" t="s">
+      <c r="C56" s="63" t="s">
         <v>238</v>
       </c>
-      <c r="K57" s="80" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" ht="13.5" spans="1:11">
-      <c r="A58" s="1"/>
-      <c r="B58" s="39">
-        <v>53</v>
-      </c>
-      <c r="C58" s="63"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="53"/>
-      <c r="G58" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H58" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I58" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J58" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="K58" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="59" customFormat="1" ht="13.5" spans="1:11">
-      <c r="A59" s="1"/>
-      <c r="B59" s="39">
-        <v>54</v>
-      </c>
-      <c r="C59" s="64"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H59" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I59" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J59" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="K59" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="60" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A60" s="1"/>
-      <c r="B60" s="39">
-        <v>55</v>
-      </c>
-      <c r="C60" s="63" t="s">
-        <v>200</v>
-      </c>
-      <c r="D60" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="E60" s="42" t="s">
-        <v>202</v>
-      </c>
-      <c r="F60" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="G60" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H60" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I60" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J60" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="K60" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A61" s="1"/>
-      <c r="B61" s="39">
-        <v>56</v>
-      </c>
-      <c r="C61" s="63" t="s">
-        <v>200</v>
-      </c>
-      <c r="D61" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="E61" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="F61" s="53" t="s">
-        <v>206</v>
-      </c>
-      <c r="G61" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H61" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I61" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J61" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="K61" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="62" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A62" s="1"/>
-      <c r="B62" s="39">
-        <v>57</v>
-      </c>
-      <c r="C62" s="64" t="s">
-        <v>200</v>
-      </c>
-      <c r="D62" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="E62" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="F62" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="G62" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H62" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I62" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J62" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="K62" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="63" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A63" s="1"/>
-      <c r="B63" s="39">
-        <v>58</v>
-      </c>
-      <c r="C63" s="63" t="s">
-        <v>200</v>
-      </c>
-      <c r="D63" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="E63" s="42" t="s">
-        <v>202</v>
-      </c>
-      <c r="F63" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="G63" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H63" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I63" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J63" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="K63" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="64" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A64" s="1"/>
-      <c r="B64" s="39">
-        <v>59</v>
-      </c>
-      <c r="C64" s="63" t="s">
-        <v>200</v>
-      </c>
-      <c r="D64" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="E64" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="F64" s="53" t="s">
-        <v>206</v>
-      </c>
-      <c r="G64" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H64" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I64" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J64" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="K64" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="65" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A65" s="1"/>
-      <c r="B65" s="39">
-        <v>60</v>
-      </c>
-      <c r="C65" s="64" t="s">
-        <v>200</v>
-      </c>
-      <c r="D65" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="E65" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="F65" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="G65" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H65" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I65" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J65" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="K65" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="66" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A66" s="1"/>
-      <c r="B66" s="39">
-        <v>61</v>
-      </c>
-      <c r="C66" s="63" t="s">
-        <v>200</v>
-      </c>
-      <c r="D66" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="E66" s="42" t="s">
-        <v>202</v>
-      </c>
-      <c r="F66" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="G66" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H66" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I66" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J66" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="K66" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="67" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A67" s="1"/>
-      <c r="B67" s="39">
-        <v>62</v>
-      </c>
-      <c r="C67" s="63" t="s">
-        <v>200</v>
-      </c>
-      <c r="D67" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="E67" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="F67" s="53" t="s">
-        <v>206</v>
-      </c>
-      <c r="G67" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H67" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I67" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J67" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="K67" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="68" customFormat="1" ht="63.75" spans="1:11">
-      <c r="A68" s="1"/>
-      <c r="B68" s="39">
-        <v>63</v>
-      </c>
-      <c r="C68" s="64" t="s">
-        <v>200</v>
-      </c>
-      <c r="D68" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="E68" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="F68" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="G68" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="H68" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="I68" s="62" t="s">
-        <v>87</v>
-      </c>
-      <c r="J68" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="K68" s="38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="69" customFormat="1" spans="1:11">
-      <c r="A69" s="1"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="11"/>
-      <c r="I69" s="11"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-    </row>
-    <row r="71" spans="1:11">
-      <c r="B71" s="81" t="s">
+      <c r="D56" s="33" t="s">
         <v>239</v>
       </c>
-      <c r="C71" s="82"/>
-      <c r="D71" s="82"/>
-      <c r="E71" s="82"/>
-      <c r="F71" s="82"/>
-      <c r="G71" s="82"/>
+      <c r="E56" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="F56" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="G56" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H56" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="I56" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="J56" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K56" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:11">
+      <c r="A57" s="1"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+    </row>
+    <row r="59" ht="12.75" spans="1:11">
+      <c r="B59" s="73" t="s">
+        <v>242</v>
+      </c>
+      <c r="C59" s="74"/>
+      <c r="D59" s="74"/>
+      <c r="E59" s="74"/>
+      <c r="F59" s="74"/>
+      <c r="G59" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7578,7 +7314,7 @@
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
   </mergeCells>
-  <conditionalFormatting sqref="G69:I69">
+  <conditionalFormatting sqref="G57:I57">
     <cfRule type="cellIs" dxfId="0" priority="21" stopIfTrue="1" operator="equal">
       <formula>"○"</formula>
     </cfRule>
@@ -7586,7 +7322,7 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:I68">
+  <conditionalFormatting sqref="G6:I56">
     <cfRule type="cellIs" dxfId="0" priority="33" stopIfTrue="1" operator="equal">
       <formula>"○"</formula>
     </cfRule>
@@ -7598,7 +7334,7 @@
     <dataValidation showInputMessage="1" showErrorMessage="1" prompt="概要设计" sqref="G5"/>
     <dataValidation showInputMessage="1" showErrorMessage="1" prompt="编码" sqref="H5"/>
     <dataValidation showInputMessage="1" showErrorMessage="1" prompt="单体测试" sqref="I5"/>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" prompt="○ ：完成&#10;△ ：进行中&#10;× ：未着手&#10;N/A：不适用" sqref="G6:I34 G35:I68">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" prompt="○ ：完成&#10;△ ：进行中&#10;× ：未着手&#10;N/A：不适用" sqref="G6:I56">
       <formula1>"○,△,×,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7667,5 +7403,6 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>